--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit1_2_DownSamplingR.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit1_2_DownSamplingR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952F472C-4DB3-47B8-8AD2-F4131FB780BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC85C675-0095-44CF-818E-F65E024AD826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{427F1CDB-5AAB-483C-A031-4C1182026265}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{427F1CDB-5AAB-483C-A031-4C1182026265}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="88">
   <si>
     <t>OP_Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -388,6 +388,10 @@
     <t>32*(24/4)*2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Requant_Sel[3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -618,10 +622,34 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -633,31 +661,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1123,23 +1127,26 @@
       <c r="M5" s="8" t="s">
         <v>77</v>
       </c>
+      <c r="N5" s="7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="D7" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
       <c r="L7" s="9" t="s">
         <v>0</v>
       </c>
@@ -1165,14 +1172,14 @@
       <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
       <c r="L8" s="11" t="s">
         <v>5</v>
       </c>
@@ -1208,14 +1215,14 @@
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C9" s="17"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
       <c r="L9" s="12" t="s">
         <v>15</v>
       </c>
@@ -1232,14 +1239,14 @@
       <c r="U9" s="10"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C10" s="17"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
       <c r="L10" s="14" t="s">
         <v>17</v>
       </c>
@@ -1263,14 +1270,14 @@
       <c r="U10" s="10"/>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C11" s="17"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
       <c r="L11" s="15" t="s">
         <v>23</v>
       </c>
@@ -1292,22 +1299,22 @@
       <c r="B12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="E12" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
       <c r="L12" s="9" t="s">
         <v>0</v>
       </c>
@@ -1333,14 +1340,14 @@
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
       <c r="L13" s="11" t="s">
         <v>5</v>
       </c>
@@ -1376,14 +1383,14 @@
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
       <c r="L14" s="12" t="s">
         <v>15</v>
       </c>
@@ -1409,14 +1416,14 @@
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
       <c r="L15" s="14" t="s">
         <v>17</v>
       </c>
@@ -1440,14 +1447,14 @@
       <c r="U15" s="10"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
       <c r="L16" s="15" t="s">
         <v>23</v>
       </c>
@@ -1469,24 +1476,24 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="18" t="s">
+      <c r="D17" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
+      <c r="F17" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
       <c r="L17" s="9" t="s">
         <v>0</v>
       </c>
@@ -1512,14 +1519,14 @@
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
       <c r="L18" s="11" t="s">
         <v>5</v>
       </c>
@@ -1555,14 +1562,14 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C19" s="17"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
       <c r="L19" s="12" t="s">
         <v>15</v>
       </c>
@@ -1588,14 +1595,14 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C20" s="17"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
       <c r="L20" s="14" t="s">
         <v>17</v>
       </c>
@@ -1619,14 +1626,14 @@
       <c r="U20" s="10"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C21" s="17"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
       <c r="L21" s="15" t="s">
         <v>23</v>
       </c>
@@ -1645,24 +1652,24 @@
       <c r="U21" s="10"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="23"/>
-      <c r="F22" s="18" t="s">
+      <c r="D22" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="22"/>
+      <c r="F22" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="17"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="21"/>
       <c r="L22" s="9" t="s">
         <v>0</v>
       </c>
@@ -1685,14 +1692,14 @@
       <c r="U22" s="10"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="21"/>
       <c r="L23" s="11" t="s">
         <v>5</v>
       </c>
@@ -1728,14 +1735,14 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="17"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="21"/>
       <c r="L24" s="12" t="s">
         <v>15</v>
       </c>
@@ -1761,14 +1768,14 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="17"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="21"/>
       <c r="L25" s="14" t="s">
         <v>17</v>
       </c>
@@ -1791,14 +1798,14 @@
       <c r="U25" s="10"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="21"/>
       <c r="L26" s="15" t="s">
         <v>23</v>
       </c>
@@ -1827,26 +1834,26 @@
       <c r="B29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I29" s="25" t="s">
+      <c r="E29" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="22"/>
+      <c r="G29" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J29" s="17"/>
+      <c r="J29" s="21"/>
       <c r="L29" s="9" t="s">
         <v>0</v>
       </c>
@@ -1872,14 +1879,14 @@
       <c r="B30">
         <v>3</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="17"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="21"/>
       <c r="L30" s="11" t="s">
         <v>5</v>
       </c>
@@ -1915,14 +1922,14 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="17"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="21"/>
       <c r="L31" s="12" t="s">
         <v>15</v>
       </c>
@@ -1948,14 +1955,14 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="17"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="21"/>
       <c r="L32" s="14" t="s">
         <v>17</v>
       </c>
@@ -1979,14 +1986,14 @@
       <c r="U32" s="10"/>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="17"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="21"/>
       <c r="L33" s="15" t="s">
         <v>23</v>
       </c>
@@ -2003,24 +2010,24 @@
       <c r="U33" s="10"/>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34" s="18" t="s">
+      <c r="D34" s="21"/>
+      <c r="E34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="22"/>
+      <c r="G34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="22" t="s">
+      <c r="J34" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="9" t="s">
@@ -2045,14 +2052,14 @@
       <c r="U34" s="10"/>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="22"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="26"/>
       <c r="L35" s="11" t="s">
         <v>5</v>
       </c>
@@ -2088,14 +2095,14 @@
       </c>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="22"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="26"/>
       <c r="L36" s="12" t="s">
         <v>15</v>
       </c>
@@ -2121,14 +2128,14 @@
       </c>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="22"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="26"/>
       <c r="L37" s="14" t="s">
         <v>17</v>
       </c>
@@ -2151,14 +2158,14 @@
       <c r="U37" s="10"/>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="22"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="26"/>
       <c r="L38" s="15" t="s">
         <v>23</v>
       </c>
@@ -2178,26 +2185,26 @@
       <c r="B39" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="D39" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="27" t="s">
+      <c r="F39" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="21"/>
+      <c r="J39" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L39" s="9" t="s">
@@ -2225,14 +2232,14 @@
       <c r="B40">
         <v>4</v>
       </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="27"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="20"/>
       <c r="L40" s="11" t="s">
         <v>5</v>
       </c>
@@ -2271,14 +2278,14 @@
       <c r="B41" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="27"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="20"/>
       <c r="L41" s="12" t="s">
         <v>15</v>
       </c>
@@ -2307,14 +2314,14 @@
       <c r="B42">
         <v>0</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="27"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="20"/>
       <c r="L42" s="14" t="s">
         <v>17</v>
       </c>
@@ -2339,14 +2346,14 @@
       <c r="U42" s="10"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C43" s="17"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="27"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="20"/>
       <c r="L43" s="15" t="s">
         <v>23</v>
       </c>
@@ -2365,26 +2372,26 @@
       <c r="U43" s="10"/>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44" s="23"/>
-      <c r="F44" s="18" t="s">
+      <c r="D44" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="22"/>
+      <c r="F44" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G44" s="18" t="s">
+      <c r="G44" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H44" s="18" t="s">
+      <c r="H44" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I44" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" s="17"/>
+      <c r="I44" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44" s="21"/>
       <c r="L44" s="9" t="s">
         <v>0</v>
       </c>
@@ -2407,14 +2414,14 @@
       <c r="U44" s="10"/>
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="17"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="21"/>
       <c r="L45" s="11" t="s">
         <v>5</v>
       </c>
@@ -2450,14 +2457,14 @@
       </c>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="17"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="21"/>
       <c r="L46" s="12" t="s">
         <v>15</v>
       </c>
@@ -2483,14 +2490,14 @@
       </c>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="17"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="21"/>
       <c r="L47" s="14" t="s">
         <v>17</v>
       </c>
@@ -2513,14 +2520,14 @@
       <c r="U47" s="10"/>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="17"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="21"/>
       <c r="L48" s="15" t="s">
         <v>23</v>
       </c>
@@ -2543,26 +2550,26 @@
       <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E50" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="17"/>
-      <c r="I50" s="25" t="s">
+      <c r="E50" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="21"/>
+      <c r="I50" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J50" s="17"/>
+      <c r="J50" s="21"/>
       <c r="L50" s="9" t="s">
         <v>0</v>
       </c>
@@ -2588,14 +2595,14 @@
       <c r="B51">
         <v>5</v>
       </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="17"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="21"/>
       <c r="L51" s="11" t="s">
         <v>5</v>
       </c>
@@ -2631,14 +2638,14 @@
       </c>
     </row>
     <row r="52" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C52" s="17"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="17"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="21"/>
       <c r="L52" s="12" t="s">
         <v>15</v>
       </c>
@@ -2664,14 +2671,14 @@
       </c>
     </row>
     <row r="53" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C53" s="17"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="17"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="21"/>
       <c r="L53" s="14" t="s">
         <v>17</v>
       </c>
@@ -2695,14 +2702,14 @@
       <c r="U53" s="10"/>
     </row>
     <row r="54" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C54" s="17"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="17"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="21"/>
       <c r="L54" s="15" t="s">
         <v>23</v>
       </c>
@@ -2719,24 +2726,24 @@
       <c r="U54" s="10"/>
     </row>
     <row r="55" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="17"/>
-      <c r="I55" s="18" t="s">
+      <c r="D55" s="21"/>
+      <c r="E55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="21"/>
+      <c r="I55" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J55" s="22" t="s">
+      <c r="J55" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L55" s="9" t="s">
@@ -2761,14 +2768,14 @@
       <c r="U55" s="10"/>
     </row>
     <row r="56" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="22"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="26"/>
       <c r="L56" s="11" t="s">
         <v>5</v>
       </c>
@@ -2804,14 +2811,14 @@
       </c>
     </row>
     <row r="57" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="22"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="26"/>
       <c r="L57" s="12" t="s">
         <v>15</v>
       </c>
@@ -2837,14 +2844,14 @@
       </c>
     </row>
     <row r="58" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="22"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="26"/>
       <c r="L58" s="14" t="s">
         <v>17</v>
       </c>
@@ -2867,14 +2874,14 @@
       <c r="U58" s="10"/>
     </row>
     <row r="59" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="22"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="26"/>
       <c r="L59" s="15" t="s">
         <v>23</v>
       </c>
@@ -2894,26 +2901,26 @@
       <c r="B60" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="18" t="s">
+      <c r="D60" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F60" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I60" s="17"/>
-      <c r="J60" s="27" t="s">
+      <c r="F60" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H60" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" s="21"/>
+      <c r="J60" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L60" s="9" t="s">
@@ -2941,14 +2948,14 @@
       <c r="B61">
         <v>6</v>
       </c>
-      <c r="C61" s="17"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="27"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="20"/>
       <c r="L61" s="11" t="s">
         <v>5</v>
       </c>
@@ -2987,14 +2994,14 @@
       <c r="B62" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="17"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="27"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="20"/>
       <c r="L62" s="12" t="s">
         <v>15</v>
       </c>
@@ -3023,14 +3030,14 @@
       <c r="B63">
         <v>1</v>
       </c>
-      <c r="C63" s="17"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="27"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="20"/>
       <c r="L63" s="14" t="s">
         <v>17</v>
       </c>
@@ -3055,14 +3062,14 @@
       <c r="U63" s="10"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C64" s="17"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="27"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="20"/>
       <c r="L64" s="15" t="s">
         <v>23</v>
       </c>
@@ -3081,26 +3088,26 @@
       <c r="U64" s="10"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D65" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="23"/>
-      <c r="F65" s="18" t="s">
+      <c r="D65" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G65" s="18" t="s">
+      <c r="G65" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H65" s="18" t="s">
+      <c r="H65" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I65" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" s="17"/>
+      <c r="I65" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" s="21"/>
       <c r="L65" s="9" t="s">
         <v>0</v>
       </c>
@@ -3123,14 +3130,14 @@
       <c r="U65" s="10"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="22"/>
-      <c r="J66" s="17"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="21"/>
       <c r="L66" s="11" t="s">
         <v>5</v>
       </c>
@@ -3166,14 +3173,14 @@
       </c>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="17"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="21"/>
       <c r="L67" s="12" t="s">
         <v>15</v>
       </c>
@@ -3199,14 +3206,14 @@
       </c>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="17"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="21"/>
       <c r="L68" s="14" t="s">
         <v>17</v>
       </c>
@@ -3229,14 +3236,14 @@
       <c r="U68" s="10"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="17"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="21"/>
       <c r="L69" s="15" t="s">
         <v>23</v>
       </c>
@@ -3259,26 +3266,26 @@
       <c r="B71" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E71" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F71" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I71" s="25" t="s">
+      <c r="E71" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F71" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I71" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J71" s="17"/>
+      <c r="J71" s="21"/>
       <c r="L71" s="9" t="s">
         <v>0</v>
       </c>
@@ -3304,14 +3311,14 @@
       <c r="B72">
         <v>7</v>
       </c>
-      <c r="C72" s="17"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="17"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="24"/>
+      <c r="J72" s="21"/>
       <c r="L72" s="11" t="s">
         <v>5</v>
       </c>
@@ -3347,14 +3354,14 @@
       </c>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C73" s="17"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="17"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="24"/>
+      <c r="J73" s="21"/>
       <c r="L73" s="12" t="s">
         <v>15</v>
       </c>
@@ -3380,14 +3387,14 @@
       </c>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C74" s="17"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="17"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="21"/>
       <c r="L74" s="14" t="s">
         <v>17</v>
       </c>
@@ -3411,14 +3418,14 @@
       <c r="U74" s="10"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C75" s="17"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="17"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="17"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="21"/>
+      <c r="H75" s="21"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="21"/>
       <c r="L75" s="15" t="s">
         <v>23</v>
       </c>
@@ -3435,24 +3442,24 @@
       <c r="U75" s="10"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C76" s="17" t="s">
+      <c r="C76" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="17"/>
-      <c r="H76" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I76" s="18" t="s">
+      <c r="D76" s="21"/>
+      <c r="E76" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J76" s="22" t="s">
+      <c r="J76" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L76" s="9" t="s">
@@ -3477,14 +3484,14 @@
       <c r="U76" s="10"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="18"/>
-      <c r="J77" s="22"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21"/>
+      <c r="I77" s="25"/>
+      <c r="J77" s="26"/>
       <c r="L77" s="11" t="s">
         <v>5</v>
       </c>
@@ -3520,14 +3527,14 @@
       </c>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C78" s="17"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="18"/>
-      <c r="J78" s="22"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="26"/>
       <c r="L78" s="12" t="s">
         <v>15</v>
       </c>
@@ -3553,14 +3560,14 @@
       </c>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="18"/>
-      <c r="J79" s="22"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="21"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="26"/>
       <c r="L79" s="14" t="s">
         <v>17</v>
       </c>
@@ -3583,14 +3590,14 @@
       <c r="U79" s="10"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="18"/>
-      <c r="J80" s="22"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="26"/>
       <c r="L80" s="15" t="s">
         <v>23</v>
       </c>
@@ -3610,26 +3617,26 @@
       <c r="B81" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C81" s="17" t="s">
+      <c r="C81" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D81" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E81" s="18" t="s">
+      <c r="D81" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F81" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I81" s="17"/>
-      <c r="J81" s="27" t="s">
+      <c r="F81" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I81" s="21"/>
+      <c r="J81" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L81" s="9" t="s">
@@ -3657,14 +3664,14 @@
       <c r="B82">
         <v>8</v>
       </c>
-      <c r="C82" s="17"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="18"/>
-      <c r="F82" s="17"/>
-      <c r="G82" s="22"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="17"/>
-      <c r="J82" s="27"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="20"/>
       <c r="L82" s="11" t="s">
         <v>5</v>
       </c>
@@ -3703,14 +3710,14 @@
       <c r="B83" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C83" s="17"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="18"/>
-      <c r="F83" s="17"/>
-      <c r="G83" s="22"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
-      <c r="J83" s="27"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="20"/>
       <c r="L83" s="12" t="s">
         <v>15</v>
       </c>
@@ -3739,14 +3746,14 @@
       <c r="B84">
         <v>2</v>
       </c>
-      <c r="C84" s="17"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="18"/>
-      <c r="F84" s="17"/>
-      <c r="G84" s="22"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="27"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="20"/>
       <c r="L84" s="14" t="s">
         <v>17</v>
       </c>
@@ -3771,14 +3778,14 @@
       <c r="U84" s="10"/>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C85" s="17"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="17"/>
-      <c r="G85" s="22"/>
-      <c r="H85" s="17"/>
-      <c r="I85" s="17"/>
-      <c r="J85" s="27"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="22"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="21"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="20"/>
       <c r="L85" s="15" t="s">
         <v>23</v>
       </c>
@@ -3797,26 +3804,26 @@
       <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D86" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E86" s="23"/>
-      <c r="F86" s="18" t="s">
+      <c r="D86" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="22"/>
+      <c r="F86" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G86" s="18" t="s">
+      <c r="G86" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H86" s="18" t="s">
+      <c r="H86" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I86" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J86" s="23"/>
+      <c r="I86" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J86" s="22"/>
       <c r="L86" s="9" t="s">
         <v>0</v>
       </c>
@@ -3839,14 +3846,14 @@
       <c r="U86" s="10"/>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="18"/>
-      <c r="I87" s="22"/>
-      <c r="J87" s="23"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="22"/>
       <c r="L87" s="11" t="s">
         <v>5</v>
       </c>
@@ -3882,14 +3889,14 @@
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="22"/>
-      <c r="J88" s="23"/>
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="26"/>
+      <c r="J88" s="22"/>
       <c r="L88" s="12" t="s">
         <v>15</v>
       </c>
@@ -3915,14 +3922,14 @@
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-      <c r="H89" s="18"/>
-      <c r="I89" s="22"/>
-      <c r="J89" s="23"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="H89" s="25"/>
+      <c r="I89" s="26"/>
+      <c r="J89" s="22"/>
       <c r="L89" s="14" t="s">
         <v>17</v>
       </c>
@@ -3945,14 +3952,14 @@
       <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C90" s="17"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
-      <c r="H90" s="18"/>
-      <c r="I90" s="22"/>
-      <c r="J90" s="23"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="26"/>
+      <c r="J90" s="22"/>
       <c r="L90" s="15" t="s">
         <v>23</v>
       </c>
@@ -3981,26 +3988,26 @@
       <c r="B93" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C93" s="17" t="s">
+      <c r="C93" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D93" s="18" t="s">
+      <c r="D93" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E93" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F93" s="23"/>
-      <c r="G93" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I93" s="25" t="s">
+      <c r="E93" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F93" s="22"/>
+      <c r="G93" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H93" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I93" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J93" s="17"/>
+      <c r="J93" s="21"/>
       <c r="L93" s="9" t="s">
         <v>0</v>
       </c>
@@ -4026,14 +4033,14 @@
       <c r="B94">
         <v>9</v>
       </c>
-      <c r="C94" s="17"/>
-      <c r="D94" s="18"/>
-      <c r="E94" s="23"/>
-      <c r="F94" s="23"/>
-      <c r="G94" s="17"/>
-      <c r="H94" s="22"/>
-      <c r="I94" s="26"/>
-      <c r="J94" s="17"/>
+      <c r="C94" s="21"/>
+      <c r="D94" s="25"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="26"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="21"/>
       <c r="L94" s="11" t="s">
         <v>5</v>
       </c>
@@ -4069,14 +4076,14 @@
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C95" s="17"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="23"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="17"/>
-      <c r="H95" s="22"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="17"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="25"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="26"/>
+      <c r="I95" s="24"/>
+      <c r="J95" s="21"/>
       <c r="L95" s="12" t="s">
         <v>15</v>
       </c>
@@ -4102,14 +4109,14 @@
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C96" s="17"/>
-      <c r="D96" s="18"/>
-      <c r="E96" s="23"/>
-      <c r="F96" s="23"/>
-      <c r="G96" s="17"/>
-      <c r="H96" s="22"/>
-      <c r="I96" s="26"/>
-      <c r="J96" s="17"/>
+      <c r="C96" s="21"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="21"/>
+      <c r="H96" s="26"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="21"/>
       <c r="L96" s="14" t="s">
         <v>17</v>
       </c>
@@ -4133,14 +4140,14 @@
       <c r="U96" s="10"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C97" s="17"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="22"/>
-      <c r="I97" s="26"/>
-      <c r="J97" s="17"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="24"/>
+      <c r="J97" s="21"/>
       <c r="L97" s="15" t="s">
         <v>23</v>
       </c>
@@ -4157,24 +4164,24 @@
       <c r="U97" s="10"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C98" s="17" t="s">
+      <c r="C98" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D98" s="17"/>
-      <c r="E98" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F98" s="23"/>
-      <c r="G98" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I98" s="18" t="s">
+      <c r="D98" s="21"/>
+      <c r="E98" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98" s="22"/>
+      <c r="G98" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H98" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I98" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J98" s="22" t="s">
+      <c r="J98" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L98" s="9" t="s">
@@ -4199,14 +4206,14 @@
       <c r="U98" s="10"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C99" s="17"/>
-      <c r="D99" s="17"/>
-      <c r="E99" s="17"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="17"/>
-      <c r="H99" s="17"/>
-      <c r="I99" s="18"/>
-      <c r="J99" s="22"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="25"/>
+      <c r="J99" s="26"/>
       <c r="L99" s="11" t="s">
         <v>5</v>
       </c>
@@ -4242,14 +4249,14 @@
       </c>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C100" s="17"/>
-      <c r="D100" s="17"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="23"/>
-      <c r="G100" s="17"/>
-      <c r="H100" s="17"/>
-      <c r="I100" s="18"/>
-      <c r="J100" s="22"/>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="21"/>
+      <c r="H100" s="21"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="26"/>
       <c r="L100" s="12" t="s">
         <v>15</v>
       </c>
@@ -4275,14 +4282,14 @@
       </c>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C101" s="17"/>
-      <c r="D101" s="17"/>
-      <c r="E101" s="17"/>
-      <c r="F101" s="23"/>
-      <c r="G101" s="17"/>
-      <c r="H101" s="17"/>
-      <c r="I101" s="18"/>
-      <c r="J101" s="22"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="21"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="25"/>
+      <c r="J101" s="26"/>
       <c r="L101" s="14" t="s">
         <v>17</v>
       </c>
@@ -4305,14 +4312,14 @@
       <c r="U101" s="10"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C102" s="17"/>
-      <c r="D102" s="17"/>
-      <c r="E102" s="17"/>
-      <c r="F102" s="23"/>
-      <c r="G102" s="17"/>
-      <c r="H102" s="17"/>
-      <c r="I102" s="18"/>
-      <c r="J102" s="22"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="21"/>
+      <c r="H102" s="21"/>
+      <c r="I102" s="25"/>
+      <c r="J102" s="26"/>
       <c r="L102" s="15" t="s">
         <v>23</v>
       </c>
@@ -4332,26 +4339,26 @@
       <c r="B103" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C103" s="17" t="s">
+      <c r="C103" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D103" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E103" s="18" t="s">
+      <c r="D103" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F103" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I103" s="17"/>
-      <c r="J103" s="27" t="s">
+      <c r="F103" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H103" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I103" s="21"/>
+      <c r="J103" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L103" s="9" t="s">
@@ -4379,14 +4386,14 @@
       <c r="B104">
         <v>10</v>
       </c>
-      <c r="C104" s="17"/>
-      <c r="D104" s="23"/>
-      <c r="E104" s="18"/>
-      <c r="F104" s="22"/>
-      <c r="G104" s="17"/>
-      <c r="H104" s="17"/>
-      <c r="I104" s="17"/>
-      <c r="J104" s="27"/>
+      <c r="C104" s="21"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="25"/>
+      <c r="F104" s="26"/>
+      <c r="G104" s="21"/>
+      <c r="H104" s="21"/>
+      <c r="I104" s="21"/>
+      <c r="J104" s="20"/>
       <c r="L104" s="11" t="s">
         <v>5</v>
       </c>
@@ -4425,14 +4432,14 @@
       <c r="B105" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C105" s="17"/>
-      <c r="D105" s="23"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="22"/>
-      <c r="G105" s="17"/>
-      <c r="H105" s="17"/>
-      <c r="I105" s="17"/>
-      <c r="J105" s="27"/>
+      <c r="C105" s="21"/>
+      <c r="D105" s="22"/>
+      <c r="E105" s="25"/>
+      <c r="F105" s="26"/>
+      <c r="G105" s="21"/>
+      <c r="H105" s="21"/>
+      <c r="I105" s="21"/>
+      <c r="J105" s="20"/>
       <c r="L105" s="12" t="s">
         <v>15</v>
       </c>
@@ -4461,14 +4468,14 @@
       <c r="B106">
         <v>3</v>
       </c>
-      <c r="C106" s="17"/>
-      <c r="D106" s="23"/>
-      <c r="E106" s="18"/>
-      <c r="F106" s="22"/>
-      <c r="G106" s="17"/>
-      <c r="H106" s="17"/>
-      <c r="I106" s="17"/>
-      <c r="J106" s="27"/>
+      <c r="C106" s="21"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="25"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="21"/>
+      <c r="H106" s="21"/>
+      <c r="I106" s="21"/>
+      <c r="J106" s="20"/>
       <c r="L106" s="14" t="s">
         <v>17</v>
       </c>
@@ -4493,14 +4500,14 @@
       <c r="U106" s="10"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C107" s="17"/>
-      <c r="D107" s="23"/>
-      <c r="E107" s="18"/>
-      <c r="F107" s="22"/>
-      <c r="G107" s="17"/>
-      <c r="H107" s="17"/>
-      <c r="I107" s="17"/>
-      <c r="J107" s="27"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="22"/>
+      <c r="E107" s="25"/>
+      <c r="F107" s="26"/>
+      <c r="G107" s="21"/>
+      <c r="H107" s="21"/>
+      <c r="I107" s="21"/>
+      <c r="J107" s="20"/>
       <c r="L107" s="15" t="s">
         <v>23</v>
       </c>
@@ -4519,26 +4526,26 @@
       <c r="U107" s="10"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C108" s="17" t="s">
+      <c r="C108" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D108" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E108" s="23"/>
-      <c r="F108" s="18" t="s">
+      <c r="D108" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" s="22"/>
+      <c r="F108" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G108" s="18" t="s">
+      <c r="G108" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H108" s="18" t="s">
+      <c r="H108" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I108" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J108" s="17"/>
+      <c r="I108" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J108" s="21"/>
       <c r="L108" s="9" t="s">
         <v>0</v>
       </c>
@@ -4561,14 +4568,14 @@
       <c r="U108" s="10"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C109" s="17"/>
-      <c r="D109" s="17"/>
-      <c r="E109" s="23"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="18"/>
-      <c r="H109" s="18"/>
-      <c r="I109" s="22"/>
-      <c r="J109" s="17"/>
+      <c r="C109" s="21"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="25"/>
+      <c r="G109" s="25"/>
+      <c r="H109" s="25"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="21"/>
       <c r="L109" s="11" t="s">
         <v>5</v>
       </c>
@@ -4604,14 +4611,14 @@
       </c>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C110" s="17"/>
-      <c r="D110" s="17"/>
-      <c r="E110" s="23"/>
-      <c r="F110" s="18"/>
-      <c r="G110" s="18"/>
-      <c r="H110" s="18"/>
-      <c r="I110" s="22"/>
-      <c r="J110" s="17"/>
+      <c r="C110" s="21"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25"/>
+      <c r="H110" s="25"/>
+      <c r="I110" s="26"/>
+      <c r="J110" s="21"/>
       <c r="L110" s="12" t="s">
         <v>15</v>
       </c>
@@ -4637,14 +4644,14 @@
       </c>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C111" s="17"/>
-      <c r="D111" s="17"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="18"/>
-      <c r="G111" s="18"/>
-      <c r="H111" s="18"/>
-      <c r="I111" s="22"/>
-      <c r="J111" s="17"/>
+      <c r="C111" s="21"/>
+      <c r="D111" s="21"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
+      <c r="H111" s="25"/>
+      <c r="I111" s="26"/>
+      <c r="J111" s="21"/>
       <c r="L111" s="14" t="s">
         <v>17</v>
       </c>
@@ -4667,14 +4674,14 @@
       <c r="U111" s="10"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C112" s="17"/>
-      <c r="D112" s="17"/>
-      <c r="E112" s="23"/>
-      <c r="F112" s="18"/>
-      <c r="G112" s="18"/>
-      <c r="H112" s="18"/>
-      <c r="I112" s="22"/>
-      <c r="J112" s="17"/>
+      <c r="C112" s="21"/>
+      <c r="D112" s="21"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25"/>
+      <c r="H112" s="25"/>
+      <c r="I112" s="26"/>
+      <c r="J112" s="21"/>
       <c r="L112" s="15" t="s">
         <v>23</v>
       </c>
@@ -4697,26 +4704,26 @@
       <c r="B114" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C114" s="17" t="s">
+      <c r="C114" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D114" s="18" t="s">
+      <c r="D114" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E114" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F114" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G114" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="17"/>
-      <c r="I114" s="25" t="s">
+      <c r="E114" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F114" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H114" s="21"/>
+      <c r="I114" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J114" s="17"/>
+      <c r="J114" s="21"/>
       <c r="L114" s="9" t="s">
         <v>0</v>
       </c>
@@ -4742,14 +4749,14 @@
       <c r="B115">
         <v>11</v>
       </c>
-      <c r="C115" s="17"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="23"/>
-      <c r="F115" s="17"/>
-      <c r="G115" s="22"/>
-      <c r="H115" s="17"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="17"/>
+      <c r="C115" s="21"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="21"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="21"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="21"/>
       <c r="L115" s="11" t="s">
         <v>5</v>
       </c>
@@ -4785,14 +4792,14 @@
       </c>
     </row>
     <row r="116" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C116" s="17"/>
-      <c r="D116" s="18"/>
-      <c r="E116" s="23"/>
-      <c r="F116" s="17"/>
-      <c r="G116" s="22"/>
-      <c r="H116" s="17"/>
-      <c r="I116" s="26"/>
-      <c r="J116" s="17"/>
+      <c r="C116" s="21"/>
+      <c r="D116" s="25"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="21"/>
+      <c r="G116" s="26"/>
+      <c r="H116" s="21"/>
+      <c r="I116" s="24"/>
+      <c r="J116" s="21"/>
       <c r="L116" s="12" t="s">
         <v>15</v>
       </c>
@@ -4818,14 +4825,14 @@
       </c>
     </row>
     <row r="117" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C117" s="17"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="23"/>
-      <c r="F117" s="17"/>
-      <c r="G117" s="22"/>
-      <c r="H117" s="17"/>
-      <c r="I117" s="26"/>
-      <c r="J117" s="17"/>
+      <c r="C117" s="21"/>
+      <c r="D117" s="25"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="21"/>
+      <c r="G117" s="26"/>
+      <c r="H117" s="21"/>
+      <c r="I117" s="24"/>
+      <c r="J117" s="21"/>
       <c r="L117" s="14" t="s">
         <v>17</v>
       </c>
@@ -4849,14 +4856,14 @@
       <c r="U117" s="10"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C118" s="17"/>
-      <c r="D118" s="18"/>
-      <c r="E118" s="23"/>
-      <c r="F118" s="17"/>
-      <c r="G118" s="22"/>
-      <c r="H118" s="17"/>
-      <c r="I118" s="26"/>
-      <c r="J118" s="17"/>
+      <c r="C118" s="21"/>
+      <c r="D118" s="25"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="21"/>
+      <c r="G118" s="26"/>
+      <c r="H118" s="21"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="21"/>
       <c r="L118" s="15" t="s">
         <v>23</v>
       </c>
@@ -4873,24 +4880,24 @@
       <c r="U118" s="10"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C119" s="17" t="s">
+      <c r="C119" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D119" s="17"/>
-      <c r="E119" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F119" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="17"/>
-      <c r="I119" s="18" t="s">
+      <c r="D119" s="21"/>
+      <c r="E119" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F119" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H119" s="21"/>
+      <c r="I119" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J119" s="22" t="s">
+      <c r="J119" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L119" s="9" t="s">
@@ -4915,14 +4922,14 @@
       <c r="U119" s="10"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C120" s="17"/>
-      <c r="D120" s="17"/>
-      <c r="E120" s="17"/>
-      <c r="F120" s="17"/>
-      <c r="G120" s="17"/>
-      <c r="H120" s="17"/>
-      <c r="I120" s="18"/>
-      <c r="J120" s="22"/>
+      <c r="C120" s="21"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="21"/>
+      <c r="G120" s="21"/>
+      <c r="H120" s="21"/>
+      <c r="I120" s="25"/>
+      <c r="J120" s="26"/>
       <c r="L120" s="11" t="s">
         <v>5</v>
       </c>
@@ -4958,14 +4965,14 @@
       </c>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C121" s="17"/>
-      <c r="D121" s="17"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="17"/>
-      <c r="G121" s="17"/>
-      <c r="H121" s="17"/>
-      <c r="I121" s="18"/>
-      <c r="J121" s="22"/>
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="21"/>
+      <c r="G121" s="21"/>
+      <c r="H121" s="21"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="26"/>
       <c r="L121" s="12" t="s">
         <v>15</v>
       </c>
@@ -4991,14 +4998,14 @@
       </c>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C122" s="17"/>
-      <c r="D122" s="17"/>
-      <c r="E122" s="17"/>
-      <c r="F122" s="17"/>
-      <c r="G122" s="17"/>
-      <c r="H122" s="17"/>
-      <c r="I122" s="18"/>
-      <c r="J122" s="22"/>
+      <c r="C122" s="21"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="21"/>
+      <c r="F122" s="21"/>
+      <c r="G122" s="21"/>
+      <c r="H122" s="21"/>
+      <c r="I122" s="25"/>
+      <c r="J122" s="26"/>
       <c r="L122" s="14" t="s">
         <v>17</v>
       </c>
@@ -5021,14 +5028,14 @@
       <c r="U122" s="10"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C123" s="17"/>
-      <c r="D123" s="17"/>
-      <c r="E123" s="17"/>
-      <c r="F123" s="17"/>
-      <c r="G123" s="17"/>
-      <c r="H123" s="17"/>
-      <c r="I123" s="18"/>
-      <c r="J123" s="22"/>
+      <c r="C123" s="21"/>
+      <c r="D123" s="21"/>
+      <c r="E123" s="21"/>
+      <c r="F123" s="21"/>
+      <c r="G123" s="21"/>
+      <c r="H123" s="21"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="26"/>
       <c r="L123" s="15" t="s">
         <v>23</v>
       </c>
@@ -5048,26 +5055,26 @@
       <c r="B124" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C124" s="17" t="s">
+      <c r="C124" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D124" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E124" s="18" t="s">
+      <c r="D124" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E124" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F124" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G124" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I124" s="17"/>
-      <c r="J124" s="27" t="s">
+      <c r="F124" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H124" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I124" s="21"/>
+      <c r="J124" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L124" s="9" t="s">
@@ -5095,14 +5102,14 @@
       <c r="B125">
         <v>12</v>
       </c>
-      <c r="C125" s="17"/>
-      <c r="D125" s="23"/>
-      <c r="E125" s="18"/>
-      <c r="F125" s="17"/>
-      <c r="G125" s="17"/>
-      <c r="H125" s="22"/>
-      <c r="I125" s="17"/>
-      <c r="J125" s="27"/>
+      <c r="C125" s="21"/>
+      <c r="D125" s="22"/>
+      <c r="E125" s="25"/>
+      <c r="F125" s="21"/>
+      <c r="G125" s="21"/>
+      <c r="H125" s="26"/>
+      <c r="I125" s="21"/>
+      <c r="J125" s="20"/>
       <c r="L125" s="11" t="s">
         <v>5</v>
       </c>
@@ -5141,14 +5148,14 @@
       <c r="B126" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C126" s="17"/>
-      <c r="D126" s="23"/>
-      <c r="E126" s="18"/>
-      <c r="F126" s="17"/>
-      <c r="G126" s="17"/>
-      <c r="H126" s="22"/>
-      <c r="I126" s="17"/>
-      <c r="J126" s="27"/>
+      <c r="C126" s="21"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="25"/>
+      <c r="F126" s="21"/>
+      <c r="G126" s="21"/>
+      <c r="H126" s="26"/>
+      <c r="I126" s="21"/>
+      <c r="J126" s="20"/>
       <c r="L126" s="12" t="s">
         <v>15</v>
       </c>
@@ -5177,14 +5184,14 @@
       <c r="B127">
         <v>4</v>
       </c>
-      <c r="C127" s="17"/>
-      <c r="D127" s="23"/>
-      <c r="E127" s="18"/>
-      <c r="F127" s="17"/>
-      <c r="G127" s="17"/>
-      <c r="H127" s="22"/>
-      <c r="I127" s="17"/>
-      <c r="J127" s="27"/>
+      <c r="C127" s="21"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="25"/>
+      <c r="F127" s="21"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="26"/>
+      <c r="I127" s="21"/>
+      <c r="J127" s="20"/>
       <c r="L127" s="14" t="s">
         <v>17</v>
       </c>
@@ -5209,14 +5216,14 @@
       <c r="U127" s="10"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C128" s="17"/>
-      <c r="D128" s="23"/>
-      <c r="E128" s="18"/>
-      <c r="F128" s="17"/>
-      <c r="G128" s="17"/>
-      <c r="H128" s="22"/>
-      <c r="I128" s="17"/>
-      <c r="J128" s="27"/>
+      <c r="C128" s="21"/>
+      <c r="D128" s="22"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="21"/>
+      <c r="G128" s="21"/>
+      <c r="H128" s="26"/>
+      <c r="I128" s="21"/>
+      <c r="J128" s="20"/>
       <c r="L128" s="15" t="s">
         <v>23</v>
       </c>
@@ -5233,26 +5240,26 @@
       <c r="U128" s="10"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C129" s="17" t="s">
+      <c r="C129" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D129" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E129" s="23"/>
-      <c r="F129" s="18" t="s">
+      <c r="D129" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E129" s="22"/>
+      <c r="F129" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G129" s="18" t="s">
+      <c r="G129" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H129" s="18" t="s">
+      <c r="H129" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I129" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J129" s="17"/>
+      <c r="I129" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J129" s="21"/>
       <c r="L129" s="9" t="s">
         <v>0</v>
       </c>
@@ -5275,14 +5282,14 @@
       <c r="U129" s="10"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C130" s="17"/>
-      <c r="D130" s="17"/>
-      <c r="E130" s="23"/>
-      <c r="F130" s="18"/>
-      <c r="G130" s="18"/>
-      <c r="H130" s="18"/>
-      <c r="I130" s="22"/>
-      <c r="J130" s="17"/>
+      <c r="C130" s="21"/>
+      <c r="D130" s="21"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="25"/>
+      <c r="G130" s="25"/>
+      <c r="H130" s="25"/>
+      <c r="I130" s="26"/>
+      <c r="J130" s="21"/>
       <c r="L130" s="11" t="s">
         <v>5</v>
       </c>
@@ -5318,14 +5325,14 @@
       </c>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C131" s="17"/>
-      <c r="D131" s="17"/>
-      <c r="E131" s="23"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="18"/>
-      <c r="H131" s="18"/>
-      <c r="I131" s="22"/>
-      <c r="J131" s="17"/>
+      <c r="C131" s="21"/>
+      <c r="D131" s="21"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="25"/>
+      <c r="G131" s="25"/>
+      <c r="H131" s="25"/>
+      <c r="I131" s="26"/>
+      <c r="J131" s="21"/>
       <c r="L131" s="12" t="s">
         <v>15</v>
       </c>
@@ -5351,14 +5358,14 @@
       </c>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C132" s="17"/>
-      <c r="D132" s="17"/>
-      <c r="E132" s="23"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="18"/>
-      <c r="H132" s="18"/>
-      <c r="I132" s="22"/>
-      <c r="J132" s="17"/>
+      <c r="C132" s="21"/>
+      <c r="D132" s="21"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="25"/>
+      <c r="G132" s="25"/>
+      <c r="H132" s="25"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="21"/>
       <c r="L132" s="14" t="s">
         <v>17</v>
       </c>
@@ -5381,14 +5388,14 @@
       <c r="U132" s="10"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C133" s="17"/>
-      <c r="D133" s="17"/>
-      <c r="E133" s="23"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="18"/>
-      <c r="H133" s="18"/>
-      <c r="I133" s="22"/>
-      <c r="J133" s="17"/>
+      <c r="C133" s="21"/>
+      <c r="D133" s="21"/>
+      <c r="E133" s="22"/>
+      <c r="F133" s="25"/>
+      <c r="G133" s="25"/>
+      <c r="H133" s="25"/>
+      <c r="I133" s="26"/>
+      <c r="J133" s="21"/>
       <c r="L133" s="15" t="s">
         <v>23</v>
       </c>
@@ -5411,26 +5418,26 @@
       <c r="B135" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C135" s="17" t="s">
+      <c r="C135" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D135" s="18" t="s">
+      <c r="D135" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E135" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F135" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="17"/>
-      <c r="H135" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I135" s="25" t="s">
+      <c r="E135" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F135" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="21"/>
+      <c r="H135" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I135" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J135" s="17"/>
+      <c r="J135" s="21"/>
       <c r="L135" s="9" t="s">
         <v>0</v>
       </c>
@@ -5456,14 +5463,14 @@
       <c r="B136">
         <v>13</v>
       </c>
-      <c r="C136" s="17"/>
-      <c r="D136" s="18"/>
-      <c r="E136" s="23"/>
-      <c r="F136" s="22"/>
-      <c r="G136" s="17"/>
-      <c r="H136" s="17"/>
-      <c r="I136" s="26"/>
-      <c r="J136" s="17"/>
+      <c r="C136" s="21"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="22"/>
+      <c r="F136" s="26"/>
+      <c r="G136" s="21"/>
+      <c r="H136" s="21"/>
+      <c r="I136" s="24"/>
+      <c r="J136" s="21"/>
       <c r="L136" s="11" t="s">
         <v>5</v>
       </c>
@@ -5499,14 +5506,14 @@
       </c>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C137" s="17"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="23"/>
-      <c r="F137" s="22"/>
-      <c r="G137" s="17"/>
-      <c r="H137" s="17"/>
-      <c r="I137" s="26"/>
-      <c r="J137" s="17"/>
+      <c r="C137" s="21"/>
+      <c r="D137" s="25"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="21"/>
+      <c r="H137" s="21"/>
+      <c r="I137" s="24"/>
+      <c r="J137" s="21"/>
       <c r="L137" s="12" t="s">
         <v>15</v>
       </c>
@@ -5532,14 +5539,14 @@
       </c>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C138" s="17"/>
-      <c r="D138" s="18"/>
-      <c r="E138" s="23"/>
-      <c r="F138" s="22"/>
-      <c r="G138" s="17"/>
-      <c r="H138" s="17"/>
-      <c r="I138" s="26"/>
-      <c r="J138" s="17"/>
+      <c r="C138" s="21"/>
+      <c r="D138" s="25"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="21"/>
+      <c r="H138" s="21"/>
+      <c r="I138" s="24"/>
+      <c r="J138" s="21"/>
       <c r="L138" s="14" t="s">
         <v>17</v>
       </c>
@@ -5563,14 +5570,14 @@
       <c r="U138" s="10"/>
     </row>
     <row r="139" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C139" s="17"/>
-      <c r="D139" s="18"/>
-      <c r="E139" s="23"/>
-      <c r="F139" s="22"/>
-      <c r="G139" s="17"/>
-      <c r="H139" s="17"/>
-      <c r="I139" s="26"/>
-      <c r="J139" s="17"/>
+      <c r="C139" s="21"/>
+      <c r="D139" s="25"/>
+      <c r="E139" s="22"/>
+      <c r="F139" s="26"/>
+      <c r="G139" s="21"/>
+      <c r="H139" s="21"/>
+      <c r="I139" s="24"/>
+      <c r="J139" s="21"/>
       <c r="L139" s="15" t="s">
         <v>23</v>
       </c>
@@ -5587,24 +5594,24 @@
       <c r="U139" s="10"/>
     </row>
     <row r="140" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C140" s="17" t="s">
+      <c r="C140" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D140" s="17"/>
-      <c r="E140" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F140" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G140" s="17"/>
-      <c r="H140" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I140" s="18" t="s">
+      <c r="D140" s="21"/>
+      <c r="E140" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F140" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I140" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J140" s="22" t="s">
+      <c r="J140" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L140" s="9" t="s">
@@ -5629,14 +5636,14 @@
       <c r="U140" s="10"/>
     </row>
     <row r="141" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C141" s="17"/>
-      <c r="D141" s="17"/>
-      <c r="E141" s="17"/>
-      <c r="F141" s="17"/>
-      <c r="G141" s="17"/>
-      <c r="H141" s="17"/>
-      <c r="I141" s="18"/>
-      <c r="J141" s="22"/>
+      <c r="C141" s="21"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="21"/>
+      <c r="G141" s="21"/>
+      <c r="H141" s="21"/>
+      <c r="I141" s="25"/>
+      <c r="J141" s="26"/>
       <c r="L141" s="11" t="s">
         <v>5</v>
       </c>
@@ -5672,14 +5679,14 @@
       </c>
     </row>
     <row r="142" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C142" s="17"/>
-      <c r="D142" s="17"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="17"/>
-      <c r="G142" s="17"/>
-      <c r="H142" s="17"/>
-      <c r="I142" s="18"/>
-      <c r="J142" s="22"/>
+      <c r="C142" s="21"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21"/>
+      <c r="H142" s="21"/>
+      <c r="I142" s="25"/>
+      <c r="J142" s="26"/>
       <c r="L142" s="12" t="s">
         <v>15</v>
       </c>
@@ -5705,14 +5712,14 @@
       </c>
     </row>
     <row r="143" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C143" s="17"/>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="17"/>
-      <c r="G143" s="17"/>
-      <c r="H143" s="17"/>
-      <c r="I143" s="18"/>
-      <c r="J143" s="22"/>
+      <c r="C143" s="21"/>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21"/>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="26"/>
       <c r="L143" s="14" t="s">
         <v>17</v>
       </c>
@@ -5735,14 +5742,14 @@
       <c r="U143" s="10"/>
     </row>
     <row r="144" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C144" s="17"/>
-      <c r="D144" s="17"/>
-      <c r="E144" s="17"/>
-      <c r="F144" s="17"/>
-      <c r="G144" s="17"/>
-      <c r="H144" s="17"/>
-      <c r="I144" s="18"/>
-      <c r="J144" s="22"/>
+      <c r="C144" s="21"/>
+      <c r="D144" s="21"/>
+      <c r="E144" s="21"/>
+      <c r="F144" s="21"/>
+      <c r="G144" s="21"/>
+      <c r="H144" s="21"/>
+      <c r="I144" s="25"/>
+      <c r="J144" s="26"/>
       <c r="L144" s="15" t="s">
         <v>23</v>
       </c>
@@ -5762,26 +5769,26 @@
       <c r="B145" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C145" s="17" t="s">
+      <c r="C145" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D145" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E145" s="18" t="s">
+      <c r="D145" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E145" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F145" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G145" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H145" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I145" s="17"/>
-      <c r="J145" s="27" t="s">
+      <c r="F145" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G145" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H145" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I145" s="21"/>
+      <c r="J145" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L145" s="9" t="s">
@@ -5809,14 +5816,14 @@
       <c r="B146">
         <v>14</v>
       </c>
-      <c r="C146" s="17"/>
-      <c r="D146" s="23"/>
-      <c r="E146" s="18"/>
-      <c r="F146" s="17"/>
-      <c r="G146" s="22"/>
-      <c r="H146" s="17"/>
-      <c r="I146" s="17"/>
-      <c r="J146" s="27"/>
+      <c r="C146" s="21"/>
+      <c r="D146" s="22"/>
+      <c r="E146" s="25"/>
+      <c r="F146" s="21"/>
+      <c r="G146" s="26"/>
+      <c r="H146" s="21"/>
+      <c r="I146" s="21"/>
+      <c r="J146" s="20"/>
       <c r="L146" s="11" t="s">
         <v>5</v>
       </c>
@@ -5855,14 +5862,14 @@
       <c r="B147" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C147" s="17"/>
-      <c r="D147" s="23"/>
-      <c r="E147" s="18"/>
-      <c r="F147" s="17"/>
-      <c r="G147" s="22"/>
-      <c r="H147" s="17"/>
-      <c r="I147" s="17"/>
-      <c r="J147" s="27"/>
+      <c r="C147" s="21"/>
+      <c r="D147" s="22"/>
+      <c r="E147" s="25"/>
+      <c r="F147" s="21"/>
+      <c r="G147" s="26"/>
+      <c r="H147" s="21"/>
+      <c r="I147" s="21"/>
+      <c r="J147" s="20"/>
       <c r="L147" s="12" t="s">
         <v>15</v>
       </c>
@@ -5891,14 +5898,14 @@
       <c r="B148">
         <v>5</v>
       </c>
-      <c r="C148" s="17"/>
-      <c r="D148" s="23"/>
-      <c r="E148" s="18"/>
-      <c r="F148" s="17"/>
-      <c r="G148" s="22"/>
-      <c r="H148" s="17"/>
-      <c r="I148" s="17"/>
-      <c r="J148" s="27"/>
+      <c r="C148" s="21"/>
+      <c r="D148" s="22"/>
+      <c r="E148" s="25"/>
+      <c r="F148" s="21"/>
+      <c r="G148" s="26"/>
+      <c r="H148" s="21"/>
+      <c r="I148" s="21"/>
+      <c r="J148" s="20"/>
       <c r="L148" s="14" t="s">
         <v>17</v>
       </c>
@@ -5923,14 +5930,14 @@
       <c r="U148" s="10"/>
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C149" s="17"/>
-      <c r="D149" s="23"/>
-      <c r="E149" s="18"/>
-      <c r="F149" s="17"/>
-      <c r="G149" s="22"/>
-      <c r="H149" s="17"/>
-      <c r="I149" s="17"/>
-      <c r="J149" s="27"/>
+      <c r="C149" s="21"/>
+      <c r="D149" s="22"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="21"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="21"/>
+      <c r="I149" s="21"/>
+      <c r="J149" s="20"/>
       <c r="L149" s="15" t="s">
         <v>23</v>
       </c>
@@ -5947,26 +5954,26 @@
       <c r="U149" s="10"/>
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C150" s="17" t="s">
+      <c r="C150" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D150" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E150" s="23"/>
-      <c r="F150" s="18" t="s">
+      <c r="D150" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E150" s="22"/>
+      <c r="F150" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G150" s="18" t="s">
+      <c r="G150" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H150" s="18" t="s">
+      <c r="H150" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I150" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J150" s="23"/>
+      <c r="I150" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J150" s="22"/>
       <c r="L150" s="9" t="s">
         <v>0</v>
       </c>
@@ -5989,14 +5996,14 @@
       <c r="U150" s="10"/>
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C151" s="17"/>
-      <c r="D151" s="17"/>
-      <c r="E151" s="23"/>
-      <c r="F151" s="18"/>
-      <c r="G151" s="18"/>
-      <c r="H151" s="18"/>
-      <c r="I151" s="22"/>
-      <c r="J151" s="23"/>
+      <c r="C151" s="21"/>
+      <c r="D151" s="21"/>
+      <c r="E151" s="22"/>
+      <c r="F151" s="25"/>
+      <c r="G151" s="25"/>
+      <c r="H151" s="25"/>
+      <c r="I151" s="26"/>
+      <c r="J151" s="22"/>
       <c r="L151" s="11" t="s">
         <v>5</v>
       </c>
@@ -6032,14 +6039,14 @@
       </c>
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C152" s="17"/>
-      <c r="D152" s="17"/>
-      <c r="E152" s="23"/>
-      <c r="F152" s="18"/>
-      <c r="G152" s="18"/>
-      <c r="H152" s="18"/>
-      <c r="I152" s="22"/>
-      <c r="J152" s="23"/>
+      <c r="C152" s="21"/>
+      <c r="D152" s="21"/>
+      <c r="E152" s="22"/>
+      <c r="F152" s="25"/>
+      <c r="G152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="26"/>
+      <c r="J152" s="22"/>
       <c r="L152" s="12" t="s">
         <v>15</v>
       </c>
@@ -6065,14 +6072,14 @@
       </c>
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C153" s="17"/>
-      <c r="D153" s="17"/>
-      <c r="E153" s="23"/>
-      <c r="F153" s="18"/>
-      <c r="G153" s="18"/>
-      <c r="H153" s="18"/>
-      <c r="I153" s="22"/>
-      <c r="J153" s="23"/>
+      <c r="C153" s="21"/>
+      <c r="D153" s="21"/>
+      <c r="E153" s="22"/>
+      <c r="F153" s="25"/>
+      <c r="G153" s="25"/>
+      <c r="H153" s="25"/>
+      <c r="I153" s="26"/>
+      <c r="J153" s="22"/>
       <c r="L153" s="14" t="s">
         <v>17</v>
       </c>
@@ -6095,14 +6102,14 @@
       <c r="U153" s="10"/>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C154" s="17"/>
-      <c r="D154" s="17"/>
-      <c r="E154" s="23"/>
-      <c r="F154" s="18"/>
-      <c r="G154" s="18"/>
-      <c r="H154" s="18"/>
-      <c r="I154" s="22"/>
-      <c r="J154" s="23"/>
+      <c r="C154" s="21"/>
+      <c r="D154" s="21"/>
+      <c r="E154" s="22"/>
+      <c r="F154" s="25"/>
+      <c r="G154" s="25"/>
+      <c r="H154" s="25"/>
+      <c r="I154" s="26"/>
+      <c r="J154" s="22"/>
       <c r="L154" s="15" t="s">
         <v>23</v>
       </c>
@@ -6131,26 +6138,26 @@
       <c r="B157" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C157" s="17" t="s">
+      <c r="C157" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D157" s="18" t="s">
+      <c r="D157" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E157" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F157" s="23"/>
-      <c r="G157" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H157" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I157" s="25" t="s">
+      <c r="E157" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F157" s="22"/>
+      <c r="G157" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H157" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I157" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J157" s="17"/>
+      <c r="J157" s="21"/>
       <c r="L157" s="9" t="s">
         <v>0</v>
       </c>
@@ -6176,14 +6183,14 @@
       <c r="B158">
         <v>15</v>
       </c>
-      <c r="C158" s="17"/>
-      <c r="D158" s="18"/>
-      <c r="E158" s="23"/>
-      <c r="F158" s="23"/>
-      <c r="G158" s="17"/>
-      <c r="H158" s="22"/>
-      <c r="I158" s="26"/>
-      <c r="J158" s="17"/>
+      <c r="C158" s="21"/>
+      <c r="D158" s="25"/>
+      <c r="E158" s="22"/>
+      <c r="F158" s="22"/>
+      <c r="G158" s="21"/>
+      <c r="H158" s="26"/>
+      <c r="I158" s="24"/>
+      <c r="J158" s="21"/>
       <c r="L158" s="11" t="s">
         <v>5</v>
       </c>
@@ -6219,14 +6226,14 @@
       </c>
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C159" s="17"/>
-      <c r="D159" s="18"/>
-      <c r="E159" s="23"/>
-      <c r="F159" s="23"/>
-      <c r="G159" s="17"/>
-      <c r="H159" s="22"/>
-      <c r="I159" s="26"/>
-      <c r="J159" s="17"/>
+      <c r="C159" s="21"/>
+      <c r="D159" s="25"/>
+      <c r="E159" s="22"/>
+      <c r="F159" s="22"/>
+      <c r="G159" s="21"/>
+      <c r="H159" s="26"/>
+      <c r="I159" s="24"/>
+      <c r="J159" s="21"/>
       <c r="L159" s="12" t="s">
         <v>15</v>
       </c>
@@ -6252,14 +6259,14 @@
       </c>
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C160" s="17"/>
-      <c r="D160" s="18"/>
-      <c r="E160" s="23"/>
-      <c r="F160" s="23"/>
-      <c r="G160" s="17"/>
-      <c r="H160" s="22"/>
-      <c r="I160" s="26"/>
-      <c r="J160" s="17"/>
+      <c r="C160" s="21"/>
+      <c r="D160" s="25"/>
+      <c r="E160" s="22"/>
+      <c r="F160" s="22"/>
+      <c r="G160" s="21"/>
+      <c r="H160" s="26"/>
+      <c r="I160" s="24"/>
+      <c r="J160" s="21"/>
       <c r="L160" s="14" t="s">
         <v>17</v>
       </c>
@@ -6283,14 +6290,14 @@
       <c r="U160" s="10"/>
     </row>
     <row r="161" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C161" s="17"/>
-      <c r="D161" s="18"/>
-      <c r="E161" s="23"/>
-      <c r="F161" s="23"/>
-      <c r="G161" s="17"/>
-      <c r="H161" s="22"/>
-      <c r="I161" s="26"/>
-      <c r="J161" s="17"/>
+      <c r="C161" s="21"/>
+      <c r="D161" s="25"/>
+      <c r="E161" s="22"/>
+      <c r="F161" s="22"/>
+      <c r="G161" s="21"/>
+      <c r="H161" s="26"/>
+      <c r="I161" s="24"/>
+      <c r="J161" s="21"/>
       <c r="L161" s="15" t="s">
         <v>23</v>
       </c>
@@ -6307,24 +6314,24 @@
       <c r="U161" s="10"/>
     </row>
     <row r="162" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C162" s="17" t="s">
+      <c r="C162" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D162" s="17"/>
-      <c r="E162" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F162" s="23"/>
-      <c r="G162" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H162" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I162" s="18" t="s">
+      <c r="D162" s="21"/>
+      <c r="E162" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F162" s="22"/>
+      <c r="G162" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H162" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I162" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J162" s="22" t="s">
+      <c r="J162" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L162" s="9" t="s">
@@ -6349,14 +6356,14 @@
       <c r="U162" s="10"/>
     </row>
     <row r="163" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C163" s="17"/>
-      <c r="D163" s="17"/>
-      <c r="E163" s="17"/>
-      <c r="F163" s="23"/>
-      <c r="G163" s="17"/>
-      <c r="H163" s="17"/>
-      <c r="I163" s="18"/>
-      <c r="J163" s="22"/>
+      <c r="C163" s="21"/>
+      <c r="D163" s="21"/>
+      <c r="E163" s="21"/>
+      <c r="F163" s="22"/>
+      <c r="G163" s="21"/>
+      <c r="H163" s="21"/>
+      <c r="I163" s="25"/>
+      <c r="J163" s="26"/>
       <c r="L163" s="11" t="s">
         <v>5</v>
       </c>
@@ -6392,14 +6399,14 @@
       </c>
     </row>
     <row r="164" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C164" s="17"/>
-      <c r="D164" s="17"/>
-      <c r="E164" s="17"/>
-      <c r="F164" s="23"/>
-      <c r="G164" s="17"/>
-      <c r="H164" s="17"/>
-      <c r="I164" s="18"/>
-      <c r="J164" s="22"/>
+      <c r="C164" s="21"/>
+      <c r="D164" s="21"/>
+      <c r="E164" s="21"/>
+      <c r="F164" s="22"/>
+      <c r="G164" s="21"/>
+      <c r="H164" s="21"/>
+      <c r="I164" s="25"/>
+      <c r="J164" s="26"/>
       <c r="L164" s="12" t="s">
         <v>15</v>
       </c>
@@ -6425,14 +6432,14 @@
       </c>
     </row>
     <row r="165" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C165" s="17"/>
-      <c r="D165" s="17"/>
-      <c r="E165" s="17"/>
-      <c r="F165" s="23"/>
-      <c r="G165" s="17"/>
-      <c r="H165" s="17"/>
-      <c r="I165" s="18"/>
-      <c r="J165" s="22"/>
+      <c r="C165" s="21"/>
+      <c r="D165" s="21"/>
+      <c r="E165" s="21"/>
+      <c r="F165" s="22"/>
+      <c r="G165" s="21"/>
+      <c r="H165" s="21"/>
+      <c r="I165" s="25"/>
+      <c r="J165" s="26"/>
       <c r="L165" s="14" t="s">
         <v>17</v>
       </c>
@@ -6455,14 +6462,14 @@
       <c r="U165" s="10"/>
     </row>
     <row r="166" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C166" s="17"/>
-      <c r="D166" s="17"/>
-      <c r="E166" s="17"/>
-      <c r="F166" s="23"/>
-      <c r="G166" s="17"/>
-      <c r="H166" s="17"/>
-      <c r="I166" s="18"/>
-      <c r="J166" s="22"/>
+      <c r="C166" s="21"/>
+      <c r="D166" s="21"/>
+      <c r="E166" s="21"/>
+      <c r="F166" s="22"/>
+      <c r="G166" s="21"/>
+      <c r="H166" s="21"/>
+      <c r="I166" s="25"/>
+      <c r="J166" s="26"/>
       <c r="L166" s="15" t="s">
         <v>23</v>
       </c>
@@ -6482,26 +6489,26 @@
       <c r="B167" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C167" s="17" t="s">
+      <c r="C167" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D167" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E167" s="18" t="s">
+      <c r="D167" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E167" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F167" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G167" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H167" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I167" s="17"/>
-      <c r="J167" s="27" t="s">
+      <c r="F167" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G167" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H167" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I167" s="21"/>
+      <c r="J167" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L167" s="9" t="s">
@@ -6529,14 +6536,14 @@
       <c r="B168">
         <v>16</v>
       </c>
-      <c r="C168" s="17"/>
-      <c r="D168" s="23"/>
-      <c r="E168" s="18"/>
-      <c r="F168" s="22"/>
-      <c r="G168" s="17"/>
-      <c r="H168" s="17"/>
-      <c r="I168" s="17"/>
-      <c r="J168" s="27"/>
+      <c r="C168" s="21"/>
+      <c r="D168" s="22"/>
+      <c r="E168" s="25"/>
+      <c r="F168" s="26"/>
+      <c r="G168" s="21"/>
+      <c r="H168" s="21"/>
+      <c r="I168" s="21"/>
+      <c r="J168" s="20"/>
       <c r="L168" s="11" t="s">
         <v>5</v>
       </c>
@@ -6575,14 +6582,14 @@
       <c r="B169" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C169" s="17"/>
-      <c r="D169" s="23"/>
-      <c r="E169" s="18"/>
-      <c r="F169" s="22"/>
-      <c r="G169" s="17"/>
-      <c r="H169" s="17"/>
-      <c r="I169" s="17"/>
-      <c r="J169" s="27"/>
+      <c r="C169" s="21"/>
+      <c r="D169" s="22"/>
+      <c r="E169" s="25"/>
+      <c r="F169" s="26"/>
+      <c r="G169" s="21"/>
+      <c r="H169" s="21"/>
+      <c r="I169" s="21"/>
+      <c r="J169" s="20"/>
       <c r="L169" s="12" t="s">
         <v>15</v>
       </c>
@@ -6611,14 +6618,14 @@
       <c r="B170">
         <v>6</v>
       </c>
-      <c r="C170" s="17"/>
-      <c r="D170" s="23"/>
-      <c r="E170" s="18"/>
-      <c r="F170" s="22"/>
-      <c r="G170" s="17"/>
-      <c r="H170" s="17"/>
-      <c r="I170" s="17"/>
-      <c r="J170" s="27"/>
+      <c r="C170" s="21"/>
+      <c r="D170" s="22"/>
+      <c r="E170" s="25"/>
+      <c r="F170" s="26"/>
+      <c r="G170" s="21"/>
+      <c r="H170" s="21"/>
+      <c r="I170" s="21"/>
+      <c r="J170" s="20"/>
       <c r="L170" s="14" t="s">
         <v>17</v>
       </c>
@@ -6643,14 +6650,14 @@
       <c r="U170" s="10"/>
     </row>
     <row r="171" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C171" s="17"/>
-      <c r="D171" s="23"/>
-      <c r="E171" s="18"/>
-      <c r="F171" s="22"/>
-      <c r="G171" s="17"/>
-      <c r="H171" s="17"/>
-      <c r="I171" s="17"/>
-      <c r="J171" s="27"/>
+      <c r="C171" s="21"/>
+      <c r="D171" s="22"/>
+      <c r="E171" s="25"/>
+      <c r="F171" s="26"/>
+      <c r="G171" s="21"/>
+      <c r="H171" s="21"/>
+      <c r="I171" s="21"/>
+      <c r="J171" s="20"/>
       <c r="L171" s="15" t="s">
         <v>23</v>
       </c>
@@ -6667,26 +6674,26 @@
       <c r="U171" s="10"/>
     </row>
     <row r="172" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C172" s="17" t="s">
+      <c r="C172" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D172" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E172" s="23"/>
-      <c r="F172" s="18" t="s">
+      <c r="D172" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E172" s="22"/>
+      <c r="F172" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G172" s="18" t="s">
+      <c r="G172" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H172" s="18" t="s">
+      <c r="H172" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I172" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J172" s="17"/>
+      <c r="I172" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J172" s="21"/>
       <c r="L172" s="9" t="s">
         <v>0</v>
       </c>
@@ -6709,14 +6716,14 @@
       <c r="U172" s="10"/>
     </row>
     <row r="173" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C173" s="17"/>
-      <c r="D173" s="17"/>
-      <c r="E173" s="23"/>
-      <c r="F173" s="18"/>
-      <c r="G173" s="18"/>
-      <c r="H173" s="18"/>
-      <c r="I173" s="22"/>
-      <c r="J173" s="17"/>
+      <c r="C173" s="21"/>
+      <c r="D173" s="21"/>
+      <c r="E173" s="22"/>
+      <c r="F173" s="25"/>
+      <c r="G173" s="25"/>
+      <c r="H173" s="25"/>
+      <c r="I173" s="26"/>
+      <c r="J173" s="21"/>
       <c r="L173" s="11" t="s">
         <v>5</v>
       </c>
@@ -6752,14 +6759,14 @@
       </c>
     </row>
     <row r="174" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C174" s="17"/>
-      <c r="D174" s="17"/>
-      <c r="E174" s="23"/>
-      <c r="F174" s="18"/>
-      <c r="G174" s="18"/>
-      <c r="H174" s="18"/>
-      <c r="I174" s="22"/>
-      <c r="J174" s="17"/>
+      <c r="C174" s="21"/>
+      <c r="D174" s="21"/>
+      <c r="E174" s="22"/>
+      <c r="F174" s="25"/>
+      <c r="G174" s="25"/>
+      <c r="H174" s="25"/>
+      <c r="I174" s="26"/>
+      <c r="J174" s="21"/>
       <c r="L174" s="12" t="s">
         <v>15</v>
       </c>
@@ -6785,14 +6792,14 @@
       </c>
     </row>
     <row r="175" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C175" s="17"/>
-      <c r="D175" s="17"/>
-      <c r="E175" s="23"/>
-      <c r="F175" s="18"/>
-      <c r="G175" s="18"/>
-      <c r="H175" s="18"/>
-      <c r="I175" s="22"/>
-      <c r="J175" s="17"/>
+      <c r="C175" s="21"/>
+      <c r="D175" s="21"/>
+      <c r="E175" s="22"/>
+      <c r="F175" s="25"/>
+      <c r="G175" s="25"/>
+      <c r="H175" s="25"/>
+      <c r="I175" s="26"/>
+      <c r="J175" s="21"/>
       <c r="L175" s="14" t="s">
         <v>17</v>
       </c>
@@ -6815,14 +6822,14 @@
       <c r="U175" s="10"/>
     </row>
     <row r="176" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C176" s="17"/>
-      <c r="D176" s="17"/>
-      <c r="E176" s="23"/>
-      <c r="F176" s="18"/>
-      <c r="G176" s="18"/>
-      <c r="H176" s="18"/>
-      <c r="I176" s="22"/>
-      <c r="J176" s="17"/>
+      <c r="C176" s="21"/>
+      <c r="D176" s="21"/>
+      <c r="E176" s="22"/>
+      <c r="F176" s="25"/>
+      <c r="G176" s="25"/>
+      <c r="H176" s="25"/>
+      <c r="I176" s="26"/>
+      <c r="J176" s="21"/>
       <c r="L176" s="15" t="s">
         <v>23</v>
       </c>
@@ -6845,26 +6852,26 @@
       <c r="B178" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C178" s="17" t="s">
+      <c r="C178" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D178" s="18" t="s">
+      <c r="D178" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E178" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F178" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G178" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H178" s="17"/>
-      <c r="I178" s="25" t="s">
+      <c r="E178" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F178" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G178" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H178" s="21"/>
+      <c r="I178" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J178" s="17"/>
+      <c r="J178" s="21"/>
       <c r="L178" s="9" t="s">
         <v>0</v>
       </c>
@@ -6890,14 +6897,14 @@
       <c r="B179">
         <v>17</v>
       </c>
-      <c r="C179" s="17"/>
-      <c r="D179" s="18"/>
-      <c r="E179" s="23"/>
-      <c r="F179" s="17"/>
-      <c r="G179" s="22"/>
-      <c r="H179" s="17"/>
-      <c r="I179" s="26"/>
-      <c r="J179" s="17"/>
+      <c r="C179" s="21"/>
+      <c r="D179" s="25"/>
+      <c r="E179" s="22"/>
+      <c r="F179" s="21"/>
+      <c r="G179" s="26"/>
+      <c r="H179" s="21"/>
+      <c r="I179" s="24"/>
+      <c r="J179" s="21"/>
       <c r="L179" s="11" t="s">
         <v>5</v>
       </c>
@@ -6933,14 +6940,14 @@
       </c>
     </row>
     <row r="180" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C180" s="17"/>
-      <c r="D180" s="18"/>
-      <c r="E180" s="23"/>
-      <c r="F180" s="17"/>
-      <c r="G180" s="22"/>
-      <c r="H180" s="17"/>
-      <c r="I180" s="26"/>
-      <c r="J180" s="17"/>
+      <c r="C180" s="21"/>
+      <c r="D180" s="25"/>
+      <c r="E180" s="22"/>
+      <c r="F180" s="21"/>
+      <c r="G180" s="26"/>
+      <c r="H180" s="21"/>
+      <c r="I180" s="24"/>
+      <c r="J180" s="21"/>
       <c r="L180" s="12" t="s">
         <v>15</v>
       </c>
@@ -6966,14 +6973,14 @@
       </c>
     </row>
     <row r="181" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C181" s="17"/>
-      <c r="D181" s="18"/>
-      <c r="E181" s="23"/>
-      <c r="F181" s="17"/>
-      <c r="G181" s="22"/>
-      <c r="H181" s="17"/>
-      <c r="I181" s="26"/>
-      <c r="J181" s="17"/>
+      <c r="C181" s="21"/>
+      <c r="D181" s="25"/>
+      <c r="E181" s="22"/>
+      <c r="F181" s="21"/>
+      <c r="G181" s="26"/>
+      <c r="H181" s="21"/>
+      <c r="I181" s="24"/>
+      <c r="J181" s="21"/>
       <c r="L181" s="14" t="s">
         <v>17</v>
       </c>
@@ -6997,14 +7004,14 @@
       <c r="U181" s="10"/>
     </row>
     <row r="182" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C182" s="17"/>
-      <c r="D182" s="18"/>
-      <c r="E182" s="23"/>
-      <c r="F182" s="17"/>
-      <c r="G182" s="22"/>
-      <c r="H182" s="17"/>
-      <c r="I182" s="26"/>
-      <c r="J182" s="17"/>
+      <c r="C182" s="21"/>
+      <c r="D182" s="25"/>
+      <c r="E182" s="22"/>
+      <c r="F182" s="21"/>
+      <c r="G182" s="26"/>
+      <c r="H182" s="21"/>
+      <c r="I182" s="24"/>
+      <c r="J182" s="21"/>
       <c r="L182" s="15" t="s">
         <v>23</v>
       </c>
@@ -7021,24 +7028,24 @@
       <c r="U182" s="10"/>
     </row>
     <row r="183" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C183" s="17" t="s">
+      <c r="C183" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D183" s="17"/>
-      <c r="E183" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F183" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G183" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H183" s="17"/>
-      <c r="I183" s="18" t="s">
+      <c r="D183" s="21"/>
+      <c r="E183" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F183" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G183" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H183" s="21"/>
+      <c r="I183" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J183" s="22" t="s">
+      <c r="J183" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L183" s="9" t="s">
@@ -7063,14 +7070,14 @@
       <c r="U183" s="10"/>
     </row>
     <row r="184" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C184" s="17"/>
-      <c r="D184" s="17"/>
-      <c r="E184" s="17"/>
-      <c r="F184" s="17"/>
-      <c r="G184" s="17"/>
-      <c r="H184" s="17"/>
-      <c r="I184" s="18"/>
-      <c r="J184" s="22"/>
+      <c r="C184" s="21"/>
+      <c r="D184" s="21"/>
+      <c r="E184" s="21"/>
+      <c r="F184" s="21"/>
+      <c r="G184" s="21"/>
+      <c r="H184" s="21"/>
+      <c r="I184" s="25"/>
+      <c r="J184" s="26"/>
       <c r="L184" s="11" t="s">
         <v>5</v>
       </c>
@@ -7106,14 +7113,14 @@
       </c>
     </row>
     <row r="185" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C185" s="17"/>
-      <c r="D185" s="17"/>
-      <c r="E185" s="17"/>
-      <c r="F185" s="17"/>
-      <c r="G185" s="17"/>
-      <c r="H185" s="17"/>
-      <c r="I185" s="18"/>
-      <c r="J185" s="22"/>
+      <c r="C185" s="21"/>
+      <c r="D185" s="21"/>
+      <c r="E185" s="21"/>
+      <c r="F185" s="21"/>
+      <c r="G185" s="21"/>
+      <c r="H185" s="21"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="26"/>
       <c r="L185" s="12" t="s">
         <v>15</v>
       </c>
@@ -7139,14 +7146,14 @@
       </c>
     </row>
     <row r="186" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C186" s="17"/>
-      <c r="D186" s="17"/>
-      <c r="E186" s="17"/>
-      <c r="F186" s="17"/>
-      <c r="G186" s="17"/>
-      <c r="H186" s="17"/>
-      <c r="I186" s="18"/>
-      <c r="J186" s="22"/>
+      <c r="C186" s="21"/>
+      <c r="D186" s="21"/>
+      <c r="E186" s="21"/>
+      <c r="F186" s="21"/>
+      <c r="G186" s="21"/>
+      <c r="H186" s="21"/>
+      <c r="I186" s="25"/>
+      <c r="J186" s="26"/>
       <c r="L186" s="14" t="s">
         <v>17</v>
       </c>
@@ -7169,14 +7176,14 @@
       <c r="U186" s="10"/>
     </row>
     <row r="187" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C187" s="17"/>
-      <c r="D187" s="17"/>
-      <c r="E187" s="17"/>
-      <c r="F187" s="17"/>
-      <c r="G187" s="17"/>
-      <c r="H187" s="17"/>
-      <c r="I187" s="18"/>
-      <c r="J187" s="22"/>
+      <c r="C187" s="21"/>
+      <c r="D187" s="21"/>
+      <c r="E187" s="21"/>
+      <c r="F187" s="21"/>
+      <c r="G187" s="21"/>
+      <c r="H187" s="21"/>
+      <c r="I187" s="25"/>
+      <c r="J187" s="26"/>
       <c r="L187" s="15" t="s">
         <v>23</v>
       </c>
@@ -7196,26 +7203,26 @@
       <c r="B188" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C188" s="17" t="s">
+      <c r="C188" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D188" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E188" s="18" t="s">
+      <c r="D188" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E188" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F188" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G188" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H188" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I188" s="17"/>
-      <c r="J188" s="27" t="s">
+      <c r="F188" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G188" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H188" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I188" s="21"/>
+      <c r="J188" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L188" s="9" t="s">
@@ -7243,14 +7250,14 @@
       <c r="B189">
         <v>18</v>
       </c>
-      <c r="C189" s="17"/>
-      <c r="D189" s="23"/>
-      <c r="E189" s="18"/>
-      <c r="F189" s="17"/>
-      <c r="G189" s="17"/>
-      <c r="H189" s="22"/>
-      <c r="I189" s="17"/>
-      <c r="J189" s="27"/>
+      <c r="C189" s="21"/>
+      <c r="D189" s="22"/>
+      <c r="E189" s="25"/>
+      <c r="F189" s="21"/>
+      <c r="G189" s="21"/>
+      <c r="H189" s="26"/>
+      <c r="I189" s="21"/>
+      <c r="J189" s="20"/>
       <c r="L189" s="11" t="s">
         <v>5</v>
       </c>
@@ -7289,14 +7296,14 @@
       <c r="B190" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C190" s="17"/>
-      <c r="D190" s="23"/>
-      <c r="E190" s="18"/>
-      <c r="F190" s="17"/>
-      <c r="G190" s="17"/>
-      <c r="H190" s="22"/>
-      <c r="I190" s="17"/>
-      <c r="J190" s="27"/>
+      <c r="C190" s="21"/>
+      <c r="D190" s="22"/>
+      <c r="E190" s="25"/>
+      <c r="F190" s="21"/>
+      <c r="G190" s="21"/>
+      <c r="H190" s="26"/>
+      <c r="I190" s="21"/>
+      <c r="J190" s="20"/>
       <c r="L190" s="12" t="s">
         <v>15</v>
       </c>
@@ -7325,14 +7332,14 @@
       <c r="B191">
         <v>7</v>
       </c>
-      <c r="C191" s="17"/>
-      <c r="D191" s="23"/>
-      <c r="E191" s="18"/>
-      <c r="F191" s="17"/>
-      <c r="G191" s="17"/>
-      <c r="H191" s="22"/>
-      <c r="I191" s="17"/>
-      <c r="J191" s="27"/>
+      <c r="C191" s="21"/>
+      <c r="D191" s="22"/>
+      <c r="E191" s="25"/>
+      <c r="F191" s="21"/>
+      <c r="G191" s="21"/>
+      <c r="H191" s="26"/>
+      <c r="I191" s="21"/>
+      <c r="J191" s="20"/>
       <c r="L191" s="14" t="s">
         <v>17</v>
       </c>
@@ -7357,14 +7364,14 @@
       <c r="U191" s="10"/>
     </row>
     <row r="192" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C192" s="17"/>
-      <c r="D192" s="23"/>
-      <c r="E192" s="18"/>
-      <c r="F192" s="17"/>
-      <c r="G192" s="17"/>
-      <c r="H192" s="22"/>
-      <c r="I192" s="17"/>
-      <c r="J192" s="27"/>
+      <c r="C192" s="21"/>
+      <c r="D192" s="22"/>
+      <c r="E192" s="25"/>
+      <c r="F192" s="21"/>
+      <c r="G192" s="21"/>
+      <c r="H192" s="26"/>
+      <c r="I192" s="21"/>
+      <c r="J192" s="20"/>
       <c r="L192" s="15" t="s">
         <v>23</v>
       </c>
@@ -7381,26 +7388,26 @@
       <c r="U192" s="10"/>
     </row>
     <row r="193" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C193" s="17" t="s">
+      <c r="C193" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D193" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E193" s="23"/>
-      <c r="F193" s="18" t="s">
+      <c r="D193" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E193" s="22"/>
+      <c r="F193" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G193" s="18" t="s">
+      <c r="G193" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H193" s="18" t="s">
+      <c r="H193" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I193" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J193" s="17"/>
+      <c r="I193" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J193" s="21"/>
       <c r="L193" s="9" t="s">
         <v>0</v>
       </c>
@@ -7423,14 +7430,14 @@
       <c r="U193" s="10"/>
     </row>
     <row r="194" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C194" s="17"/>
-      <c r="D194" s="17"/>
-      <c r="E194" s="23"/>
-      <c r="F194" s="18"/>
-      <c r="G194" s="18"/>
-      <c r="H194" s="18"/>
-      <c r="I194" s="22"/>
-      <c r="J194" s="17"/>
+      <c r="C194" s="21"/>
+      <c r="D194" s="21"/>
+      <c r="E194" s="22"/>
+      <c r="F194" s="25"/>
+      <c r="G194" s="25"/>
+      <c r="H194" s="25"/>
+      <c r="I194" s="26"/>
+      <c r="J194" s="21"/>
       <c r="L194" s="11" t="s">
         <v>5</v>
       </c>
@@ -7466,14 +7473,14 @@
       </c>
     </row>
     <row r="195" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C195" s="17"/>
-      <c r="D195" s="17"/>
-      <c r="E195" s="23"/>
-      <c r="F195" s="18"/>
-      <c r="G195" s="18"/>
-      <c r="H195" s="18"/>
-      <c r="I195" s="22"/>
-      <c r="J195" s="17"/>
+      <c r="C195" s="21"/>
+      <c r="D195" s="21"/>
+      <c r="E195" s="22"/>
+      <c r="F195" s="25"/>
+      <c r="G195" s="25"/>
+      <c r="H195" s="25"/>
+      <c r="I195" s="26"/>
+      <c r="J195" s="21"/>
       <c r="L195" s="12" t="s">
         <v>15</v>
       </c>
@@ -7499,14 +7506,14 @@
       </c>
     </row>
     <row r="196" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C196" s="17"/>
-      <c r="D196" s="17"/>
-      <c r="E196" s="23"/>
-      <c r="F196" s="18"/>
-      <c r="G196" s="18"/>
-      <c r="H196" s="18"/>
-      <c r="I196" s="22"/>
-      <c r="J196" s="17"/>
+      <c r="C196" s="21"/>
+      <c r="D196" s="21"/>
+      <c r="E196" s="22"/>
+      <c r="F196" s="25"/>
+      <c r="G196" s="25"/>
+      <c r="H196" s="25"/>
+      <c r="I196" s="26"/>
+      <c r="J196" s="21"/>
       <c r="L196" s="14" t="s">
         <v>17</v>
       </c>
@@ -7529,14 +7536,14 @@
       <c r="U196" s="10"/>
     </row>
     <row r="197" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C197" s="17"/>
-      <c r="D197" s="17"/>
-      <c r="E197" s="23"/>
-      <c r="F197" s="18"/>
-      <c r="G197" s="18"/>
-      <c r="H197" s="18"/>
-      <c r="I197" s="22"/>
-      <c r="J197" s="17"/>
+      <c r="C197" s="21"/>
+      <c r="D197" s="21"/>
+      <c r="E197" s="22"/>
+      <c r="F197" s="25"/>
+      <c r="G197" s="25"/>
+      <c r="H197" s="25"/>
+      <c r="I197" s="26"/>
+      <c r="J197" s="21"/>
       <c r="L197" s="15" t="s">
         <v>23</v>
       </c>
@@ -7559,26 +7566,26 @@
       <c r="B199" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C199" s="17" t="s">
+      <c r="C199" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D199" s="18" t="s">
+      <c r="D199" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E199" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F199" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G199" s="17"/>
-      <c r="H199" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I199" s="25" t="s">
+      <c r="E199" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F199" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G199" s="21"/>
+      <c r="H199" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I199" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J199" s="17"/>
+      <c r="J199" s="21"/>
       <c r="L199" s="9" t="s">
         <v>0</v>
       </c>
@@ -7604,14 +7611,14 @@
       <c r="B200">
         <v>19</v>
       </c>
-      <c r="C200" s="17"/>
-      <c r="D200" s="18"/>
-      <c r="E200" s="23"/>
-      <c r="F200" s="22"/>
-      <c r="G200" s="17"/>
-      <c r="H200" s="17"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="17"/>
+      <c r="C200" s="21"/>
+      <c r="D200" s="25"/>
+      <c r="E200" s="22"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="21"/>
+      <c r="H200" s="21"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="21"/>
       <c r="L200" s="11" t="s">
         <v>5</v>
       </c>
@@ -7647,14 +7654,14 @@
       </c>
     </row>
     <row r="201" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C201" s="17"/>
-      <c r="D201" s="18"/>
-      <c r="E201" s="23"/>
-      <c r="F201" s="22"/>
-      <c r="G201" s="17"/>
-      <c r="H201" s="17"/>
-      <c r="I201" s="26"/>
-      <c r="J201" s="17"/>
+      <c r="C201" s="21"/>
+      <c r="D201" s="25"/>
+      <c r="E201" s="22"/>
+      <c r="F201" s="26"/>
+      <c r="G201" s="21"/>
+      <c r="H201" s="21"/>
+      <c r="I201" s="24"/>
+      <c r="J201" s="21"/>
       <c r="L201" s="12" t="s">
         <v>15</v>
       </c>
@@ -7680,14 +7687,14 @@
       </c>
     </row>
     <row r="202" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C202" s="17"/>
-      <c r="D202" s="18"/>
-      <c r="E202" s="23"/>
-      <c r="F202" s="22"/>
-      <c r="G202" s="17"/>
-      <c r="H202" s="17"/>
-      <c r="I202" s="26"/>
-      <c r="J202" s="17"/>
+      <c r="C202" s="21"/>
+      <c r="D202" s="25"/>
+      <c r="E202" s="22"/>
+      <c r="F202" s="26"/>
+      <c r="G202" s="21"/>
+      <c r="H202" s="21"/>
+      <c r="I202" s="24"/>
+      <c r="J202" s="21"/>
       <c r="L202" s="14" t="s">
         <v>17</v>
       </c>
@@ -7711,14 +7718,14 @@
       <c r="U202" s="10"/>
     </row>
     <row r="203" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C203" s="17"/>
-      <c r="D203" s="18"/>
-      <c r="E203" s="23"/>
-      <c r="F203" s="22"/>
-      <c r="G203" s="17"/>
-      <c r="H203" s="17"/>
-      <c r="I203" s="26"/>
-      <c r="J203" s="17"/>
+      <c r="C203" s="21"/>
+      <c r="D203" s="25"/>
+      <c r="E203" s="22"/>
+      <c r="F203" s="26"/>
+      <c r="G203" s="21"/>
+      <c r="H203" s="21"/>
+      <c r="I203" s="24"/>
+      <c r="J203" s="21"/>
       <c r="L203" s="15" t="s">
         <v>23</v>
       </c>
@@ -7735,24 +7742,24 @@
       <c r="U203" s="10"/>
     </row>
     <row r="204" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C204" s="17" t="s">
+      <c r="C204" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D204" s="17"/>
-      <c r="E204" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F204" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G204" s="17"/>
-      <c r="H204" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I204" s="18" t="s">
+      <c r="D204" s="21"/>
+      <c r="E204" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F204" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G204" s="21"/>
+      <c r="H204" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I204" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J204" s="22" t="s">
+      <c r="J204" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L204" s="9" t="s">
@@ -7777,14 +7784,14 @@
       <c r="U204" s="10"/>
     </row>
     <row r="205" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C205" s="17"/>
-      <c r="D205" s="17"/>
-      <c r="E205" s="17"/>
-      <c r="F205" s="17"/>
-      <c r="G205" s="17"/>
-      <c r="H205" s="17"/>
-      <c r="I205" s="18"/>
-      <c r="J205" s="22"/>
+      <c r="C205" s="21"/>
+      <c r="D205" s="21"/>
+      <c r="E205" s="21"/>
+      <c r="F205" s="21"/>
+      <c r="G205" s="21"/>
+      <c r="H205" s="21"/>
+      <c r="I205" s="25"/>
+      <c r="J205" s="26"/>
       <c r="L205" s="11" t="s">
         <v>5</v>
       </c>
@@ -7820,14 +7827,14 @@
       </c>
     </row>
     <row r="206" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C206" s="17"/>
-      <c r="D206" s="17"/>
-      <c r="E206" s="17"/>
-      <c r="F206" s="17"/>
-      <c r="G206" s="17"/>
-      <c r="H206" s="17"/>
-      <c r="I206" s="18"/>
-      <c r="J206" s="22"/>
+      <c r="C206" s="21"/>
+      <c r="D206" s="21"/>
+      <c r="E206" s="21"/>
+      <c r="F206" s="21"/>
+      <c r="G206" s="21"/>
+      <c r="H206" s="21"/>
+      <c r="I206" s="25"/>
+      <c r="J206" s="26"/>
       <c r="L206" s="12" t="s">
         <v>15</v>
       </c>
@@ -7853,14 +7860,14 @@
       </c>
     </row>
     <row r="207" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C207" s="17"/>
-      <c r="D207" s="17"/>
-      <c r="E207" s="17"/>
-      <c r="F207" s="17"/>
-      <c r="G207" s="17"/>
-      <c r="H207" s="17"/>
-      <c r="I207" s="18"/>
-      <c r="J207" s="22"/>
+      <c r="C207" s="21"/>
+      <c r="D207" s="21"/>
+      <c r="E207" s="21"/>
+      <c r="F207" s="21"/>
+      <c r="G207" s="21"/>
+      <c r="H207" s="21"/>
+      <c r="I207" s="25"/>
+      <c r="J207" s="26"/>
       <c r="L207" s="14" t="s">
         <v>17</v>
       </c>
@@ -7883,14 +7890,14 @@
       <c r="U207" s="10"/>
     </row>
     <row r="208" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C208" s="17"/>
-      <c r="D208" s="17"/>
-      <c r="E208" s="17"/>
-      <c r="F208" s="17"/>
-      <c r="G208" s="17"/>
-      <c r="H208" s="17"/>
-      <c r="I208" s="18"/>
-      <c r="J208" s="22"/>
+      <c r="C208" s="21"/>
+      <c r="D208" s="21"/>
+      <c r="E208" s="21"/>
+      <c r="F208" s="21"/>
+      <c r="G208" s="21"/>
+      <c r="H208" s="21"/>
+      <c r="I208" s="25"/>
+      <c r="J208" s="26"/>
       <c r="L208" s="15" t="s">
         <v>23</v>
       </c>
@@ -7910,26 +7917,26 @@
       <c r="B209" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C209" s="17" t="s">
+      <c r="C209" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D209" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E209" s="18" t="s">
+      <c r="D209" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E209" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F209" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G209" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H209" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I209" s="17"/>
-      <c r="J209" s="27" t="s">
+      <c r="F209" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G209" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H209" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I209" s="21"/>
+      <c r="J209" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L209" s="9" t="s">
@@ -7957,14 +7964,14 @@
       <c r="B210">
         <v>20</v>
       </c>
-      <c r="C210" s="17"/>
-      <c r="D210" s="23"/>
-      <c r="E210" s="18"/>
-      <c r="F210" s="17"/>
-      <c r="G210" s="22"/>
-      <c r="H210" s="17"/>
-      <c r="I210" s="17"/>
-      <c r="J210" s="27"/>
+      <c r="C210" s="21"/>
+      <c r="D210" s="22"/>
+      <c r="E210" s="25"/>
+      <c r="F210" s="21"/>
+      <c r="G210" s="26"/>
+      <c r="H210" s="21"/>
+      <c r="I210" s="21"/>
+      <c r="J210" s="20"/>
       <c r="L210" s="11" t="s">
         <v>5</v>
       </c>
@@ -8003,14 +8010,14 @@
       <c r="B211" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C211" s="17"/>
-      <c r="D211" s="23"/>
-      <c r="E211" s="18"/>
-      <c r="F211" s="17"/>
-      <c r="G211" s="22"/>
-      <c r="H211" s="17"/>
-      <c r="I211" s="17"/>
-      <c r="J211" s="27"/>
+      <c r="C211" s="21"/>
+      <c r="D211" s="22"/>
+      <c r="E211" s="25"/>
+      <c r="F211" s="21"/>
+      <c r="G211" s="26"/>
+      <c r="H211" s="21"/>
+      <c r="I211" s="21"/>
+      <c r="J211" s="20"/>
       <c r="L211" s="12" t="s">
         <v>15</v>
       </c>
@@ -8039,14 +8046,14 @@
       <c r="B212">
         <v>8</v>
       </c>
-      <c r="C212" s="17"/>
-      <c r="D212" s="23"/>
-      <c r="E212" s="18"/>
-      <c r="F212" s="17"/>
-      <c r="G212" s="22"/>
-      <c r="H212" s="17"/>
-      <c r="I212" s="17"/>
-      <c r="J212" s="27"/>
+      <c r="C212" s="21"/>
+      <c r="D212" s="22"/>
+      <c r="E212" s="25"/>
+      <c r="F212" s="21"/>
+      <c r="G212" s="26"/>
+      <c r="H212" s="21"/>
+      <c r="I212" s="21"/>
+      <c r="J212" s="20"/>
       <c r="L212" s="14" t="s">
         <v>17</v>
       </c>
@@ -8071,14 +8078,14 @@
       <c r="U212" s="10"/>
     </row>
     <row r="213" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C213" s="17"/>
-      <c r="D213" s="23"/>
-      <c r="E213" s="18"/>
-      <c r="F213" s="17"/>
-      <c r="G213" s="22"/>
-      <c r="H213" s="17"/>
-      <c r="I213" s="17"/>
-      <c r="J213" s="27"/>
+      <c r="C213" s="21"/>
+      <c r="D213" s="22"/>
+      <c r="E213" s="25"/>
+      <c r="F213" s="21"/>
+      <c r="G213" s="26"/>
+      <c r="H213" s="21"/>
+      <c r="I213" s="21"/>
+      <c r="J213" s="20"/>
       <c r="L213" s="15" t="s">
         <v>23</v>
       </c>
@@ -8095,26 +8102,26 @@
       <c r="U213" s="10"/>
     </row>
     <row r="214" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C214" s="17" t="s">
+      <c r="C214" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D214" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E214" s="23"/>
-      <c r="F214" s="18" t="s">
+      <c r="D214" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E214" s="22"/>
+      <c r="F214" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G214" s="18" t="s">
+      <c r="G214" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H214" s="18" t="s">
+      <c r="H214" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I214" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J214" s="23"/>
+      <c r="I214" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J214" s="22"/>
       <c r="L214" s="9" t="s">
         <v>0</v>
       </c>
@@ -8137,14 +8144,14 @@
       <c r="U214" s="10"/>
     </row>
     <row r="215" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C215" s="17"/>
-      <c r="D215" s="17"/>
-      <c r="E215" s="23"/>
-      <c r="F215" s="18"/>
-      <c r="G215" s="18"/>
-      <c r="H215" s="18"/>
-      <c r="I215" s="22"/>
-      <c r="J215" s="23"/>
+      <c r="C215" s="21"/>
+      <c r="D215" s="21"/>
+      <c r="E215" s="22"/>
+      <c r="F215" s="25"/>
+      <c r="G215" s="25"/>
+      <c r="H215" s="25"/>
+      <c r="I215" s="26"/>
+      <c r="J215" s="22"/>
       <c r="L215" s="11" t="s">
         <v>5</v>
       </c>
@@ -8180,14 +8187,14 @@
       </c>
     </row>
     <row r="216" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C216" s="17"/>
-      <c r="D216" s="17"/>
-      <c r="E216" s="23"/>
-      <c r="F216" s="18"/>
-      <c r="G216" s="18"/>
-      <c r="H216" s="18"/>
-      <c r="I216" s="22"/>
-      <c r="J216" s="23"/>
+      <c r="C216" s="21"/>
+      <c r="D216" s="21"/>
+      <c r="E216" s="22"/>
+      <c r="F216" s="25"/>
+      <c r="G216" s="25"/>
+      <c r="H216" s="25"/>
+      <c r="I216" s="26"/>
+      <c r="J216" s="22"/>
       <c r="L216" s="12" t="s">
         <v>15</v>
       </c>
@@ -8213,14 +8220,14 @@
       </c>
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C217" s="17"/>
-      <c r="D217" s="17"/>
-      <c r="E217" s="23"/>
-      <c r="F217" s="18"/>
-      <c r="G217" s="18"/>
-      <c r="H217" s="18"/>
-      <c r="I217" s="22"/>
-      <c r="J217" s="23"/>
+      <c r="C217" s="21"/>
+      <c r="D217" s="21"/>
+      <c r="E217" s="22"/>
+      <c r="F217" s="25"/>
+      <c r="G217" s="25"/>
+      <c r="H217" s="25"/>
+      <c r="I217" s="26"/>
+      <c r="J217" s="22"/>
       <c r="L217" s="14" t="s">
         <v>17</v>
       </c>
@@ -8243,14 +8250,14 @@
       <c r="U217" s="10"/>
     </row>
     <row r="218" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C218" s="17"/>
-      <c r="D218" s="17"/>
-      <c r="E218" s="23"/>
-      <c r="F218" s="18"/>
-      <c r="G218" s="18"/>
-      <c r="H218" s="18"/>
-      <c r="I218" s="22"/>
-      <c r="J218" s="23"/>
+      <c r="C218" s="21"/>
+      <c r="D218" s="21"/>
+      <c r="E218" s="22"/>
+      <c r="F218" s="25"/>
+      <c r="G218" s="25"/>
+      <c r="H218" s="25"/>
+      <c r="I218" s="26"/>
+      <c r="J218" s="22"/>
       <c r="L218" s="15" t="s">
         <v>23</v>
       </c>
@@ -8279,26 +8286,26 @@
       <c r="B221" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C221" s="17" t="s">
+      <c r="C221" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D221" s="18" t="s">
+      <c r="D221" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E221" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F221" s="23"/>
-      <c r="G221" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H221" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I221" s="25" t="s">
+      <c r="E221" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F221" s="22"/>
+      <c r="G221" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H221" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I221" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J221" s="17"/>
+      <c r="J221" s="21"/>
       <c r="L221" s="9" t="s">
         <v>0</v>
       </c>
@@ -8324,14 +8331,14 @@
       <c r="B222">
         <v>21</v>
       </c>
-      <c r="C222" s="17"/>
-      <c r="D222" s="18"/>
-      <c r="E222" s="23"/>
-      <c r="F222" s="23"/>
-      <c r="G222" s="17"/>
-      <c r="H222" s="22"/>
-      <c r="I222" s="26"/>
-      <c r="J222" s="17"/>
+      <c r="C222" s="21"/>
+      <c r="D222" s="25"/>
+      <c r="E222" s="22"/>
+      <c r="F222" s="22"/>
+      <c r="G222" s="21"/>
+      <c r="H222" s="26"/>
+      <c r="I222" s="24"/>
+      <c r="J222" s="21"/>
       <c r="L222" s="11" t="s">
         <v>5</v>
       </c>
@@ -8367,14 +8374,14 @@
       </c>
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C223" s="17"/>
-      <c r="D223" s="18"/>
-      <c r="E223" s="23"/>
-      <c r="F223" s="23"/>
-      <c r="G223" s="17"/>
-      <c r="H223" s="22"/>
-      <c r="I223" s="26"/>
-      <c r="J223" s="17"/>
+      <c r="C223" s="21"/>
+      <c r="D223" s="25"/>
+      <c r="E223" s="22"/>
+      <c r="F223" s="22"/>
+      <c r="G223" s="21"/>
+      <c r="H223" s="26"/>
+      <c r="I223" s="24"/>
+      <c r="J223" s="21"/>
       <c r="L223" s="12" t="s">
         <v>15</v>
       </c>
@@ -8400,14 +8407,14 @@
       </c>
     </row>
     <row r="224" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C224" s="17"/>
-      <c r="D224" s="18"/>
-      <c r="E224" s="23"/>
-      <c r="F224" s="23"/>
-      <c r="G224" s="17"/>
-      <c r="H224" s="22"/>
-      <c r="I224" s="26"/>
-      <c r="J224" s="17"/>
+      <c r="C224" s="21"/>
+      <c r="D224" s="25"/>
+      <c r="E224" s="22"/>
+      <c r="F224" s="22"/>
+      <c r="G224" s="21"/>
+      <c r="H224" s="26"/>
+      <c r="I224" s="24"/>
+      <c r="J224" s="21"/>
       <c r="L224" s="14" t="s">
         <v>17</v>
       </c>
@@ -8431,14 +8438,14 @@
       <c r="U224" s="10"/>
     </row>
     <row r="225" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C225" s="17"/>
-      <c r="D225" s="18"/>
-      <c r="E225" s="23"/>
-      <c r="F225" s="23"/>
-      <c r="G225" s="17"/>
-      <c r="H225" s="22"/>
-      <c r="I225" s="26"/>
-      <c r="J225" s="17"/>
+      <c r="C225" s="21"/>
+      <c r="D225" s="25"/>
+      <c r="E225" s="22"/>
+      <c r="F225" s="22"/>
+      <c r="G225" s="21"/>
+      <c r="H225" s="26"/>
+      <c r="I225" s="24"/>
+      <c r="J225" s="21"/>
       <c r="L225" s="15" t="s">
         <v>23</v>
       </c>
@@ -8455,24 +8462,24 @@
       <c r="U225" s="10"/>
     </row>
     <row r="226" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C226" s="17" t="s">
+      <c r="C226" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D226" s="17"/>
-      <c r="E226" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F226" s="23"/>
-      <c r="G226" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H226" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I226" s="18" t="s">
+      <c r="D226" s="21"/>
+      <c r="E226" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F226" s="22"/>
+      <c r="G226" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H226" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I226" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J226" s="22" t="s">
+      <c r="J226" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L226" s="9" t="s">
@@ -8497,14 +8504,14 @@
       <c r="U226" s="10"/>
     </row>
     <row r="227" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C227" s="17"/>
-      <c r="D227" s="17"/>
-      <c r="E227" s="17"/>
-      <c r="F227" s="23"/>
-      <c r="G227" s="17"/>
-      <c r="H227" s="17"/>
-      <c r="I227" s="18"/>
-      <c r="J227" s="22"/>
+      <c r="C227" s="21"/>
+      <c r="D227" s="21"/>
+      <c r="E227" s="21"/>
+      <c r="F227" s="22"/>
+      <c r="G227" s="21"/>
+      <c r="H227" s="21"/>
+      <c r="I227" s="25"/>
+      <c r="J227" s="26"/>
       <c r="L227" s="11" t="s">
         <v>5</v>
       </c>
@@ -8540,14 +8547,14 @@
       </c>
     </row>
     <row r="228" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C228" s="17"/>
-      <c r="D228" s="17"/>
-      <c r="E228" s="17"/>
-      <c r="F228" s="23"/>
-      <c r="G228" s="17"/>
-      <c r="H228" s="17"/>
-      <c r="I228" s="18"/>
-      <c r="J228" s="22"/>
+      <c r="C228" s="21"/>
+      <c r="D228" s="21"/>
+      <c r="E228" s="21"/>
+      <c r="F228" s="22"/>
+      <c r="G228" s="21"/>
+      <c r="H228" s="21"/>
+      <c r="I228" s="25"/>
+      <c r="J228" s="26"/>
       <c r="L228" s="12" t="s">
         <v>15</v>
       </c>
@@ -8573,14 +8580,14 @@
       </c>
     </row>
     <row r="229" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C229" s="17"/>
-      <c r="D229" s="17"/>
-      <c r="E229" s="17"/>
-      <c r="F229" s="23"/>
-      <c r="G229" s="17"/>
-      <c r="H229" s="17"/>
-      <c r="I229" s="18"/>
-      <c r="J229" s="22"/>
+      <c r="C229" s="21"/>
+      <c r="D229" s="21"/>
+      <c r="E229" s="21"/>
+      <c r="F229" s="22"/>
+      <c r="G229" s="21"/>
+      <c r="H229" s="21"/>
+      <c r="I229" s="25"/>
+      <c r="J229" s="26"/>
       <c r="L229" s="14" t="s">
         <v>17</v>
       </c>
@@ -8603,14 +8610,14 @@
       <c r="U229" s="10"/>
     </row>
     <row r="230" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C230" s="17"/>
-      <c r="D230" s="17"/>
-      <c r="E230" s="17"/>
-      <c r="F230" s="23"/>
-      <c r="G230" s="17"/>
-      <c r="H230" s="17"/>
-      <c r="I230" s="18"/>
-      <c r="J230" s="22"/>
+      <c r="C230" s="21"/>
+      <c r="D230" s="21"/>
+      <c r="E230" s="21"/>
+      <c r="F230" s="22"/>
+      <c r="G230" s="21"/>
+      <c r="H230" s="21"/>
+      <c r="I230" s="25"/>
+      <c r="J230" s="26"/>
       <c r="L230" s="15" t="s">
         <v>23</v>
       </c>
@@ -8630,26 +8637,26 @@
       <c r="B231" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C231" s="17" t="s">
+      <c r="C231" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D231" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E231" s="18" t="s">
+      <c r="D231" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E231" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F231" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G231" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H231" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I231" s="17"/>
-      <c r="J231" s="27" t="s">
+      <c r="F231" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G231" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H231" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I231" s="21"/>
+      <c r="J231" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L231" s="9" t="s">
@@ -8677,14 +8684,14 @@
       <c r="B232">
         <v>22</v>
       </c>
-      <c r="C232" s="17"/>
-      <c r="D232" s="23"/>
-      <c r="E232" s="18"/>
-      <c r="F232" s="22"/>
-      <c r="G232" s="17"/>
-      <c r="H232" s="17"/>
-      <c r="I232" s="17"/>
-      <c r="J232" s="27"/>
+      <c r="C232" s="21"/>
+      <c r="D232" s="22"/>
+      <c r="E232" s="25"/>
+      <c r="F232" s="26"/>
+      <c r="G232" s="21"/>
+      <c r="H232" s="21"/>
+      <c r="I232" s="21"/>
+      <c r="J232" s="20"/>
       <c r="L232" s="11" t="s">
         <v>5</v>
       </c>
@@ -8723,14 +8730,14 @@
       <c r="B233" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C233" s="17"/>
-      <c r="D233" s="23"/>
-      <c r="E233" s="18"/>
-      <c r="F233" s="22"/>
-      <c r="G233" s="17"/>
-      <c r="H233" s="17"/>
-      <c r="I233" s="17"/>
-      <c r="J233" s="27"/>
+      <c r="C233" s="21"/>
+      <c r="D233" s="22"/>
+      <c r="E233" s="25"/>
+      <c r="F233" s="26"/>
+      <c r="G233" s="21"/>
+      <c r="H233" s="21"/>
+      <c r="I233" s="21"/>
+      <c r="J233" s="20"/>
       <c r="L233" s="12" t="s">
         <v>15</v>
       </c>
@@ -8759,14 +8766,14 @@
       <c r="B234">
         <v>9</v>
       </c>
-      <c r="C234" s="17"/>
-      <c r="D234" s="23"/>
-      <c r="E234" s="18"/>
-      <c r="F234" s="22"/>
-      <c r="G234" s="17"/>
-      <c r="H234" s="17"/>
-      <c r="I234" s="17"/>
-      <c r="J234" s="27"/>
+      <c r="C234" s="21"/>
+      <c r="D234" s="22"/>
+      <c r="E234" s="25"/>
+      <c r="F234" s="26"/>
+      <c r="G234" s="21"/>
+      <c r="H234" s="21"/>
+      <c r="I234" s="21"/>
+      <c r="J234" s="20"/>
       <c r="L234" s="14" t="s">
         <v>17</v>
       </c>
@@ -8791,14 +8798,14 @@
       <c r="U234" s="10"/>
     </row>
     <row r="235" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C235" s="17"/>
-      <c r="D235" s="23"/>
-      <c r="E235" s="18"/>
-      <c r="F235" s="22"/>
-      <c r="G235" s="17"/>
-      <c r="H235" s="17"/>
-      <c r="I235" s="17"/>
-      <c r="J235" s="27"/>
+      <c r="C235" s="21"/>
+      <c r="D235" s="22"/>
+      <c r="E235" s="25"/>
+      <c r="F235" s="26"/>
+      <c r="G235" s="21"/>
+      <c r="H235" s="21"/>
+      <c r="I235" s="21"/>
+      <c r="J235" s="20"/>
       <c r="L235" s="15" t="s">
         <v>23</v>
       </c>
@@ -8815,26 +8822,26 @@
       <c r="U235" s="10"/>
     </row>
     <row r="236" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C236" s="17" t="s">
+      <c r="C236" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D236" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E236" s="23"/>
-      <c r="F236" s="18" t="s">
+      <c r="D236" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E236" s="22"/>
+      <c r="F236" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G236" s="18" t="s">
+      <c r="G236" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H236" s="18" t="s">
+      <c r="H236" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I236" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J236" s="17"/>
+      <c r="I236" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J236" s="21"/>
       <c r="L236" s="9" t="s">
         <v>0</v>
       </c>
@@ -8857,14 +8864,14 @@
       <c r="U236" s="10"/>
     </row>
     <row r="237" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C237" s="17"/>
-      <c r="D237" s="17"/>
-      <c r="E237" s="23"/>
-      <c r="F237" s="18"/>
-      <c r="G237" s="18"/>
-      <c r="H237" s="18"/>
-      <c r="I237" s="22"/>
-      <c r="J237" s="17"/>
+      <c r="C237" s="21"/>
+      <c r="D237" s="21"/>
+      <c r="E237" s="22"/>
+      <c r="F237" s="25"/>
+      <c r="G237" s="25"/>
+      <c r="H237" s="25"/>
+      <c r="I237" s="26"/>
+      <c r="J237" s="21"/>
       <c r="L237" s="11" t="s">
         <v>5</v>
       </c>
@@ -8900,14 +8907,14 @@
       </c>
     </row>
     <row r="238" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C238" s="17"/>
-      <c r="D238" s="17"/>
-      <c r="E238" s="23"/>
-      <c r="F238" s="18"/>
-      <c r="G238" s="18"/>
-      <c r="H238" s="18"/>
-      <c r="I238" s="22"/>
-      <c r="J238" s="17"/>
+      <c r="C238" s="21"/>
+      <c r="D238" s="21"/>
+      <c r="E238" s="22"/>
+      <c r="F238" s="25"/>
+      <c r="G238" s="25"/>
+      <c r="H238" s="25"/>
+      <c r="I238" s="26"/>
+      <c r="J238" s="21"/>
       <c r="L238" s="12" t="s">
         <v>15</v>
       </c>
@@ -8933,14 +8940,14 @@
       </c>
     </row>
     <row r="239" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C239" s="17"/>
-      <c r="D239" s="17"/>
-      <c r="E239" s="23"/>
-      <c r="F239" s="18"/>
-      <c r="G239" s="18"/>
-      <c r="H239" s="18"/>
-      <c r="I239" s="22"/>
-      <c r="J239" s="17"/>
+      <c r="C239" s="21"/>
+      <c r="D239" s="21"/>
+      <c r="E239" s="22"/>
+      <c r="F239" s="25"/>
+      <c r="G239" s="25"/>
+      <c r="H239" s="25"/>
+      <c r="I239" s="26"/>
+      <c r="J239" s="21"/>
       <c r="L239" s="14" t="s">
         <v>17</v>
       </c>
@@ -8963,14 +8970,14 @@
       <c r="U239" s="10"/>
     </row>
     <row r="240" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C240" s="17"/>
-      <c r="D240" s="17"/>
-      <c r="E240" s="23"/>
-      <c r="F240" s="18"/>
-      <c r="G240" s="18"/>
-      <c r="H240" s="18"/>
-      <c r="I240" s="22"/>
-      <c r="J240" s="17"/>
+      <c r="C240" s="21"/>
+      <c r="D240" s="21"/>
+      <c r="E240" s="22"/>
+      <c r="F240" s="25"/>
+      <c r="G240" s="25"/>
+      <c r="H240" s="25"/>
+      <c r="I240" s="26"/>
+      <c r="J240" s="21"/>
       <c r="L240" s="15" t="s">
         <v>23</v>
       </c>
@@ -8993,26 +9000,26 @@
       <c r="B242" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C242" s="17" t="s">
+      <c r="C242" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D242" s="18" t="s">
+      <c r="D242" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E242" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F242" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G242" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H242" s="17"/>
-      <c r="I242" s="25" t="s">
+      <c r="E242" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F242" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G242" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H242" s="21"/>
+      <c r="I242" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J242" s="17"/>
+      <c r="J242" s="21"/>
       <c r="L242" s="9" t="s">
         <v>0</v>
       </c>
@@ -9038,14 +9045,14 @@
       <c r="B243">
         <v>23</v>
       </c>
-      <c r="C243" s="17"/>
-      <c r="D243" s="18"/>
-      <c r="E243" s="23"/>
-      <c r="F243" s="17"/>
-      <c r="G243" s="22"/>
-      <c r="H243" s="17"/>
-      <c r="I243" s="26"/>
-      <c r="J243" s="17"/>
+      <c r="C243" s="21"/>
+      <c r="D243" s="25"/>
+      <c r="E243" s="22"/>
+      <c r="F243" s="21"/>
+      <c r="G243" s="26"/>
+      <c r="H243" s="21"/>
+      <c r="I243" s="24"/>
+      <c r="J243" s="21"/>
       <c r="L243" s="11" t="s">
         <v>5</v>
       </c>
@@ -9081,14 +9088,14 @@
       </c>
     </row>
     <row r="244" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C244" s="17"/>
-      <c r="D244" s="18"/>
-      <c r="E244" s="23"/>
-      <c r="F244" s="17"/>
-      <c r="G244" s="22"/>
-      <c r="H244" s="17"/>
-      <c r="I244" s="26"/>
-      <c r="J244" s="17"/>
+      <c r="C244" s="21"/>
+      <c r="D244" s="25"/>
+      <c r="E244" s="22"/>
+      <c r="F244" s="21"/>
+      <c r="G244" s="26"/>
+      <c r="H244" s="21"/>
+      <c r="I244" s="24"/>
+      <c r="J244" s="21"/>
       <c r="L244" s="12" t="s">
         <v>15</v>
       </c>
@@ -9114,14 +9121,14 @@
       </c>
     </row>
     <row r="245" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C245" s="17"/>
-      <c r="D245" s="18"/>
-      <c r="E245" s="23"/>
-      <c r="F245" s="17"/>
-      <c r="G245" s="22"/>
-      <c r="H245" s="17"/>
-      <c r="I245" s="26"/>
-      <c r="J245" s="17"/>
+      <c r="C245" s="21"/>
+      <c r="D245" s="25"/>
+      <c r="E245" s="22"/>
+      <c r="F245" s="21"/>
+      <c r="G245" s="26"/>
+      <c r="H245" s="21"/>
+      <c r="I245" s="24"/>
+      <c r="J245" s="21"/>
       <c r="L245" s="14" t="s">
         <v>17</v>
       </c>
@@ -9145,14 +9152,14 @@
       <c r="U245" s="10"/>
     </row>
     <row r="246" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C246" s="17"/>
-      <c r="D246" s="18"/>
-      <c r="E246" s="23"/>
-      <c r="F246" s="17"/>
-      <c r="G246" s="22"/>
-      <c r="H246" s="17"/>
-      <c r="I246" s="26"/>
-      <c r="J246" s="17"/>
+      <c r="C246" s="21"/>
+      <c r="D246" s="25"/>
+      <c r="E246" s="22"/>
+      <c r="F246" s="21"/>
+      <c r="G246" s="26"/>
+      <c r="H246" s="21"/>
+      <c r="I246" s="24"/>
+      <c r="J246" s="21"/>
       <c r="L246" s="15" t="s">
         <v>23</v>
       </c>
@@ -9169,24 +9176,24 @@
       <c r="U246" s="10"/>
     </row>
     <row r="247" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C247" s="17" t="s">
+      <c r="C247" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D247" s="17"/>
-      <c r="E247" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F247" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G247" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H247" s="17"/>
-      <c r="I247" s="18" t="s">
+      <c r="D247" s="21"/>
+      <c r="E247" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F247" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G247" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H247" s="21"/>
+      <c r="I247" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J247" s="22" t="s">
+      <c r="J247" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L247" s="9" t="s">
@@ -9211,14 +9218,14 @@
       <c r="U247" s="10"/>
     </row>
     <row r="248" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C248" s="17"/>
-      <c r="D248" s="17"/>
-      <c r="E248" s="17"/>
-      <c r="F248" s="17"/>
-      <c r="G248" s="17"/>
-      <c r="H248" s="17"/>
-      <c r="I248" s="18"/>
-      <c r="J248" s="22"/>
+      <c r="C248" s="21"/>
+      <c r="D248" s="21"/>
+      <c r="E248" s="21"/>
+      <c r="F248" s="21"/>
+      <c r="G248" s="21"/>
+      <c r="H248" s="21"/>
+      <c r="I248" s="25"/>
+      <c r="J248" s="26"/>
       <c r="L248" s="11" t="s">
         <v>5</v>
       </c>
@@ -9254,14 +9261,14 @@
       </c>
     </row>
     <row r="249" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C249" s="17"/>
-      <c r="D249" s="17"/>
-      <c r="E249" s="17"/>
-      <c r="F249" s="17"/>
-      <c r="G249" s="17"/>
-      <c r="H249" s="17"/>
-      <c r="I249" s="18"/>
-      <c r="J249" s="22"/>
+      <c r="C249" s="21"/>
+      <c r="D249" s="21"/>
+      <c r="E249" s="21"/>
+      <c r="F249" s="21"/>
+      <c r="G249" s="21"/>
+      <c r="H249" s="21"/>
+      <c r="I249" s="25"/>
+      <c r="J249" s="26"/>
       <c r="L249" s="12" t="s">
         <v>15</v>
       </c>
@@ -9287,14 +9294,14 @@
       </c>
     </row>
     <row r="250" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C250" s="17"/>
-      <c r="D250" s="17"/>
-      <c r="E250" s="17"/>
-      <c r="F250" s="17"/>
-      <c r="G250" s="17"/>
-      <c r="H250" s="17"/>
-      <c r="I250" s="18"/>
-      <c r="J250" s="22"/>
+      <c r="C250" s="21"/>
+      <c r="D250" s="21"/>
+      <c r="E250" s="21"/>
+      <c r="F250" s="21"/>
+      <c r="G250" s="21"/>
+      <c r="H250" s="21"/>
+      <c r="I250" s="25"/>
+      <c r="J250" s="26"/>
       <c r="L250" s="14" t="s">
         <v>17</v>
       </c>
@@ -9317,14 +9324,14 @@
       <c r="U250" s="10"/>
     </row>
     <row r="251" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C251" s="17"/>
-      <c r="D251" s="17"/>
-      <c r="E251" s="17"/>
-      <c r="F251" s="17"/>
-      <c r="G251" s="17"/>
-      <c r="H251" s="17"/>
-      <c r="I251" s="18"/>
-      <c r="J251" s="22"/>
+      <c r="C251" s="21"/>
+      <c r="D251" s="21"/>
+      <c r="E251" s="21"/>
+      <c r="F251" s="21"/>
+      <c r="G251" s="21"/>
+      <c r="H251" s="21"/>
+      <c r="I251" s="25"/>
+      <c r="J251" s="26"/>
       <c r="L251" s="15" t="s">
         <v>23</v>
       </c>
@@ -9344,26 +9351,26 @@
       <c r="B252" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C252" s="17" t="s">
+      <c r="C252" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D252" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E252" s="18" t="s">
+      <c r="D252" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E252" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F252" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G252" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H252" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I252" s="17"/>
-      <c r="J252" s="27" t="s">
+      <c r="F252" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G252" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H252" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I252" s="21"/>
+      <c r="J252" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L252" s="9" t="s">
@@ -9391,14 +9398,14 @@
       <c r="B253">
         <v>24</v>
       </c>
-      <c r="C253" s="17"/>
-      <c r="D253" s="23"/>
-      <c r="E253" s="18"/>
-      <c r="F253" s="17"/>
-      <c r="G253" s="17"/>
-      <c r="H253" s="22"/>
-      <c r="I253" s="17"/>
-      <c r="J253" s="27"/>
+      <c r="C253" s="21"/>
+      <c r="D253" s="22"/>
+      <c r="E253" s="25"/>
+      <c r="F253" s="21"/>
+      <c r="G253" s="21"/>
+      <c r="H253" s="26"/>
+      <c r="I253" s="21"/>
+      <c r="J253" s="20"/>
       <c r="L253" s="11" t="s">
         <v>5</v>
       </c>
@@ -9437,14 +9444,14 @@
       <c r="B254" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C254" s="17"/>
-      <c r="D254" s="23"/>
-      <c r="E254" s="18"/>
-      <c r="F254" s="17"/>
-      <c r="G254" s="17"/>
-      <c r="H254" s="22"/>
-      <c r="I254" s="17"/>
-      <c r="J254" s="27"/>
+      <c r="C254" s="21"/>
+      <c r="D254" s="22"/>
+      <c r="E254" s="25"/>
+      <c r="F254" s="21"/>
+      <c r="G254" s="21"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="21"/>
+      <c r="J254" s="20"/>
       <c r="L254" s="12" t="s">
         <v>15</v>
       </c>
@@ -9473,14 +9480,14 @@
       <c r="B255">
         <v>10</v>
       </c>
-      <c r="C255" s="17"/>
-      <c r="D255" s="23"/>
-      <c r="E255" s="18"/>
-      <c r="F255" s="17"/>
-      <c r="G255" s="17"/>
-      <c r="H255" s="22"/>
-      <c r="I255" s="17"/>
-      <c r="J255" s="27"/>
+      <c r="C255" s="21"/>
+      <c r="D255" s="22"/>
+      <c r="E255" s="25"/>
+      <c r="F255" s="21"/>
+      <c r="G255" s="21"/>
+      <c r="H255" s="26"/>
+      <c r="I255" s="21"/>
+      <c r="J255" s="20"/>
       <c r="L255" s="14" t="s">
         <v>17</v>
       </c>
@@ -9505,14 +9512,14 @@
       <c r="U255" s="10"/>
     </row>
     <row r="256" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C256" s="17"/>
-      <c r="D256" s="23"/>
-      <c r="E256" s="18"/>
-      <c r="F256" s="17"/>
-      <c r="G256" s="17"/>
-      <c r="H256" s="22"/>
-      <c r="I256" s="17"/>
-      <c r="J256" s="27"/>
+      <c r="C256" s="21"/>
+      <c r="D256" s="22"/>
+      <c r="E256" s="25"/>
+      <c r="F256" s="21"/>
+      <c r="G256" s="21"/>
+      <c r="H256" s="26"/>
+      <c r="I256" s="21"/>
+      <c r="J256" s="20"/>
       <c r="L256" s="15" t="s">
         <v>23</v>
       </c>
@@ -9529,26 +9536,26 @@
       <c r="U256" s="10"/>
     </row>
     <row r="257" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C257" s="17" t="s">
+      <c r="C257" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D257" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E257" s="23"/>
-      <c r="F257" s="18" t="s">
+      <c r="D257" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E257" s="22"/>
+      <c r="F257" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G257" s="18" t="s">
+      <c r="G257" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H257" s="18" t="s">
+      <c r="H257" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I257" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J257" s="17"/>
+      <c r="I257" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J257" s="21"/>
       <c r="L257" s="9" t="s">
         <v>0</v>
       </c>
@@ -9571,14 +9578,14 @@
       <c r="U257" s="10"/>
     </row>
     <row r="258" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C258" s="17"/>
-      <c r="D258" s="17"/>
-      <c r="E258" s="23"/>
-      <c r="F258" s="18"/>
-      <c r="G258" s="18"/>
-      <c r="H258" s="18"/>
-      <c r="I258" s="22"/>
-      <c r="J258" s="17"/>
+      <c r="C258" s="21"/>
+      <c r="D258" s="21"/>
+      <c r="E258" s="22"/>
+      <c r="F258" s="25"/>
+      <c r="G258" s="25"/>
+      <c r="H258" s="25"/>
+      <c r="I258" s="26"/>
+      <c r="J258" s="21"/>
       <c r="L258" s="11" t="s">
         <v>5</v>
       </c>
@@ -9614,14 +9621,14 @@
       </c>
     </row>
     <row r="259" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C259" s="17"/>
-      <c r="D259" s="17"/>
-      <c r="E259" s="23"/>
-      <c r="F259" s="18"/>
-      <c r="G259" s="18"/>
-      <c r="H259" s="18"/>
-      <c r="I259" s="22"/>
-      <c r="J259" s="17"/>
+      <c r="C259" s="21"/>
+      <c r="D259" s="21"/>
+      <c r="E259" s="22"/>
+      <c r="F259" s="25"/>
+      <c r="G259" s="25"/>
+      <c r="H259" s="25"/>
+      <c r="I259" s="26"/>
+      <c r="J259" s="21"/>
       <c r="L259" s="12" t="s">
         <v>15</v>
       </c>
@@ -9647,14 +9654,14 @@
       </c>
     </row>
     <row r="260" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C260" s="17"/>
-      <c r="D260" s="17"/>
-      <c r="E260" s="23"/>
-      <c r="F260" s="18"/>
-      <c r="G260" s="18"/>
-      <c r="H260" s="18"/>
-      <c r="I260" s="22"/>
-      <c r="J260" s="17"/>
+      <c r="C260" s="21"/>
+      <c r="D260" s="21"/>
+      <c r="E260" s="22"/>
+      <c r="F260" s="25"/>
+      <c r="G260" s="25"/>
+      <c r="H260" s="25"/>
+      <c r="I260" s="26"/>
+      <c r="J260" s="21"/>
       <c r="L260" s="14" t="s">
         <v>17</v>
       </c>
@@ -9677,14 +9684,14 @@
       <c r="U260" s="10"/>
     </row>
     <row r="261" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C261" s="17"/>
-      <c r="D261" s="17"/>
-      <c r="E261" s="23"/>
-      <c r="F261" s="18"/>
-      <c r="G261" s="18"/>
-      <c r="H261" s="18"/>
-      <c r="I261" s="22"/>
-      <c r="J261" s="17"/>
+      <c r="C261" s="21"/>
+      <c r="D261" s="21"/>
+      <c r="E261" s="22"/>
+      <c r="F261" s="25"/>
+      <c r="G261" s="25"/>
+      <c r="H261" s="25"/>
+      <c r="I261" s="26"/>
+      <c r="J261" s="21"/>
       <c r="L261" s="15" t="s">
         <v>23</v>
       </c>
@@ -9707,26 +9714,26 @@
       <c r="B263" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C263" s="17" t="s">
+      <c r="C263" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D263" s="18" t="s">
+      <c r="D263" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E263" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F263" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G263" s="17"/>
-      <c r="H263" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I263" s="25" t="s">
+      <c r="E263" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F263" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G263" s="21"/>
+      <c r="H263" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I263" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J263" s="17"/>
+      <c r="J263" s="21"/>
       <c r="L263" s="9" t="s">
         <v>0</v>
       </c>
@@ -9752,14 +9759,14 @@
       <c r="B264">
         <v>25</v>
       </c>
-      <c r="C264" s="17"/>
-      <c r="D264" s="18"/>
-      <c r="E264" s="23"/>
-      <c r="F264" s="22"/>
-      <c r="G264" s="17"/>
-      <c r="H264" s="17"/>
-      <c r="I264" s="26"/>
-      <c r="J264" s="17"/>
+      <c r="C264" s="21"/>
+      <c r="D264" s="25"/>
+      <c r="E264" s="22"/>
+      <c r="F264" s="26"/>
+      <c r="G264" s="21"/>
+      <c r="H264" s="21"/>
+      <c r="I264" s="24"/>
+      <c r="J264" s="21"/>
       <c r="L264" s="11" t="s">
         <v>5</v>
       </c>
@@ -9795,14 +9802,14 @@
       </c>
     </row>
     <row r="265" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C265" s="17"/>
-      <c r="D265" s="18"/>
-      <c r="E265" s="23"/>
-      <c r="F265" s="22"/>
-      <c r="G265" s="17"/>
-      <c r="H265" s="17"/>
-      <c r="I265" s="26"/>
-      <c r="J265" s="17"/>
+      <c r="C265" s="21"/>
+      <c r="D265" s="25"/>
+      <c r="E265" s="22"/>
+      <c r="F265" s="26"/>
+      <c r="G265" s="21"/>
+      <c r="H265" s="21"/>
+      <c r="I265" s="24"/>
+      <c r="J265" s="21"/>
       <c r="L265" s="12" t="s">
         <v>15</v>
       </c>
@@ -9828,14 +9835,14 @@
       </c>
     </row>
     <row r="266" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C266" s="17"/>
-      <c r="D266" s="18"/>
-      <c r="E266" s="23"/>
-      <c r="F266" s="22"/>
-      <c r="G266" s="17"/>
-      <c r="H266" s="17"/>
-      <c r="I266" s="26"/>
-      <c r="J266" s="17"/>
+      <c r="C266" s="21"/>
+      <c r="D266" s="25"/>
+      <c r="E266" s="22"/>
+      <c r="F266" s="26"/>
+      <c r="G266" s="21"/>
+      <c r="H266" s="21"/>
+      <c r="I266" s="24"/>
+      <c r="J266" s="21"/>
       <c r="L266" s="14" t="s">
         <v>17</v>
       </c>
@@ -9859,14 +9866,14 @@
       <c r="U266" s="10"/>
     </row>
     <row r="267" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C267" s="17"/>
-      <c r="D267" s="18"/>
-      <c r="E267" s="23"/>
-      <c r="F267" s="22"/>
-      <c r="G267" s="17"/>
-      <c r="H267" s="17"/>
-      <c r="I267" s="26"/>
-      <c r="J267" s="17"/>
+      <c r="C267" s="21"/>
+      <c r="D267" s="25"/>
+      <c r="E267" s="22"/>
+      <c r="F267" s="26"/>
+      <c r="G267" s="21"/>
+      <c r="H267" s="21"/>
+      <c r="I267" s="24"/>
+      <c r="J267" s="21"/>
       <c r="L267" s="15" t="s">
         <v>23</v>
       </c>
@@ -9883,24 +9890,24 @@
       <c r="U267" s="10"/>
     </row>
     <row r="268" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C268" s="17" t="s">
+      <c r="C268" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D268" s="17"/>
-      <c r="E268" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F268" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G268" s="17"/>
-      <c r="H268" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I268" s="18" t="s">
+      <c r="D268" s="21"/>
+      <c r="E268" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F268" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G268" s="21"/>
+      <c r="H268" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I268" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J268" s="22" t="s">
+      <c r="J268" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L268" s="9" t="s">
@@ -9925,14 +9932,14 @@
       <c r="U268" s="10"/>
     </row>
     <row r="269" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C269" s="17"/>
-      <c r="D269" s="17"/>
-      <c r="E269" s="17"/>
-      <c r="F269" s="17"/>
-      <c r="G269" s="17"/>
-      <c r="H269" s="17"/>
-      <c r="I269" s="18"/>
-      <c r="J269" s="22"/>
+      <c r="C269" s="21"/>
+      <c r="D269" s="21"/>
+      <c r="E269" s="21"/>
+      <c r="F269" s="21"/>
+      <c r="G269" s="21"/>
+      <c r="H269" s="21"/>
+      <c r="I269" s="25"/>
+      <c r="J269" s="26"/>
       <c r="L269" s="11" t="s">
         <v>5</v>
       </c>
@@ -9968,14 +9975,14 @@
       </c>
     </row>
     <row r="270" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C270" s="17"/>
-      <c r="D270" s="17"/>
-      <c r="E270" s="17"/>
-      <c r="F270" s="17"/>
-      <c r="G270" s="17"/>
-      <c r="H270" s="17"/>
-      <c r="I270" s="18"/>
-      <c r="J270" s="22"/>
+      <c r="C270" s="21"/>
+      <c r="D270" s="21"/>
+      <c r="E270" s="21"/>
+      <c r="F270" s="21"/>
+      <c r="G270" s="21"/>
+      <c r="H270" s="21"/>
+      <c r="I270" s="25"/>
+      <c r="J270" s="26"/>
       <c r="L270" s="12" t="s">
         <v>15</v>
       </c>
@@ -10001,14 +10008,14 @@
       </c>
     </row>
     <row r="271" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C271" s="17"/>
-      <c r="D271" s="17"/>
-      <c r="E271" s="17"/>
-      <c r="F271" s="17"/>
-      <c r="G271" s="17"/>
-      <c r="H271" s="17"/>
-      <c r="I271" s="18"/>
-      <c r="J271" s="22"/>
+      <c r="C271" s="21"/>
+      <c r="D271" s="21"/>
+      <c r="E271" s="21"/>
+      <c r="F271" s="21"/>
+      <c r="G271" s="21"/>
+      <c r="H271" s="21"/>
+      <c r="I271" s="25"/>
+      <c r="J271" s="26"/>
       <c r="L271" s="14" t="s">
         <v>17</v>
       </c>
@@ -10031,14 +10038,14 @@
       <c r="U271" s="10"/>
     </row>
     <row r="272" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C272" s="17"/>
-      <c r="D272" s="17"/>
-      <c r="E272" s="17"/>
-      <c r="F272" s="17"/>
-      <c r="G272" s="17"/>
-      <c r="H272" s="17"/>
-      <c r="I272" s="18"/>
-      <c r="J272" s="22"/>
+      <c r="C272" s="21"/>
+      <c r="D272" s="21"/>
+      <c r="E272" s="21"/>
+      <c r="F272" s="21"/>
+      <c r="G272" s="21"/>
+      <c r="H272" s="21"/>
+      <c r="I272" s="25"/>
+      <c r="J272" s="26"/>
       <c r="L272" s="15" t="s">
         <v>23</v>
       </c>
@@ -10058,26 +10065,26 @@
       <c r="B273" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C273" s="17" t="s">
+      <c r="C273" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D273" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E273" s="18" t="s">
+      <c r="D273" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E273" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F273" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G273" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H273" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I273" s="17"/>
-      <c r="J273" s="27" t="s">
+      <c r="F273" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G273" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H273" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I273" s="21"/>
+      <c r="J273" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L273" s="9" t="s">
@@ -10105,14 +10112,14 @@
       <c r="B274">
         <v>26</v>
       </c>
-      <c r="C274" s="17"/>
-      <c r="D274" s="23"/>
-      <c r="E274" s="18"/>
-      <c r="F274" s="17"/>
-      <c r="G274" s="22"/>
-      <c r="H274" s="17"/>
-      <c r="I274" s="17"/>
-      <c r="J274" s="27"/>
+      <c r="C274" s="21"/>
+      <c r="D274" s="22"/>
+      <c r="E274" s="25"/>
+      <c r="F274" s="21"/>
+      <c r="G274" s="26"/>
+      <c r="H274" s="21"/>
+      <c r="I274" s="21"/>
+      <c r="J274" s="20"/>
       <c r="L274" s="11" t="s">
         <v>5</v>
       </c>
@@ -10151,14 +10158,14 @@
       <c r="B275" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C275" s="17"/>
-      <c r="D275" s="23"/>
-      <c r="E275" s="18"/>
-      <c r="F275" s="17"/>
-      <c r="G275" s="22"/>
-      <c r="H275" s="17"/>
-      <c r="I275" s="17"/>
-      <c r="J275" s="27"/>
+      <c r="C275" s="21"/>
+      <c r="D275" s="22"/>
+      <c r="E275" s="25"/>
+      <c r="F275" s="21"/>
+      <c r="G275" s="26"/>
+      <c r="H275" s="21"/>
+      <c r="I275" s="21"/>
+      <c r="J275" s="20"/>
       <c r="L275" s="12" t="s">
         <v>15</v>
       </c>
@@ -10187,14 +10194,14 @@
       <c r="B276">
         <v>11</v>
       </c>
-      <c r="C276" s="17"/>
-      <c r="D276" s="23"/>
-      <c r="E276" s="18"/>
-      <c r="F276" s="17"/>
-      <c r="G276" s="22"/>
-      <c r="H276" s="17"/>
-      <c r="I276" s="17"/>
-      <c r="J276" s="27"/>
+      <c r="C276" s="21"/>
+      <c r="D276" s="22"/>
+      <c r="E276" s="25"/>
+      <c r="F276" s="21"/>
+      <c r="G276" s="26"/>
+      <c r="H276" s="21"/>
+      <c r="I276" s="21"/>
+      <c r="J276" s="20"/>
       <c r="L276" s="14" t="s">
         <v>17</v>
       </c>
@@ -10219,14 +10226,14 @@
       <c r="U276" s="10"/>
     </row>
     <row r="277" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C277" s="17"/>
-      <c r="D277" s="23"/>
-      <c r="E277" s="18"/>
-      <c r="F277" s="17"/>
-      <c r="G277" s="22"/>
-      <c r="H277" s="17"/>
-      <c r="I277" s="17"/>
-      <c r="J277" s="27"/>
+      <c r="C277" s="21"/>
+      <c r="D277" s="22"/>
+      <c r="E277" s="25"/>
+      <c r="F277" s="21"/>
+      <c r="G277" s="26"/>
+      <c r="H277" s="21"/>
+      <c r="I277" s="21"/>
+      <c r="J277" s="20"/>
       <c r="L277" s="15" t="s">
         <v>23</v>
       </c>
@@ -10243,26 +10250,26 @@
       <c r="U277" s="10"/>
     </row>
     <row r="278" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C278" s="17" t="s">
+      <c r="C278" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D278" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E278" s="23"/>
-      <c r="F278" s="18" t="s">
+      <c r="D278" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E278" s="22"/>
+      <c r="F278" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G278" s="18" t="s">
+      <c r="G278" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H278" s="18" t="s">
+      <c r="H278" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I278" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J278" s="23"/>
+      <c r="I278" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J278" s="22"/>
       <c r="L278" s="9" t="s">
         <v>0</v>
       </c>
@@ -10285,14 +10292,14 @@
       <c r="U278" s="10"/>
     </row>
     <row r="279" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C279" s="17"/>
-      <c r="D279" s="17"/>
-      <c r="E279" s="23"/>
-      <c r="F279" s="18"/>
-      <c r="G279" s="18"/>
-      <c r="H279" s="18"/>
-      <c r="I279" s="22"/>
-      <c r="J279" s="23"/>
+      <c r="C279" s="21"/>
+      <c r="D279" s="21"/>
+      <c r="E279" s="22"/>
+      <c r="F279" s="25"/>
+      <c r="G279" s="25"/>
+      <c r="H279" s="25"/>
+      <c r="I279" s="26"/>
+      <c r="J279" s="22"/>
       <c r="L279" s="11" t="s">
         <v>5</v>
       </c>
@@ -10328,14 +10335,14 @@
       </c>
     </row>
     <row r="280" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C280" s="17"/>
-      <c r="D280" s="17"/>
-      <c r="E280" s="23"/>
-      <c r="F280" s="18"/>
-      <c r="G280" s="18"/>
-      <c r="H280" s="18"/>
-      <c r="I280" s="22"/>
-      <c r="J280" s="23"/>
+      <c r="C280" s="21"/>
+      <c r="D280" s="21"/>
+      <c r="E280" s="22"/>
+      <c r="F280" s="25"/>
+      <c r="G280" s="25"/>
+      <c r="H280" s="25"/>
+      <c r="I280" s="26"/>
+      <c r="J280" s="22"/>
       <c r="L280" s="12" t="s">
         <v>15</v>
       </c>
@@ -10361,14 +10368,14 @@
       </c>
     </row>
     <row r="281" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C281" s="17"/>
-      <c r="D281" s="17"/>
-      <c r="E281" s="23"/>
-      <c r="F281" s="18"/>
-      <c r="G281" s="18"/>
-      <c r="H281" s="18"/>
-      <c r="I281" s="22"/>
-      <c r="J281" s="23"/>
+      <c r="C281" s="21"/>
+      <c r="D281" s="21"/>
+      <c r="E281" s="22"/>
+      <c r="F281" s="25"/>
+      <c r="G281" s="25"/>
+      <c r="H281" s="25"/>
+      <c r="I281" s="26"/>
+      <c r="J281" s="22"/>
       <c r="L281" s="14" t="s">
         <v>17</v>
       </c>
@@ -10391,14 +10398,14 @@
       <c r="U281" s="10"/>
     </row>
     <row r="282" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C282" s="17"/>
-      <c r="D282" s="17"/>
-      <c r="E282" s="23"/>
-      <c r="F282" s="18"/>
-      <c r="G282" s="18"/>
-      <c r="H282" s="18"/>
-      <c r="I282" s="22"/>
-      <c r="J282" s="23"/>
+      <c r="C282" s="21"/>
+      <c r="D282" s="21"/>
+      <c r="E282" s="22"/>
+      <c r="F282" s="25"/>
+      <c r="G282" s="25"/>
+      <c r="H282" s="25"/>
+      <c r="I282" s="26"/>
+      <c r="J282" s="22"/>
       <c r="L282" s="15" t="s">
         <v>23</v>
       </c>
@@ -10433,26 +10440,26 @@
       <c r="B288" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C288" s="17" t="s">
+      <c r="C288" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D288" s="18" t="s">
+      <c r="D288" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E288" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F288" s="23"/>
-      <c r="G288" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H288" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I288" s="25" t="s">
+      <c r="E288" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F288" s="22"/>
+      <c r="G288" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H288" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I288" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J288" s="17"/>
+      <c r="J288" s="21"/>
       <c r="L288" s="9" t="s">
         <v>0</v>
       </c>
@@ -10478,14 +10485,14 @@
       <c r="B289">
         <v>27</v>
       </c>
-      <c r="C289" s="17"/>
-      <c r="D289" s="18"/>
-      <c r="E289" s="23"/>
-      <c r="F289" s="23"/>
-      <c r="G289" s="17"/>
-      <c r="H289" s="22"/>
-      <c r="I289" s="26"/>
-      <c r="J289" s="17"/>
+      <c r="C289" s="21"/>
+      <c r="D289" s="25"/>
+      <c r="E289" s="22"/>
+      <c r="F289" s="22"/>
+      <c r="G289" s="21"/>
+      <c r="H289" s="26"/>
+      <c r="I289" s="24"/>
+      <c r="J289" s="21"/>
       <c r="L289" s="11" t="s">
         <v>5</v>
       </c>
@@ -10521,14 +10528,14 @@
       </c>
     </row>
     <row r="290" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C290" s="17"/>
-      <c r="D290" s="18"/>
-      <c r="E290" s="23"/>
-      <c r="F290" s="23"/>
-      <c r="G290" s="17"/>
-      <c r="H290" s="22"/>
-      <c r="I290" s="26"/>
-      <c r="J290" s="17"/>
+      <c r="C290" s="21"/>
+      <c r="D290" s="25"/>
+      <c r="E290" s="22"/>
+      <c r="F290" s="22"/>
+      <c r="G290" s="21"/>
+      <c r="H290" s="26"/>
+      <c r="I290" s="24"/>
+      <c r="J290" s="21"/>
       <c r="L290" s="12" t="s">
         <v>15</v>
       </c>
@@ -10554,14 +10561,14 @@
       </c>
     </row>
     <row r="291" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C291" s="17"/>
-      <c r="D291" s="18"/>
-      <c r="E291" s="23"/>
-      <c r="F291" s="23"/>
-      <c r="G291" s="17"/>
-      <c r="H291" s="22"/>
-      <c r="I291" s="26"/>
-      <c r="J291" s="17"/>
+      <c r="C291" s="21"/>
+      <c r="D291" s="25"/>
+      <c r="E291" s="22"/>
+      <c r="F291" s="22"/>
+      <c r="G291" s="21"/>
+      <c r="H291" s="26"/>
+      <c r="I291" s="24"/>
+      <c r="J291" s="21"/>
       <c r="L291" s="14" t="s">
         <v>17</v>
       </c>
@@ -10585,14 +10592,14 @@
       <c r="U291" s="10"/>
     </row>
     <row r="292" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C292" s="17"/>
-      <c r="D292" s="18"/>
-      <c r="E292" s="23"/>
-      <c r="F292" s="23"/>
-      <c r="G292" s="17"/>
-      <c r="H292" s="22"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="17"/>
+      <c r="C292" s="21"/>
+      <c r="D292" s="25"/>
+      <c r="E292" s="22"/>
+      <c r="F292" s="22"/>
+      <c r="G292" s="21"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="21"/>
       <c r="L292" s="15" t="s">
         <v>23</v>
       </c>
@@ -10609,24 +10616,24 @@
       <c r="U292" s="10"/>
     </row>
     <row r="293" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C293" s="17" t="s">
+      <c r="C293" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D293" s="17"/>
-      <c r="E293" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F293" s="23"/>
-      <c r="G293" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H293" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I293" s="18" t="s">
+      <c r="D293" s="21"/>
+      <c r="E293" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F293" s="22"/>
+      <c r="G293" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H293" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I293" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J293" s="22" t="s">
+      <c r="J293" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L293" s="9" t="s">
@@ -10651,14 +10658,14 @@
       <c r="U293" s="10"/>
     </row>
     <row r="294" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C294" s="17"/>
-      <c r="D294" s="17"/>
-      <c r="E294" s="17"/>
-      <c r="F294" s="23"/>
-      <c r="G294" s="17"/>
-      <c r="H294" s="17"/>
-      <c r="I294" s="18"/>
-      <c r="J294" s="22"/>
+      <c r="C294" s="21"/>
+      <c r="D294" s="21"/>
+      <c r="E294" s="21"/>
+      <c r="F294" s="22"/>
+      <c r="G294" s="21"/>
+      <c r="H294" s="21"/>
+      <c r="I294" s="25"/>
+      <c r="J294" s="26"/>
       <c r="L294" s="11" t="s">
         <v>5</v>
       </c>
@@ -10694,14 +10701,14 @@
       </c>
     </row>
     <row r="295" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C295" s="17"/>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
-      <c r="F295" s="23"/>
-      <c r="G295" s="17"/>
-      <c r="H295" s="17"/>
-      <c r="I295" s="18"/>
-      <c r="J295" s="22"/>
+      <c r="C295" s="21"/>
+      <c r="D295" s="21"/>
+      <c r="E295" s="21"/>
+      <c r="F295" s="22"/>
+      <c r="G295" s="21"/>
+      <c r="H295" s="21"/>
+      <c r="I295" s="25"/>
+      <c r="J295" s="26"/>
       <c r="L295" s="12" t="s">
         <v>15</v>
       </c>
@@ -10727,14 +10734,14 @@
       </c>
     </row>
     <row r="296" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C296" s="17"/>
-      <c r="D296" s="17"/>
-      <c r="E296" s="17"/>
-      <c r="F296" s="23"/>
-      <c r="G296" s="17"/>
-      <c r="H296" s="17"/>
-      <c r="I296" s="18"/>
-      <c r="J296" s="22"/>
+      <c r="C296" s="21"/>
+      <c r="D296" s="21"/>
+      <c r="E296" s="21"/>
+      <c r="F296" s="22"/>
+      <c r="G296" s="21"/>
+      <c r="H296" s="21"/>
+      <c r="I296" s="25"/>
+      <c r="J296" s="26"/>
       <c r="L296" s="14" t="s">
         <v>17</v>
       </c>
@@ -10757,14 +10764,14 @@
       <c r="U296" s="10"/>
     </row>
     <row r="297" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C297" s="17"/>
-      <c r="D297" s="17"/>
-      <c r="E297" s="17"/>
-      <c r="F297" s="23"/>
-      <c r="G297" s="17"/>
-      <c r="H297" s="17"/>
-      <c r="I297" s="18"/>
-      <c r="J297" s="22"/>
+      <c r="C297" s="21"/>
+      <c r="D297" s="21"/>
+      <c r="E297" s="21"/>
+      <c r="F297" s="22"/>
+      <c r="G297" s="21"/>
+      <c r="H297" s="21"/>
+      <c r="I297" s="25"/>
+      <c r="J297" s="26"/>
       <c r="L297" s="15" t="s">
         <v>23</v>
       </c>
@@ -10784,26 +10791,26 @@
       <c r="B298" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C298" s="17" t="s">
+      <c r="C298" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D298" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E298" s="18" t="s">
+      <c r="D298" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E298" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F298" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G298" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H298" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I298" s="17"/>
-      <c r="J298" s="27" t="s">
+      <c r="F298" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G298" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H298" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I298" s="21"/>
+      <c r="J298" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L298" s="9" t="s">
@@ -10831,14 +10838,14 @@
       <c r="B299">
         <v>28</v>
       </c>
-      <c r="C299" s="17"/>
-      <c r="D299" s="23"/>
-      <c r="E299" s="18"/>
-      <c r="F299" s="22"/>
-      <c r="G299" s="17"/>
-      <c r="H299" s="17"/>
-      <c r="I299" s="17"/>
-      <c r="J299" s="27"/>
+      <c r="C299" s="21"/>
+      <c r="D299" s="22"/>
+      <c r="E299" s="25"/>
+      <c r="F299" s="26"/>
+      <c r="G299" s="21"/>
+      <c r="H299" s="21"/>
+      <c r="I299" s="21"/>
+      <c r="J299" s="20"/>
       <c r="L299" s="11" t="s">
         <v>5</v>
       </c>
@@ -10877,14 +10884,14 @@
       <c r="B300" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C300" s="17"/>
-      <c r="D300" s="23"/>
-      <c r="E300" s="18"/>
-      <c r="F300" s="22"/>
-      <c r="G300" s="17"/>
-      <c r="H300" s="17"/>
-      <c r="I300" s="17"/>
-      <c r="J300" s="27"/>
+      <c r="C300" s="21"/>
+      <c r="D300" s="22"/>
+      <c r="E300" s="25"/>
+      <c r="F300" s="26"/>
+      <c r="G300" s="21"/>
+      <c r="H300" s="21"/>
+      <c r="I300" s="21"/>
+      <c r="J300" s="20"/>
       <c r="L300" s="12" t="s">
         <v>15</v>
       </c>
@@ -10913,14 +10920,14 @@
       <c r="B301">
         <v>12</v>
       </c>
-      <c r="C301" s="17"/>
-      <c r="D301" s="23"/>
-      <c r="E301" s="18"/>
-      <c r="F301" s="22"/>
-      <c r="G301" s="17"/>
-      <c r="H301" s="17"/>
-      <c r="I301" s="17"/>
-      <c r="J301" s="27"/>
+      <c r="C301" s="21"/>
+      <c r="D301" s="22"/>
+      <c r="E301" s="25"/>
+      <c r="F301" s="26"/>
+      <c r="G301" s="21"/>
+      <c r="H301" s="21"/>
+      <c r="I301" s="21"/>
+      <c r="J301" s="20"/>
       <c r="L301" s="14" t="s">
         <v>17</v>
       </c>
@@ -10945,14 +10952,14 @@
       <c r="U301" s="10"/>
     </row>
     <row r="302" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C302" s="17"/>
-      <c r="D302" s="23"/>
-      <c r="E302" s="18"/>
-      <c r="F302" s="22"/>
-      <c r="G302" s="17"/>
-      <c r="H302" s="17"/>
-      <c r="I302" s="17"/>
-      <c r="J302" s="27"/>
+      <c r="C302" s="21"/>
+      <c r="D302" s="22"/>
+      <c r="E302" s="25"/>
+      <c r="F302" s="26"/>
+      <c r="G302" s="21"/>
+      <c r="H302" s="21"/>
+      <c r="I302" s="21"/>
+      <c r="J302" s="20"/>
       <c r="L302" s="15" t="s">
         <v>23</v>
       </c>
@@ -10969,26 +10976,26 @@
       <c r="U302" s="10"/>
     </row>
     <row r="303" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C303" s="17" t="s">
+      <c r="C303" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D303" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E303" s="23"/>
-      <c r="F303" s="18" t="s">
+      <c r="D303" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E303" s="22"/>
+      <c r="F303" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G303" s="18" t="s">
+      <c r="G303" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H303" s="18" t="s">
+      <c r="H303" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I303" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J303" s="17"/>
+      <c r="I303" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J303" s="21"/>
       <c r="L303" s="9" t="s">
         <v>0</v>
       </c>
@@ -11011,14 +11018,14 @@
       <c r="U303" s="10"/>
     </row>
     <row r="304" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C304" s="17"/>
-      <c r="D304" s="17"/>
-      <c r="E304" s="23"/>
-      <c r="F304" s="18"/>
-      <c r="G304" s="18"/>
-      <c r="H304" s="18"/>
-      <c r="I304" s="22"/>
-      <c r="J304" s="17"/>
+      <c r="C304" s="21"/>
+      <c r="D304" s="21"/>
+      <c r="E304" s="22"/>
+      <c r="F304" s="25"/>
+      <c r="G304" s="25"/>
+      <c r="H304" s="25"/>
+      <c r="I304" s="26"/>
+      <c r="J304" s="21"/>
       <c r="L304" s="11" t="s">
         <v>5</v>
       </c>
@@ -11054,14 +11061,14 @@
       </c>
     </row>
     <row r="305" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C305" s="17"/>
-      <c r="D305" s="17"/>
-      <c r="E305" s="23"/>
-      <c r="F305" s="18"/>
-      <c r="G305" s="18"/>
-      <c r="H305" s="18"/>
-      <c r="I305" s="22"/>
-      <c r="J305" s="17"/>
+      <c r="C305" s="21"/>
+      <c r="D305" s="21"/>
+      <c r="E305" s="22"/>
+      <c r="F305" s="25"/>
+      <c r="G305" s="25"/>
+      <c r="H305" s="25"/>
+      <c r="I305" s="26"/>
+      <c r="J305" s="21"/>
       <c r="L305" s="12" t="s">
         <v>15</v>
       </c>
@@ -11087,14 +11094,14 @@
       </c>
     </row>
     <row r="306" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C306" s="17"/>
-      <c r="D306" s="17"/>
-      <c r="E306" s="23"/>
-      <c r="F306" s="18"/>
-      <c r="G306" s="18"/>
-      <c r="H306" s="18"/>
-      <c r="I306" s="22"/>
-      <c r="J306" s="17"/>
+      <c r="C306" s="21"/>
+      <c r="D306" s="21"/>
+      <c r="E306" s="22"/>
+      <c r="F306" s="25"/>
+      <c r="G306" s="25"/>
+      <c r="H306" s="25"/>
+      <c r="I306" s="26"/>
+      <c r="J306" s="21"/>
       <c r="L306" s="14" t="s">
         <v>17</v>
       </c>
@@ -11117,14 +11124,14 @@
       <c r="U306" s="10"/>
     </row>
     <row r="307" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C307" s="17"/>
-      <c r="D307" s="17"/>
-      <c r="E307" s="23"/>
-      <c r="F307" s="18"/>
-      <c r="G307" s="18"/>
-      <c r="H307" s="18"/>
-      <c r="I307" s="22"/>
-      <c r="J307" s="17"/>
+      <c r="C307" s="21"/>
+      <c r="D307" s="21"/>
+      <c r="E307" s="22"/>
+      <c r="F307" s="25"/>
+      <c r="G307" s="25"/>
+      <c r="H307" s="25"/>
+      <c r="I307" s="26"/>
+      <c r="J307" s="21"/>
       <c r="L307" s="15" t="s">
         <v>23</v>
       </c>
@@ -11147,26 +11154,26 @@
       <c r="B309" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C309" s="17" t="s">
+      <c r="C309" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D309" s="18" t="s">
+      <c r="D309" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E309" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F309" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G309" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H309" s="17"/>
-      <c r="I309" s="25" t="s">
+      <c r="E309" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F309" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G309" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H309" s="21"/>
+      <c r="I309" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J309" s="17"/>
+      <c r="J309" s="21"/>
       <c r="L309" s="9" t="s">
         <v>0</v>
       </c>
@@ -11192,14 +11199,14 @@
       <c r="B310">
         <v>29</v>
       </c>
-      <c r="C310" s="17"/>
-      <c r="D310" s="18"/>
-      <c r="E310" s="23"/>
-      <c r="F310" s="17"/>
-      <c r="G310" s="22"/>
-      <c r="H310" s="17"/>
-      <c r="I310" s="26"/>
-      <c r="J310" s="17"/>
+      <c r="C310" s="21"/>
+      <c r="D310" s="25"/>
+      <c r="E310" s="22"/>
+      <c r="F310" s="21"/>
+      <c r="G310" s="26"/>
+      <c r="H310" s="21"/>
+      <c r="I310" s="24"/>
+      <c r="J310" s="21"/>
       <c r="L310" s="11" t="s">
         <v>5</v>
       </c>
@@ -11235,14 +11242,14 @@
       </c>
     </row>
     <row r="311" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C311" s="17"/>
-      <c r="D311" s="18"/>
-      <c r="E311" s="23"/>
-      <c r="F311" s="17"/>
-      <c r="G311" s="22"/>
-      <c r="H311" s="17"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="17"/>
+      <c r="C311" s="21"/>
+      <c r="D311" s="25"/>
+      <c r="E311" s="22"/>
+      <c r="F311" s="21"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="21"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="21"/>
       <c r="L311" s="12" t="s">
         <v>15</v>
       </c>
@@ -11268,14 +11275,14 @@
       </c>
     </row>
     <row r="312" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C312" s="17"/>
-      <c r="D312" s="18"/>
-      <c r="E312" s="23"/>
-      <c r="F312" s="17"/>
-      <c r="G312" s="22"/>
-      <c r="H312" s="17"/>
-      <c r="I312" s="26"/>
-      <c r="J312" s="17"/>
+      <c r="C312" s="21"/>
+      <c r="D312" s="25"/>
+      <c r="E312" s="22"/>
+      <c r="F312" s="21"/>
+      <c r="G312" s="26"/>
+      <c r="H312" s="21"/>
+      <c r="I312" s="24"/>
+      <c r="J312" s="21"/>
       <c r="L312" s="14" t="s">
         <v>17</v>
       </c>
@@ -11299,14 +11306,14 @@
       <c r="U312" s="10"/>
     </row>
     <row r="313" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C313" s="17"/>
-      <c r="D313" s="18"/>
-      <c r="E313" s="23"/>
-      <c r="F313" s="17"/>
-      <c r="G313" s="22"/>
-      <c r="H313" s="17"/>
-      <c r="I313" s="26"/>
-      <c r="J313" s="17"/>
+      <c r="C313" s="21"/>
+      <c r="D313" s="25"/>
+      <c r="E313" s="22"/>
+      <c r="F313" s="21"/>
+      <c r="G313" s="26"/>
+      <c r="H313" s="21"/>
+      <c r="I313" s="24"/>
+      <c r="J313" s="21"/>
       <c r="L313" s="15" t="s">
         <v>23</v>
       </c>
@@ -11323,24 +11330,24 @@
       <c r="U313" s="10"/>
     </row>
     <row r="314" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C314" s="17" t="s">
+      <c r="C314" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D314" s="17"/>
-      <c r="E314" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F314" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G314" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H314" s="17"/>
-      <c r="I314" s="18" t="s">
+      <c r="D314" s="21"/>
+      <c r="E314" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F314" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G314" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H314" s="21"/>
+      <c r="I314" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J314" s="22" t="s">
+      <c r="J314" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L314" s="9" t="s">
@@ -11365,14 +11372,14 @@
       <c r="U314" s="10"/>
     </row>
     <row r="315" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C315" s="17"/>
-      <c r="D315" s="17"/>
-      <c r="E315" s="17"/>
-      <c r="F315" s="17"/>
-      <c r="G315" s="17"/>
-      <c r="H315" s="17"/>
-      <c r="I315" s="18"/>
-      <c r="J315" s="22"/>
+      <c r="C315" s="21"/>
+      <c r="D315" s="21"/>
+      <c r="E315" s="21"/>
+      <c r="F315" s="21"/>
+      <c r="G315" s="21"/>
+      <c r="H315" s="21"/>
+      <c r="I315" s="25"/>
+      <c r="J315" s="26"/>
       <c r="L315" s="11" t="s">
         <v>5</v>
       </c>
@@ -11408,14 +11415,14 @@
       </c>
     </row>
     <row r="316" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C316" s="17"/>
-      <c r="D316" s="17"/>
-      <c r="E316" s="17"/>
-      <c r="F316" s="17"/>
-      <c r="G316" s="17"/>
-      <c r="H316" s="17"/>
-      <c r="I316" s="18"/>
-      <c r="J316" s="22"/>
+      <c r="C316" s="21"/>
+      <c r="D316" s="21"/>
+      <c r="E316" s="21"/>
+      <c r="F316" s="21"/>
+      <c r="G316" s="21"/>
+      <c r="H316" s="21"/>
+      <c r="I316" s="25"/>
+      <c r="J316" s="26"/>
       <c r="L316" s="12" t="s">
         <v>15</v>
       </c>
@@ -11441,14 +11448,14 @@
       </c>
     </row>
     <row r="317" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C317" s="17"/>
-      <c r="D317" s="17"/>
-      <c r="E317" s="17"/>
-      <c r="F317" s="17"/>
-      <c r="G317" s="17"/>
-      <c r="H317" s="17"/>
-      <c r="I317" s="18"/>
-      <c r="J317" s="22"/>
+      <c r="C317" s="21"/>
+      <c r="D317" s="21"/>
+      <c r="E317" s="21"/>
+      <c r="F317" s="21"/>
+      <c r="G317" s="21"/>
+      <c r="H317" s="21"/>
+      <c r="I317" s="25"/>
+      <c r="J317" s="26"/>
       <c r="L317" s="14" t="s">
         <v>17</v>
       </c>
@@ -11471,14 +11478,14 @@
       <c r="U317" s="10"/>
     </row>
     <row r="318" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C318" s="17"/>
-      <c r="D318" s="17"/>
-      <c r="E318" s="17"/>
-      <c r="F318" s="17"/>
-      <c r="G318" s="17"/>
-      <c r="H318" s="17"/>
-      <c r="I318" s="18"/>
-      <c r="J318" s="22"/>
+      <c r="C318" s="21"/>
+      <c r="D318" s="21"/>
+      <c r="E318" s="21"/>
+      <c r="F318" s="21"/>
+      <c r="G318" s="21"/>
+      <c r="H318" s="21"/>
+      <c r="I318" s="25"/>
+      <c r="J318" s="26"/>
       <c r="L318" s="15" t="s">
         <v>23</v>
       </c>
@@ -11498,26 +11505,26 @@
       <c r="B319" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C319" s="17" t="s">
+      <c r="C319" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D319" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E319" s="18" t="s">
+      <c r="D319" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E319" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F319" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G319" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H319" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I319" s="17"/>
-      <c r="J319" s="27" t="s">
+      <c r="F319" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G319" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H319" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I319" s="21"/>
+      <c r="J319" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L319" s="9" t="s">
@@ -11545,14 +11552,14 @@
       <c r="B320">
         <v>30</v>
       </c>
-      <c r="C320" s="17"/>
-      <c r="D320" s="23"/>
-      <c r="E320" s="18"/>
-      <c r="F320" s="17"/>
-      <c r="G320" s="17"/>
-      <c r="H320" s="22"/>
-      <c r="I320" s="17"/>
-      <c r="J320" s="27"/>
+      <c r="C320" s="21"/>
+      <c r="D320" s="22"/>
+      <c r="E320" s="25"/>
+      <c r="F320" s="21"/>
+      <c r="G320" s="21"/>
+      <c r="H320" s="26"/>
+      <c r="I320" s="21"/>
+      <c r="J320" s="20"/>
       <c r="L320" s="11" t="s">
         <v>5</v>
       </c>
@@ -11591,14 +11598,14 @@
       <c r="B321" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C321" s="17"/>
-      <c r="D321" s="23"/>
-      <c r="E321" s="18"/>
-      <c r="F321" s="17"/>
-      <c r="G321" s="17"/>
-      <c r="H321" s="22"/>
-      <c r="I321" s="17"/>
-      <c r="J321" s="27"/>
+      <c r="C321" s="21"/>
+      <c r="D321" s="22"/>
+      <c r="E321" s="25"/>
+      <c r="F321" s="21"/>
+      <c r="G321" s="21"/>
+      <c r="H321" s="26"/>
+      <c r="I321" s="21"/>
+      <c r="J321" s="20"/>
       <c r="L321" s="12" t="s">
         <v>15</v>
       </c>
@@ -11627,14 +11634,14 @@
       <c r="B322">
         <v>13</v>
       </c>
-      <c r="C322" s="17"/>
-      <c r="D322" s="23"/>
-      <c r="E322" s="18"/>
-      <c r="F322" s="17"/>
-      <c r="G322" s="17"/>
-      <c r="H322" s="22"/>
-      <c r="I322" s="17"/>
-      <c r="J322" s="27"/>
+      <c r="C322" s="21"/>
+      <c r="D322" s="22"/>
+      <c r="E322" s="25"/>
+      <c r="F322" s="21"/>
+      <c r="G322" s="21"/>
+      <c r="H322" s="26"/>
+      <c r="I322" s="21"/>
+      <c r="J322" s="20"/>
       <c r="L322" s="14" t="s">
         <v>17</v>
       </c>
@@ -11659,14 +11666,14 @@
       <c r="U322" s="10"/>
     </row>
     <row r="323" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C323" s="17"/>
-      <c r="D323" s="23"/>
-      <c r="E323" s="18"/>
-      <c r="F323" s="17"/>
-      <c r="G323" s="17"/>
-      <c r="H323" s="22"/>
-      <c r="I323" s="17"/>
-      <c r="J323" s="27"/>
+      <c r="C323" s="21"/>
+      <c r="D323" s="22"/>
+      <c r="E323" s="25"/>
+      <c r="F323" s="21"/>
+      <c r="G323" s="21"/>
+      <c r="H323" s="26"/>
+      <c r="I323" s="21"/>
+      <c r="J323" s="20"/>
       <c r="L323" s="15" t="s">
         <v>23</v>
       </c>
@@ -11683,26 +11690,26 @@
       <c r="U323" s="10"/>
     </row>
     <row r="324" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C324" s="17" t="s">
+      <c r="C324" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D324" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E324" s="23"/>
-      <c r="F324" s="18" t="s">
+      <c r="D324" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E324" s="22"/>
+      <c r="F324" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G324" s="18" t="s">
+      <c r="G324" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H324" s="18" t="s">
+      <c r="H324" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I324" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J324" s="17"/>
+      <c r="I324" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J324" s="21"/>
       <c r="L324" s="9" t="s">
         <v>0</v>
       </c>
@@ -11725,14 +11732,14 @@
       <c r="U324" s="10"/>
     </row>
     <row r="325" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C325" s="17"/>
-      <c r="D325" s="17"/>
-      <c r="E325" s="23"/>
-      <c r="F325" s="18"/>
-      <c r="G325" s="18"/>
-      <c r="H325" s="18"/>
-      <c r="I325" s="22"/>
-      <c r="J325" s="17"/>
+      <c r="C325" s="21"/>
+      <c r="D325" s="21"/>
+      <c r="E325" s="22"/>
+      <c r="F325" s="25"/>
+      <c r="G325" s="25"/>
+      <c r="H325" s="25"/>
+      <c r="I325" s="26"/>
+      <c r="J325" s="21"/>
       <c r="L325" s="11" t="s">
         <v>5</v>
       </c>
@@ -11768,14 +11775,14 @@
       </c>
     </row>
     <row r="326" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C326" s="17"/>
-      <c r="D326" s="17"/>
-      <c r="E326" s="23"/>
-      <c r="F326" s="18"/>
-      <c r="G326" s="18"/>
-      <c r="H326" s="18"/>
-      <c r="I326" s="22"/>
-      <c r="J326" s="17"/>
+      <c r="C326" s="21"/>
+      <c r="D326" s="21"/>
+      <c r="E326" s="22"/>
+      <c r="F326" s="25"/>
+      <c r="G326" s="25"/>
+      <c r="H326" s="25"/>
+      <c r="I326" s="26"/>
+      <c r="J326" s="21"/>
       <c r="L326" s="12" t="s">
         <v>15</v>
       </c>
@@ -11801,14 +11808,14 @@
       </c>
     </row>
     <row r="327" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C327" s="17"/>
-      <c r="D327" s="17"/>
-      <c r="E327" s="23"/>
-      <c r="F327" s="18"/>
-      <c r="G327" s="18"/>
-      <c r="H327" s="18"/>
-      <c r="I327" s="22"/>
-      <c r="J327" s="17"/>
+      <c r="C327" s="21"/>
+      <c r="D327" s="21"/>
+      <c r="E327" s="22"/>
+      <c r="F327" s="25"/>
+      <c r="G327" s="25"/>
+      <c r="H327" s="25"/>
+      <c r="I327" s="26"/>
+      <c r="J327" s="21"/>
       <c r="L327" s="14" t="s">
         <v>17</v>
       </c>
@@ -11831,14 +11838,14 @@
       <c r="U327" s="10"/>
     </row>
     <row r="328" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C328" s="17"/>
-      <c r="D328" s="17"/>
-      <c r="E328" s="23"/>
-      <c r="F328" s="18"/>
-      <c r="G328" s="18"/>
-      <c r="H328" s="18"/>
-      <c r="I328" s="22"/>
-      <c r="J328" s="17"/>
+      <c r="C328" s="21"/>
+      <c r="D328" s="21"/>
+      <c r="E328" s="22"/>
+      <c r="F328" s="25"/>
+      <c r="G328" s="25"/>
+      <c r="H328" s="25"/>
+      <c r="I328" s="26"/>
+      <c r="J328" s="21"/>
       <c r="L328" s="15" t="s">
         <v>23</v>
       </c>
@@ -11861,26 +11868,26 @@
       <c r="B330" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C330" s="17" t="s">
+      <c r="C330" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D330" s="18" t="s">
+      <c r="D330" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E330" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F330" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G330" s="17"/>
-      <c r="H330" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I330" s="25" t="s">
+      <c r="E330" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F330" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G330" s="21"/>
+      <c r="H330" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I330" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J330" s="17"/>
+      <c r="J330" s="21"/>
       <c r="L330" s="9" t="s">
         <v>0</v>
       </c>
@@ -11906,14 +11913,14 @@
       <c r="B331">
         <v>31</v>
       </c>
-      <c r="C331" s="17"/>
-      <c r="D331" s="18"/>
-      <c r="E331" s="23"/>
-      <c r="F331" s="22"/>
-      <c r="G331" s="17"/>
-      <c r="H331" s="17"/>
-      <c r="I331" s="26"/>
-      <c r="J331" s="17"/>
+      <c r="C331" s="21"/>
+      <c r="D331" s="25"/>
+      <c r="E331" s="22"/>
+      <c r="F331" s="26"/>
+      <c r="G331" s="21"/>
+      <c r="H331" s="21"/>
+      <c r="I331" s="24"/>
+      <c r="J331" s="21"/>
       <c r="L331" s="11" t="s">
         <v>5</v>
       </c>
@@ -11949,14 +11956,14 @@
       </c>
     </row>
     <row r="332" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C332" s="17"/>
-      <c r="D332" s="18"/>
-      <c r="E332" s="23"/>
-      <c r="F332" s="22"/>
-      <c r="G332" s="17"/>
-      <c r="H332" s="17"/>
-      <c r="I332" s="26"/>
-      <c r="J332" s="17"/>
+      <c r="C332" s="21"/>
+      <c r="D332" s="25"/>
+      <c r="E332" s="22"/>
+      <c r="F332" s="26"/>
+      <c r="G332" s="21"/>
+      <c r="H332" s="21"/>
+      <c r="I332" s="24"/>
+      <c r="J332" s="21"/>
       <c r="L332" s="12" t="s">
         <v>15</v>
       </c>
@@ -11982,14 +11989,14 @@
       </c>
     </row>
     <row r="333" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C333" s="17"/>
-      <c r="D333" s="18"/>
-      <c r="E333" s="23"/>
-      <c r="F333" s="22"/>
-      <c r="G333" s="17"/>
-      <c r="H333" s="17"/>
-      <c r="I333" s="26"/>
-      <c r="J333" s="17"/>
+      <c r="C333" s="21"/>
+      <c r="D333" s="25"/>
+      <c r="E333" s="22"/>
+      <c r="F333" s="26"/>
+      <c r="G333" s="21"/>
+      <c r="H333" s="21"/>
+      <c r="I333" s="24"/>
+      <c r="J333" s="21"/>
       <c r="L333" s="14" t="s">
         <v>17</v>
       </c>
@@ -12013,14 +12020,14 @@
       <c r="U333" s="10"/>
     </row>
     <row r="334" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C334" s="17"/>
-      <c r="D334" s="18"/>
-      <c r="E334" s="23"/>
-      <c r="F334" s="22"/>
-      <c r="G334" s="17"/>
-      <c r="H334" s="17"/>
-      <c r="I334" s="26"/>
-      <c r="J334" s="17"/>
+      <c r="C334" s="21"/>
+      <c r="D334" s="25"/>
+      <c r="E334" s="22"/>
+      <c r="F334" s="26"/>
+      <c r="G334" s="21"/>
+      <c r="H334" s="21"/>
+      <c r="I334" s="24"/>
+      <c r="J334" s="21"/>
       <c r="L334" s="15" t="s">
         <v>23</v>
       </c>
@@ -12037,24 +12044,24 @@
       <c r="U334" s="10"/>
     </row>
     <row r="335" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C335" s="17" t="s">
+      <c r="C335" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D335" s="17"/>
-      <c r="E335" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F335" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G335" s="17"/>
-      <c r="H335" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I335" s="18" t="s">
+      <c r="D335" s="21"/>
+      <c r="E335" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F335" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G335" s="21"/>
+      <c r="H335" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I335" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J335" s="22" t="s">
+      <c r="J335" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L335" s="9" t="s">
@@ -12079,14 +12086,14 @@
       <c r="U335" s="10"/>
     </row>
     <row r="336" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C336" s="17"/>
-      <c r="D336" s="17"/>
-      <c r="E336" s="17"/>
-      <c r="F336" s="17"/>
-      <c r="G336" s="17"/>
-      <c r="H336" s="17"/>
-      <c r="I336" s="18"/>
-      <c r="J336" s="22"/>
+      <c r="C336" s="21"/>
+      <c r="D336" s="21"/>
+      <c r="E336" s="21"/>
+      <c r="F336" s="21"/>
+      <c r="G336" s="21"/>
+      <c r="H336" s="21"/>
+      <c r="I336" s="25"/>
+      <c r="J336" s="26"/>
       <c r="L336" s="11" t="s">
         <v>5</v>
       </c>
@@ -12122,14 +12129,14 @@
       </c>
     </row>
     <row r="337" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C337" s="17"/>
-      <c r="D337" s="17"/>
-      <c r="E337" s="17"/>
-      <c r="F337" s="17"/>
-      <c r="G337" s="17"/>
-      <c r="H337" s="17"/>
-      <c r="I337" s="18"/>
-      <c r="J337" s="22"/>
+      <c r="C337" s="21"/>
+      <c r="D337" s="21"/>
+      <c r="E337" s="21"/>
+      <c r="F337" s="21"/>
+      <c r="G337" s="21"/>
+      <c r="H337" s="21"/>
+      <c r="I337" s="25"/>
+      <c r="J337" s="26"/>
       <c r="L337" s="12" t="s">
         <v>15</v>
       </c>
@@ -12155,14 +12162,14 @@
       </c>
     </row>
     <row r="338" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C338" s="17"/>
-      <c r="D338" s="17"/>
-      <c r="E338" s="17"/>
-      <c r="F338" s="17"/>
-      <c r="G338" s="17"/>
-      <c r="H338" s="17"/>
-      <c r="I338" s="18"/>
-      <c r="J338" s="22"/>
+      <c r="C338" s="21"/>
+      <c r="D338" s="21"/>
+      <c r="E338" s="21"/>
+      <c r="F338" s="21"/>
+      <c r="G338" s="21"/>
+      <c r="H338" s="21"/>
+      <c r="I338" s="25"/>
+      <c r="J338" s="26"/>
       <c r="L338" s="14" t="s">
         <v>17</v>
       </c>
@@ -12185,14 +12192,14 @@
       <c r="U338" s="10"/>
     </row>
     <row r="339" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C339" s="17"/>
-      <c r="D339" s="17"/>
-      <c r="E339" s="17"/>
-      <c r="F339" s="17"/>
-      <c r="G339" s="17"/>
-      <c r="H339" s="17"/>
-      <c r="I339" s="18"/>
-      <c r="J339" s="22"/>
+      <c r="C339" s="21"/>
+      <c r="D339" s="21"/>
+      <c r="E339" s="21"/>
+      <c r="F339" s="21"/>
+      <c r="G339" s="21"/>
+      <c r="H339" s="21"/>
+      <c r="I339" s="25"/>
+      <c r="J339" s="26"/>
       <c r="L339" s="15" t="s">
         <v>23</v>
       </c>
@@ -12209,24 +12216,24 @@
       <c r="U339" s="10"/>
     </row>
     <row r="340" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C340" s="17" t="s">
+      <c r="C340" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D340" s="17"/>
-      <c r="E340" s="18" t="s">
+      <c r="D340" s="21"/>
+      <c r="E340" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F340" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G340" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H340" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I340" s="17"/>
-      <c r="J340" s="27" t="s">
+      <c r="F340" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G340" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H340" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I340" s="21"/>
+      <c r="J340" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L340" s="9" t="s">
@@ -12251,14 +12258,14 @@
       <c r="U340" s="10"/>
     </row>
     <row r="341" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C341" s="17"/>
-      <c r="D341" s="17"/>
-      <c r="E341" s="18"/>
-      <c r="F341" s="17"/>
-      <c r="G341" s="22"/>
-      <c r="H341" s="17"/>
-      <c r="I341" s="17"/>
-      <c r="J341" s="27"/>
+      <c r="C341" s="21"/>
+      <c r="D341" s="21"/>
+      <c r="E341" s="25"/>
+      <c r="F341" s="21"/>
+      <c r="G341" s="26"/>
+      <c r="H341" s="21"/>
+      <c r="I341" s="21"/>
+      <c r="J341" s="20"/>
       <c r="L341" s="11" t="s">
         <v>5</v>
       </c>
@@ -12297,14 +12304,14 @@
       <c r="B342" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C342" s="17"/>
-      <c r="D342" s="17"/>
-      <c r="E342" s="18"/>
-      <c r="F342" s="17"/>
-      <c r="G342" s="22"/>
-      <c r="H342" s="17"/>
-      <c r="I342" s="17"/>
-      <c r="J342" s="27"/>
+      <c r="C342" s="21"/>
+      <c r="D342" s="21"/>
+      <c r="E342" s="25"/>
+      <c r="F342" s="21"/>
+      <c r="G342" s="26"/>
+      <c r="H342" s="21"/>
+      <c r="I342" s="21"/>
+      <c r="J342" s="20"/>
       <c r="L342" s="12" t="s">
         <v>15</v>
       </c>
@@ -12333,14 +12340,14 @@
       <c r="B343">
         <v>14</v>
       </c>
-      <c r="C343" s="17"/>
-      <c r="D343" s="17"/>
-      <c r="E343" s="18"/>
-      <c r="F343" s="17"/>
-      <c r="G343" s="22"/>
-      <c r="H343" s="17"/>
-      <c r="I343" s="17"/>
-      <c r="J343" s="27"/>
+      <c r="C343" s="21"/>
+      <c r="D343" s="21"/>
+      <c r="E343" s="25"/>
+      <c r="F343" s="21"/>
+      <c r="G343" s="26"/>
+      <c r="H343" s="21"/>
+      <c r="I343" s="21"/>
+      <c r="J343" s="20"/>
       <c r="L343" s="14" t="s">
         <v>17</v>
       </c>
@@ -12364,14 +12371,14 @@
       <c r="U343" s="10"/>
     </row>
     <row r="344" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C344" s="17"/>
-      <c r="D344" s="17"/>
-      <c r="E344" s="18"/>
-      <c r="F344" s="17"/>
-      <c r="G344" s="22"/>
-      <c r="H344" s="17"/>
-      <c r="I344" s="17"/>
-      <c r="J344" s="27"/>
+      <c r="C344" s="21"/>
+      <c r="D344" s="21"/>
+      <c r="E344" s="25"/>
+      <c r="F344" s="21"/>
+      <c r="G344" s="26"/>
+      <c r="H344" s="21"/>
+      <c r="I344" s="21"/>
+      <c r="J344" s="20"/>
       <c r="L344" s="15" t="s">
         <v>23</v>
       </c>
@@ -12388,24 +12395,24 @@
       <c r="U344" s="10"/>
     </row>
     <row r="345" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C345" s="17" t="s">
+      <c r="C345" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D345" s="17"/>
-      <c r="E345" s="23"/>
-      <c r="F345" s="18" t="s">
+      <c r="D345" s="21"/>
+      <c r="E345" s="22"/>
+      <c r="F345" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G345" s="18" t="s">
+      <c r="G345" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H345" s="18" t="s">
+      <c r="H345" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I345" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J345" s="17"/>
+      <c r="I345" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J345" s="21"/>
       <c r="L345" s="9" t="s">
         <v>0</v>
       </c>
@@ -12428,14 +12435,14 @@
       <c r="U345" s="10"/>
     </row>
     <row r="346" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C346" s="17"/>
-      <c r="D346" s="17"/>
-      <c r="E346" s="23"/>
-      <c r="F346" s="18"/>
-      <c r="G346" s="18"/>
-      <c r="H346" s="18"/>
-      <c r="I346" s="22"/>
-      <c r="J346" s="17"/>
+      <c r="C346" s="21"/>
+      <c r="D346" s="21"/>
+      <c r="E346" s="22"/>
+      <c r="F346" s="25"/>
+      <c r="G346" s="25"/>
+      <c r="H346" s="25"/>
+      <c r="I346" s="26"/>
+      <c r="J346" s="21"/>
       <c r="L346" s="11" t="s">
         <v>5</v>
       </c>
@@ -12471,14 +12478,14 @@
       </c>
     </row>
     <row r="347" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C347" s="17"/>
-      <c r="D347" s="17"/>
-      <c r="E347" s="23"/>
-      <c r="F347" s="18"/>
-      <c r="G347" s="18"/>
-      <c r="H347" s="18"/>
-      <c r="I347" s="22"/>
-      <c r="J347" s="17"/>
+      <c r="C347" s="21"/>
+      <c r="D347" s="21"/>
+      <c r="E347" s="22"/>
+      <c r="F347" s="25"/>
+      <c r="G347" s="25"/>
+      <c r="H347" s="25"/>
+      <c r="I347" s="26"/>
+      <c r="J347" s="21"/>
       <c r="L347" s="12" t="s">
         <v>15</v>
       </c>
@@ -12504,14 +12511,14 @@
       </c>
     </row>
     <row r="348" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C348" s="17"/>
-      <c r="D348" s="17"/>
-      <c r="E348" s="23"/>
-      <c r="F348" s="18"/>
-      <c r="G348" s="18"/>
-      <c r="H348" s="18"/>
-      <c r="I348" s="22"/>
-      <c r="J348" s="17"/>
+      <c r="C348" s="21"/>
+      <c r="D348" s="21"/>
+      <c r="E348" s="22"/>
+      <c r="F348" s="25"/>
+      <c r="G348" s="25"/>
+      <c r="H348" s="25"/>
+      <c r="I348" s="26"/>
+      <c r="J348" s="21"/>
       <c r="L348" s="14" t="s">
         <v>17</v>
       </c>
@@ -12534,14 +12541,14 @@
       <c r="U348" s="10"/>
     </row>
     <row r="349" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C349" s="17"/>
-      <c r="D349" s="17"/>
-      <c r="E349" s="23"/>
-      <c r="F349" s="18"/>
-      <c r="G349" s="18"/>
-      <c r="H349" s="18"/>
-      <c r="I349" s="22"/>
-      <c r="J349" s="17"/>
+      <c r="C349" s="21"/>
+      <c r="D349" s="21"/>
+      <c r="E349" s="22"/>
+      <c r="F349" s="25"/>
+      <c r="G349" s="25"/>
+      <c r="H349" s="25"/>
+      <c r="I349" s="26"/>
+      <c r="J349" s="21"/>
       <c r="L349" s="15" t="s">
         <v>23</v>
       </c>
@@ -12561,18 +12568,18 @@
       <c r="P350" s="10"/>
     </row>
     <row r="351" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C351" s="17" t="s">
+      <c r="C351" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D351" s="17"/>
-      <c r="E351" s="23"/>
-      <c r="F351" s="23"/>
-      <c r="G351" s="17"/>
-      <c r="H351" s="17"/>
-      <c r="I351" s="25" t="s">
+      <c r="D351" s="21"/>
+      <c r="E351" s="22"/>
+      <c r="F351" s="22"/>
+      <c r="G351" s="21"/>
+      <c r="H351" s="21"/>
+      <c r="I351" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J351" s="17"/>
+      <c r="J351" s="21"/>
       <c r="L351" s="9" t="s">
         <v>0</v>
       </c>
@@ -12595,14 +12602,14 @@
       <c r="U351" s="10"/>
     </row>
     <row r="352" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C352" s="17"/>
-      <c r="D352" s="17"/>
-      <c r="E352" s="23"/>
-      <c r="F352" s="23"/>
-      <c r="G352" s="17"/>
-      <c r="H352" s="17"/>
-      <c r="I352" s="26"/>
-      <c r="J352" s="17"/>
+      <c r="C352" s="21"/>
+      <c r="D352" s="21"/>
+      <c r="E352" s="22"/>
+      <c r="F352" s="22"/>
+      <c r="G352" s="21"/>
+      <c r="H352" s="21"/>
+      <c r="I352" s="24"/>
+      <c r="J352" s="21"/>
       <c r="L352" s="11" t="s">
         <v>5</v>
       </c>
@@ -12638,14 +12645,14 @@
       </c>
     </row>
     <row r="353" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C353" s="17"/>
-      <c r="D353" s="17"/>
-      <c r="E353" s="23"/>
-      <c r="F353" s="23"/>
-      <c r="G353" s="17"/>
-      <c r="H353" s="17"/>
-      <c r="I353" s="26"/>
-      <c r="J353" s="17"/>
+      <c r="C353" s="21"/>
+      <c r="D353" s="21"/>
+      <c r="E353" s="22"/>
+      <c r="F353" s="22"/>
+      <c r="G353" s="21"/>
+      <c r="H353" s="21"/>
+      <c r="I353" s="24"/>
+      <c r="J353" s="21"/>
       <c r="L353" s="12" t="s">
         <v>15</v>
       </c>
@@ -12663,14 +12670,14 @@
       <c r="V353" s="10"/>
     </row>
     <row r="354" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C354" s="17"/>
-      <c r="D354" s="17"/>
-      <c r="E354" s="23"/>
-      <c r="F354" s="23"/>
-      <c r="G354" s="17"/>
-      <c r="H354" s="17"/>
-      <c r="I354" s="26"/>
-      <c r="J354" s="17"/>
+      <c r="C354" s="21"/>
+      <c r="D354" s="21"/>
+      <c r="E354" s="22"/>
+      <c r="F354" s="22"/>
+      <c r="G354" s="21"/>
+      <c r="H354" s="21"/>
+      <c r="I354" s="24"/>
+      <c r="J354" s="21"/>
       <c r="L354" s="14" t="s">
         <v>17</v>
       </c>
@@ -12693,14 +12700,14 @@
       <c r="U354" s="10"/>
     </row>
     <row r="355" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C355" s="17"/>
-      <c r="D355" s="17"/>
-      <c r="E355" s="23"/>
-      <c r="F355" s="23"/>
-      <c r="G355" s="17"/>
-      <c r="H355" s="17"/>
-      <c r="I355" s="26"/>
-      <c r="J355" s="17"/>
+      <c r="C355" s="21"/>
+      <c r="D355" s="21"/>
+      <c r="E355" s="22"/>
+      <c r="F355" s="22"/>
+      <c r="G355" s="21"/>
+      <c r="H355" s="21"/>
+      <c r="I355" s="24"/>
+      <c r="J355" s="21"/>
       <c r="L355" s="15" t="s">
         <v>23</v>
       </c>
@@ -12717,18 +12724,18 @@
       <c r="U355" s="10"/>
     </row>
     <row r="356" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C356" s="17" t="s">
+      <c r="C356" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D356" s="17"/>
-      <c r="E356" s="23"/>
-      <c r="F356" s="23"/>
-      <c r="G356" s="17"/>
-      <c r="H356" s="17"/>
-      <c r="I356" s="18" t="s">
+      <c r="D356" s="21"/>
+      <c r="E356" s="22"/>
+      <c r="F356" s="22"/>
+      <c r="G356" s="21"/>
+      <c r="H356" s="21"/>
+      <c r="I356" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J356" s="22" t="s">
+      <c r="J356" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L356" s="9" t="s">
@@ -12753,14 +12760,14 @@
       <c r="U356" s="10"/>
     </row>
     <row r="357" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C357" s="17"/>
-      <c r="D357" s="17"/>
-      <c r="E357" s="23"/>
-      <c r="F357" s="23"/>
-      <c r="G357" s="17"/>
-      <c r="H357" s="17"/>
-      <c r="I357" s="18"/>
-      <c r="J357" s="22"/>
+      <c r="C357" s="21"/>
+      <c r="D357" s="21"/>
+      <c r="E357" s="22"/>
+      <c r="F357" s="22"/>
+      <c r="G357" s="21"/>
+      <c r="H357" s="21"/>
+      <c r="I357" s="25"/>
+      <c r="J357" s="26"/>
       <c r="L357" s="11" t="s">
         <v>5</v>
       </c>
@@ -12796,14 +12803,14 @@
       </c>
     </row>
     <row r="358" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C358" s="17"/>
-      <c r="D358" s="17"/>
-      <c r="E358" s="23"/>
-      <c r="F358" s="23"/>
-      <c r="G358" s="17"/>
-      <c r="H358" s="17"/>
-      <c r="I358" s="18"/>
-      <c r="J358" s="22"/>
+      <c r="C358" s="21"/>
+      <c r="D358" s="21"/>
+      <c r="E358" s="22"/>
+      <c r="F358" s="22"/>
+      <c r="G358" s="21"/>
+      <c r="H358" s="21"/>
+      <c r="I358" s="25"/>
+      <c r="J358" s="26"/>
       <c r="L358" s="12" t="s">
         <v>15</v>
       </c>
@@ -12829,14 +12836,14 @@
       </c>
     </row>
     <row r="359" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C359" s="17"/>
-      <c r="D359" s="17"/>
-      <c r="E359" s="23"/>
-      <c r="F359" s="23"/>
-      <c r="G359" s="17"/>
-      <c r="H359" s="17"/>
-      <c r="I359" s="18"/>
-      <c r="J359" s="22"/>
+      <c r="C359" s="21"/>
+      <c r="D359" s="21"/>
+      <c r="E359" s="22"/>
+      <c r="F359" s="22"/>
+      <c r="G359" s="21"/>
+      <c r="H359" s="21"/>
+      <c r="I359" s="25"/>
+      <c r="J359" s="26"/>
       <c r="L359" s="14" t="s">
         <v>17</v>
       </c>
@@ -12859,14 +12866,14 @@
       <c r="U359" s="10"/>
     </row>
     <row r="360" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C360" s="17"/>
-      <c r="D360" s="17"/>
-      <c r="E360" s="23"/>
-      <c r="F360" s="23"/>
-      <c r="G360" s="17"/>
-      <c r="H360" s="17"/>
-      <c r="I360" s="18"/>
-      <c r="J360" s="22"/>
+      <c r="C360" s="21"/>
+      <c r="D360" s="21"/>
+      <c r="E360" s="22"/>
+      <c r="F360" s="22"/>
+      <c r="G360" s="21"/>
+      <c r="H360" s="21"/>
+      <c r="I360" s="25"/>
+      <c r="J360" s="26"/>
       <c r="L360" s="15" t="s">
         <v>23</v>
       </c>
@@ -12883,16 +12890,16 @@
       <c r="U360" s="10"/>
     </row>
     <row r="361" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C361" s="17" t="s">
+      <c r="C361" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D361" s="17"/>
-      <c r="E361" s="23"/>
-      <c r="F361" s="23"/>
-      <c r="G361" s="17"/>
-      <c r="H361" s="17"/>
-      <c r="I361" s="28"/>
-      <c r="J361" s="27" t="s">
+      <c r="D361" s="21"/>
+      <c r="E361" s="22"/>
+      <c r="F361" s="22"/>
+      <c r="G361" s="21"/>
+      <c r="H361" s="21"/>
+      <c r="I361" s="17"/>
+      <c r="J361" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L361" s="9" t="s">
@@ -12917,14 +12924,14 @@
       <c r="U361" s="10"/>
     </row>
     <row r="362" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C362" s="17"/>
-      <c r="D362" s="17"/>
-      <c r="E362" s="23"/>
-      <c r="F362" s="23"/>
-      <c r="G362" s="17"/>
-      <c r="H362" s="17"/>
-      <c r="I362" s="29"/>
-      <c r="J362" s="27"/>
+      <c r="C362" s="21"/>
+      <c r="D362" s="21"/>
+      <c r="E362" s="22"/>
+      <c r="F362" s="22"/>
+      <c r="G362" s="21"/>
+      <c r="H362" s="21"/>
+      <c r="I362" s="18"/>
+      <c r="J362" s="20"/>
       <c r="L362" s="11" t="s">
         <v>5</v>
       </c>
@@ -12963,14 +12970,14 @@
       <c r="B363" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C363" s="17"/>
-      <c r="D363" s="17"/>
-      <c r="E363" s="23"/>
-      <c r="F363" s="23"/>
-      <c r="G363" s="17"/>
-      <c r="H363" s="17"/>
-      <c r="I363" s="29"/>
-      <c r="J363" s="27"/>
+      <c r="C363" s="21"/>
+      <c r="D363" s="21"/>
+      <c r="E363" s="22"/>
+      <c r="F363" s="22"/>
+      <c r="G363" s="21"/>
+      <c r="H363" s="21"/>
+      <c r="I363" s="18"/>
+      <c r="J363" s="20"/>
       <c r="L363" s="12" t="s">
         <v>15</v>
       </c>
@@ -12991,14 +12998,14 @@
       <c r="B364">
         <v>15</v>
       </c>
-      <c r="C364" s="17"/>
-      <c r="D364" s="17"/>
-      <c r="E364" s="23"/>
-      <c r="F364" s="23"/>
-      <c r="G364" s="17"/>
-      <c r="H364" s="17"/>
-      <c r="I364" s="29"/>
-      <c r="J364" s="27"/>
+      <c r="C364" s="21"/>
+      <c r="D364" s="21"/>
+      <c r="E364" s="22"/>
+      <c r="F364" s="22"/>
+      <c r="G364" s="21"/>
+      <c r="H364" s="21"/>
+      <c r="I364" s="18"/>
+      <c r="J364" s="20"/>
       <c r="L364" s="14" t="s">
         <v>17</v>
       </c>
@@ -13022,14 +13029,14 @@
       <c r="U364" s="10"/>
     </row>
     <row r="365" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C365" s="17"/>
-      <c r="D365" s="17"/>
-      <c r="E365" s="23"/>
-      <c r="F365" s="23"/>
-      <c r="G365" s="17"/>
-      <c r="H365" s="17"/>
-      <c r="I365" s="30"/>
-      <c r="J365" s="27"/>
+      <c r="C365" s="21"/>
+      <c r="D365" s="21"/>
+      <c r="E365" s="22"/>
+      <c r="F365" s="22"/>
+      <c r="G365" s="21"/>
+      <c r="H365" s="21"/>
+      <c r="I365" s="19"/>
+      <c r="J365" s="20"/>
       <c r="L365" s="15" t="s">
         <v>23</v>
       </c>
@@ -13049,6 +13056,518 @@
     </row>
   </sheetData>
   <mergeCells count="536">
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="H7:H11"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="G22:G26"/>
+    <mergeCell ref="H22:H26"/>
+    <mergeCell ref="I22:I26"/>
+    <mergeCell ref="J22:J26"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="J34:J38"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="I39:I43"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="D44:D48"/>
+    <mergeCell ref="E44:E48"/>
+    <mergeCell ref="F44:F48"/>
+    <mergeCell ref="G44:G48"/>
+    <mergeCell ref="H44:H48"/>
+    <mergeCell ref="I44:I48"/>
+    <mergeCell ref="J44:J48"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="D39:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="H39:H43"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="D55:D59"/>
+    <mergeCell ref="E55:E59"/>
+    <mergeCell ref="F55:F59"/>
+    <mergeCell ref="G55:G59"/>
+    <mergeCell ref="H55:H59"/>
+    <mergeCell ref="I55:I59"/>
+    <mergeCell ref="J55:J59"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="I60:I64"/>
+    <mergeCell ref="J60:J64"/>
+    <mergeCell ref="C65:C69"/>
+    <mergeCell ref="D65:D69"/>
+    <mergeCell ref="E65:E69"/>
+    <mergeCell ref="F65:F69"/>
+    <mergeCell ref="G65:G69"/>
+    <mergeCell ref="H65:H69"/>
+    <mergeCell ref="I65:I69"/>
+    <mergeCell ref="J65:J69"/>
+    <mergeCell ref="C60:C64"/>
+    <mergeCell ref="D60:D64"/>
+    <mergeCell ref="E60:E64"/>
+    <mergeCell ref="F60:F64"/>
+    <mergeCell ref="G60:G64"/>
+    <mergeCell ref="H60:H64"/>
+    <mergeCell ref="I71:I75"/>
+    <mergeCell ref="J71:J75"/>
+    <mergeCell ref="C76:C80"/>
+    <mergeCell ref="D76:D80"/>
+    <mergeCell ref="E76:E80"/>
+    <mergeCell ref="F76:F80"/>
+    <mergeCell ref="G76:G80"/>
+    <mergeCell ref="H76:H80"/>
+    <mergeCell ref="I76:I80"/>
+    <mergeCell ref="J76:J80"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="E71:E75"/>
+    <mergeCell ref="F71:F75"/>
+    <mergeCell ref="G71:G75"/>
+    <mergeCell ref="H71:H75"/>
+    <mergeCell ref="I81:I85"/>
+    <mergeCell ref="J81:J85"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="D86:D90"/>
+    <mergeCell ref="E86:E90"/>
+    <mergeCell ref="F86:F90"/>
+    <mergeCell ref="G86:G90"/>
+    <mergeCell ref="H86:H90"/>
+    <mergeCell ref="I86:I90"/>
+    <mergeCell ref="J86:J90"/>
+    <mergeCell ref="C81:C85"/>
+    <mergeCell ref="D81:D85"/>
+    <mergeCell ref="E81:E85"/>
+    <mergeCell ref="F81:F85"/>
+    <mergeCell ref="G81:G85"/>
+    <mergeCell ref="H81:H85"/>
+    <mergeCell ref="I93:I97"/>
+    <mergeCell ref="J93:J97"/>
+    <mergeCell ref="C98:C102"/>
+    <mergeCell ref="D98:D102"/>
+    <mergeCell ref="E98:E102"/>
+    <mergeCell ref="F98:F102"/>
+    <mergeCell ref="G98:G102"/>
+    <mergeCell ref="H98:H102"/>
+    <mergeCell ref="I98:I102"/>
+    <mergeCell ref="J98:J102"/>
+    <mergeCell ref="C93:C97"/>
+    <mergeCell ref="D93:D97"/>
+    <mergeCell ref="E93:E97"/>
+    <mergeCell ref="F93:F97"/>
+    <mergeCell ref="G93:G97"/>
+    <mergeCell ref="H93:H97"/>
+    <mergeCell ref="I103:I107"/>
+    <mergeCell ref="J103:J107"/>
+    <mergeCell ref="C108:C112"/>
+    <mergeCell ref="D108:D112"/>
+    <mergeCell ref="E108:E112"/>
+    <mergeCell ref="F108:F112"/>
+    <mergeCell ref="G108:G112"/>
+    <mergeCell ref="H108:H112"/>
+    <mergeCell ref="I108:I112"/>
+    <mergeCell ref="J108:J112"/>
+    <mergeCell ref="C103:C107"/>
+    <mergeCell ref="D103:D107"/>
+    <mergeCell ref="E103:E107"/>
+    <mergeCell ref="F103:F107"/>
+    <mergeCell ref="G103:G107"/>
+    <mergeCell ref="H103:H107"/>
+    <mergeCell ref="I114:I118"/>
+    <mergeCell ref="J114:J118"/>
+    <mergeCell ref="C119:C123"/>
+    <mergeCell ref="D119:D123"/>
+    <mergeCell ref="E119:E123"/>
+    <mergeCell ref="F119:F123"/>
+    <mergeCell ref="G119:G123"/>
+    <mergeCell ref="H119:H123"/>
+    <mergeCell ref="I119:I123"/>
+    <mergeCell ref="J119:J123"/>
+    <mergeCell ref="C114:C118"/>
+    <mergeCell ref="D114:D118"/>
+    <mergeCell ref="E114:E118"/>
+    <mergeCell ref="F114:F118"/>
+    <mergeCell ref="G114:G118"/>
+    <mergeCell ref="H114:H118"/>
+    <mergeCell ref="I124:I128"/>
+    <mergeCell ref="J124:J128"/>
+    <mergeCell ref="C129:C133"/>
+    <mergeCell ref="D129:D133"/>
+    <mergeCell ref="E129:E133"/>
+    <mergeCell ref="F129:F133"/>
+    <mergeCell ref="G129:G133"/>
+    <mergeCell ref="H129:H133"/>
+    <mergeCell ref="I129:I133"/>
+    <mergeCell ref="J129:J133"/>
+    <mergeCell ref="C124:C128"/>
+    <mergeCell ref="D124:D128"/>
+    <mergeCell ref="E124:E128"/>
+    <mergeCell ref="F124:F128"/>
+    <mergeCell ref="G124:G128"/>
+    <mergeCell ref="H124:H128"/>
+    <mergeCell ref="I135:I139"/>
+    <mergeCell ref="J135:J139"/>
+    <mergeCell ref="C140:C144"/>
+    <mergeCell ref="D140:D144"/>
+    <mergeCell ref="E140:E144"/>
+    <mergeCell ref="F140:F144"/>
+    <mergeCell ref="G140:G144"/>
+    <mergeCell ref="H140:H144"/>
+    <mergeCell ref="I140:I144"/>
+    <mergeCell ref="J140:J144"/>
+    <mergeCell ref="C135:C139"/>
+    <mergeCell ref="D135:D139"/>
+    <mergeCell ref="E135:E139"/>
+    <mergeCell ref="F135:F139"/>
+    <mergeCell ref="G135:G139"/>
+    <mergeCell ref="H135:H139"/>
+    <mergeCell ref="I145:I149"/>
+    <mergeCell ref="J145:J149"/>
+    <mergeCell ref="C150:C154"/>
+    <mergeCell ref="D150:D154"/>
+    <mergeCell ref="E150:E154"/>
+    <mergeCell ref="F150:F154"/>
+    <mergeCell ref="G150:G154"/>
+    <mergeCell ref="H150:H154"/>
+    <mergeCell ref="I150:I154"/>
+    <mergeCell ref="J150:J154"/>
+    <mergeCell ref="C145:C149"/>
+    <mergeCell ref="D145:D149"/>
+    <mergeCell ref="E145:E149"/>
+    <mergeCell ref="F145:F149"/>
+    <mergeCell ref="G145:G149"/>
+    <mergeCell ref="H145:H149"/>
+    <mergeCell ref="I157:I161"/>
+    <mergeCell ref="J157:J161"/>
+    <mergeCell ref="C162:C166"/>
+    <mergeCell ref="D162:D166"/>
+    <mergeCell ref="E162:E166"/>
+    <mergeCell ref="F162:F166"/>
+    <mergeCell ref="G162:G166"/>
+    <mergeCell ref="H162:H166"/>
+    <mergeCell ref="I162:I166"/>
+    <mergeCell ref="J162:J166"/>
+    <mergeCell ref="C157:C161"/>
+    <mergeCell ref="D157:D161"/>
+    <mergeCell ref="E157:E161"/>
+    <mergeCell ref="F157:F161"/>
+    <mergeCell ref="G157:G161"/>
+    <mergeCell ref="H157:H161"/>
+    <mergeCell ref="I167:I171"/>
+    <mergeCell ref="J167:J171"/>
+    <mergeCell ref="C172:C176"/>
+    <mergeCell ref="D172:D176"/>
+    <mergeCell ref="E172:E176"/>
+    <mergeCell ref="F172:F176"/>
+    <mergeCell ref="G172:G176"/>
+    <mergeCell ref="H172:H176"/>
+    <mergeCell ref="I172:I176"/>
+    <mergeCell ref="J172:J176"/>
+    <mergeCell ref="C167:C171"/>
+    <mergeCell ref="D167:D171"/>
+    <mergeCell ref="E167:E171"/>
+    <mergeCell ref="F167:F171"/>
+    <mergeCell ref="G167:G171"/>
+    <mergeCell ref="H167:H171"/>
+    <mergeCell ref="I178:I182"/>
+    <mergeCell ref="J178:J182"/>
+    <mergeCell ref="C183:C187"/>
+    <mergeCell ref="D183:D187"/>
+    <mergeCell ref="E183:E187"/>
+    <mergeCell ref="F183:F187"/>
+    <mergeCell ref="G183:G187"/>
+    <mergeCell ref="H183:H187"/>
+    <mergeCell ref="I183:I187"/>
+    <mergeCell ref="J183:J187"/>
+    <mergeCell ref="C178:C182"/>
+    <mergeCell ref="D178:D182"/>
+    <mergeCell ref="E178:E182"/>
+    <mergeCell ref="F178:F182"/>
+    <mergeCell ref="G178:G182"/>
+    <mergeCell ref="H178:H182"/>
+    <mergeCell ref="I188:I192"/>
+    <mergeCell ref="J188:J192"/>
+    <mergeCell ref="C193:C197"/>
+    <mergeCell ref="D193:D197"/>
+    <mergeCell ref="E193:E197"/>
+    <mergeCell ref="F193:F197"/>
+    <mergeCell ref="G193:G197"/>
+    <mergeCell ref="H193:H197"/>
+    <mergeCell ref="I193:I197"/>
+    <mergeCell ref="J193:J197"/>
+    <mergeCell ref="C188:C192"/>
+    <mergeCell ref="D188:D192"/>
+    <mergeCell ref="E188:E192"/>
+    <mergeCell ref="F188:F192"/>
+    <mergeCell ref="G188:G192"/>
+    <mergeCell ref="H188:H192"/>
+    <mergeCell ref="I199:I203"/>
+    <mergeCell ref="J199:J203"/>
+    <mergeCell ref="C204:C208"/>
+    <mergeCell ref="D204:D208"/>
+    <mergeCell ref="E204:E208"/>
+    <mergeCell ref="F204:F208"/>
+    <mergeCell ref="G204:G208"/>
+    <mergeCell ref="H204:H208"/>
+    <mergeCell ref="I204:I208"/>
+    <mergeCell ref="J204:J208"/>
+    <mergeCell ref="C199:C203"/>
+    <mergeCell ref="D199:D203"/>
+    <mergeCell ref="E199:E203"/>
+    <mergeCell ref="F199:F203"/>
+    <mergeCell ref="G199:G203"/>
+    <mergeCell ref="H199:H203"/>
+    <mergeCell ref="I209:I213"/>
+    <mergeCell ref="J209:J213"/>
+    <mergeCell ref="C214:C218"/>
+    <mergeCell ref="D214:D218"/>
+    <mergeCell ref="E214:E218"/>
+    <mergeCell ref="F214:F218"/>
+    <mergeCell ref="G214:G218"/>
+    <mergeCell ref="H214:H218"/>
+    <mergeCell ref="I214:I218"/>
+    <mergeCell ref="J214:J218"/>
+    <mergeCell ref="C209:C213"/>
+    <mergeCell ref="D209:D213"/>
+    <mergeCell ref="E209:E213"/>
+    <mergeCell ref="F209:F213"/>
+    <mergeCell ref="G209:G213"/>
+    <mergeCell ref="H209:H213"/>
+    <mergeCell ref="I221:I225"/>
+    <mergeCell ref="J221:J225"/>
+    <mergeCell ref="C226:C230"/>
+    <mergeCell ref="D226:D230"/>
+    <mergeCell ref="E226:E230"/>
+    <mergeCell ref="F226:F230"/>
+    <mergeCell ref="G226:G230"/>
+    <mergeCell ref="H226:H230"/>
+    <mergeCell ref="I226:I230"/>
+    <mergeCell ref="J226:J230"/>
+    <mergeCell ref="C221:C225"/>
+    <mergeCell ref="D221:D225"/>
+    <mergeCell ref="E221:E225"/>
+    <mergeCell ref="F221:F225"/>
+    <mergeCell ref="G221:G225"/>
+    <mergeCell ref="H221:H225"/>
+    <mergeCell ref="I231:I235"/>
+    <mergeCell ref="J231:J235"/>
+    <mergeCell ref="C236:C240"/>
+    <mergeCell ref="D236:D240"/>
+    <mergeCell ref="E236:E240"/>
+    <mergeCell ref="F236:F240"/>
+    <mergeCell ref="G236:G240"/>
+    <mergeCell ref="H236:H240"/>
+    <mergeCell ref="I236:I240"/>
+    <mergeCell ref="J236:J240"/>
+    <mergeCell ref="C231:C235"/>
+    <mergeCell ref="D231:D235"/>
+    <mergeCell ref="E231:E235"/>
+    <mergeCell ref="F231:F235"/>
+    <mergeCell ref="G231:G235"/>
+    <mergeCell ref="H231:H235"/>
+    <mergeCell ref="I242:I246"/>
+    <mergeCell ref="J242:J246"/>
+    <mergeCell ref="C247:C251"/>
+    <mergeCell ref="D247:D251"/>
+    <mergeCell ref="E247:E251"/>
+    <mergeCell ref="F247:F251"/>
+    <mergeCell ref="G247:G251"/>
+    <mergeCell ref="H247:H251"/>
+    <mergeCell ref="I247:I251"/>
+    <mergeCell ref="J247:J251"/>
+    <mergeCell ref="C242:C246"/>
+    <mergeCell ref="D242:D246"/>
+    <mergeCell ref="E242:E246"/>
+    <mergeCell ref="F242:F246"/>
+    <mergeCell ref="G242:G246"/>
+    <mergeCell ref="H242:H246"/>
+    <mergeCell ref="I252:I256"/>
+    <mergeCell ref="J252:J256"/>
+    <mergeCell ref="C257:C261"/>
+    <mergeCell ref="D257:D261"/>
+    <mergeCell ref="E257:E261"/>
+    <mergeCell ref="F257:F261"/>
+    <mergeCell ref="G257:G261"/>
+    <mergeCell ref="H257:H261"/>
+    <mergeCell ref="I257:I261"/>
+    <mergeCell ref="J257:J261"/>
+    <mergeCell ref="C252:C256"/>
+    <mergeCell ref="D252:D256"/>
+    <mergeCell ref="E252:E256"/>
+    <mergeCell ref="F252:F256"/>
+    <mergeCell ref="G252:G256"/>
+    <mergeCell ref="H252:H256"/>
+    <mergeCell ref="I263:I267"/>
+    <mergeCell ref="J263:J267"/>
+    <mergeCell ref="C268:C272"/>
+    <mergeCell ref="D268:D272"/>
+    <mergeCell ref="E268:E272"/>
+    <mergeCell ref="F268:F272"/>
+    <mergeCell ref="G268:G272"/>
+    <mergeCell ref="H268:H272"/>
+    <mergeCell ref="I268:I272"/>
+    <mergeCell ref="J268:J272"/>
+    <mergeCell ref="C263:C267"/>
+    <mergeCell ref="D263:D267"/>
+    <mergeCell ref="E263:E267"/>
+    <mergeCell ref="F263:F267"/>
+    <mergeCell ref="G263:G267"/>
+    <mergeCell ref="H263:H267"/>
+    <mergeCell ref="I273:I277"/>
+    <mergeCell ref="J273:J277"/>
+    <mergeCell ref="C278:C282"/>
+    <mergeCell ref="D278:D282"/>
+    <mergeCell ref="E278:E282"/>
+    <mergeCell ref="F278:F282"/>
+    <mergeCell ref="G278:G282"/>
+    <mergeCell ref="H278:H282"/>
+    <mergeCell ref="I278:I282"/>
+    <mergeCell ref="J278:J282"/>
+    <mergeCell ref="C273:C277"/>
+    <mergeCell ref="D273:D277"/>
+    <mergeCell ref="E273:E277"/>
+    <mergeCell ref="F273:F277"/>
+    <mergeCell ref="G273:G277"/>
+    <mergeCell ref="H273:H277"/>
+    <mergeCell ref="I288:I292"/>
+    <mergeCell ref="J288:J292"/>
+    <mergeCell ref="C293:C297"/>
+    <mergeCell ref="D293:D297"/>
+    <mergeCell ref="E293:E297"/>
+    <mergeCell ref="F293:F297"/>
+    <mergeCell ref="G293:G297"/>
+    <mergeCell ref="H293:H297"/>
+    <mergeCell ref="I293:I297"/>
+    <mergeCell ref="J293:J297"/>
+    <mergeCell ref="C288:C292"/>
+    <mergeCell ref="D288:D292"/>
+    <mergeCell ref="E288:E292"/>
+    <mergeCell ref="F288:F292"/>
+    <mergeCell ref="G288:G292"/>
+    <mergeCell ref="H288:H292"/>
+    <mergeCell ref="I298:I302"/>
+    <mergeCell ref="J298:J302"/>
+    <mergeCell ref="C303:C307"/>
+    <mergeCell ref="D303:D307"/>
+    <mergeCell ref="E303:E307"/>
+    <mergeCell ref="F303:F307"/>
+    <mergeCell ref="G303:G307"/>
+    <mergeCell ref="H303:H307"/>
+    <mergeCell ref="I303:I307"/>
+    <mergeCell ref="J303:J307"/>
+    <mergeCell ref="C298:C302"/>
+    <mergeCell ref="D298:D302"/>
+    <mergeCell ref="E298:E302"/>
+    <mergeCell ref="F298:F302"/>
+    <mergeCell ref="G298:G302"/>
+    <mergeCell ref="H298:H302"/>
+    <mergeCell ref="I309:I313"/>
+    <mergeCell ref="J309:J313"/>
+    <mergeCell ref="C314:C318"/>
+    <mergeCell ref="D314:D318"/>
+    <mergeCell ref="E314:E318"/>
+    <mergeCell ref="F314:F318"/>
+    <mergeCell ref="G314:G318"/>
+    <mergeCell ref="H314:H318"/>
+    <mergeCell ref="I314:I318"/>
+    <mergeCell ref="J314:J318"/>
+    <mergeCell ref="C309:C313"/>
+    <mergeCell ref="D309:D313"/>
+    <mergeCell ref="E309:E313"/>
+    <mergeCell ref="F309:F313"/>
+    <mergeCell ref="G309:G313"/>
+    <mergeCell ref="H309:H313"/>
+    <mergeCell ref="I319:I323"/>
+    <mergeCell ref="J319:J323"/>
+    <mergeCell ref="C324:C328"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="E324:E328"/>
+    <mergeCell ref="F324:F328"/>
+    <mergeCell ref="G324:G328"/>
+    <mergeCell ref="H324:H328"/>
+    <mergeCell ref="I324:I328"/>
+    <mergeCell ref="J324:J328"/>
+    <mergeCell ref="C319:C323"/>
+    <mergeCell ref="D319:D323"/>
+    <mergeCell ref="E319:E323"/>
+    <mergeCell ref="F319:F323"/>
+    <mergeCell ref="G319:G323"/>
+    <mergeCell ref="H319:H323"/>
+    <mergeCell ref="I330:I334"/>
+    <mergeCell ref="J330:J334"/>
+    <mergeCell ref="C335:C339"/>
+    <mergeCell ref="D335:D339"/>
+    <mergeCell ref="E335:E339"/>
+    <mergeCell ref="F335:F339"/>
+    <mergeCell ref="G335:G339"/>
+    <mergeCell ref="H335:H339"/>
+    <mergeCell ref="I335:I339"/>
+    <mergeCell ref="J335:J339"/>
+    <mergeCell ref="C330:C334"/>
+    <mergeCell ref="D330:D334"/>
+    <mergeCell ref="E330:E334"/>
+    <mergeCell ref="F330:F334"/>
+    <mergeCell ref="G330:G334"/>
+    <mergeCell ref="H330:H334"/>
+    <mergeCell ref="I340:I344"/>
+    <mergeCell ref="J340:J344"/>
+    <mergeCell ref="C345:C349"/>
+    <mergeCell ref="D345:D349"/>
+    <mergeCell ref="E345:E349"/>
+    <mergeCell ref="F345:F349"/>
+    <mergeCell ref="G345:G349"/>
+    <mergeCell ref="H345:H349"/>
+    <mergeCell ref="I345:I349"/>
+    <mergeCell ref="J345:J349"/>
+    <mergeCell ref="C340:C344"/>
+    <mergeCell ref="D340:D344"/>
+    <mergeCell ref="E340:E344"/>
+    <mergeCell ref="F340:F344"/>
+    <mergeCell ref="G340:G344"/>
+    <mergeCell ref="H340:H344"/>
     <mergeCell ref="I361:I365"/>
     <mergeCell ref="J361:J365"/>
     <mergeCell ref="C361:C365"/>
@@ -13073,518 +13592,6 @@
     <mergeCell ref="F351:F355"/>
     <mergeCell ref="G351:G355"/>
     <mergeCell ref="H351:H355"/>
-    <mergeCell ref="I340:I344"/>
-    <mergeCell ref="J340:J344"/>
-    <mergeCell ref="C345:C349"/>
-    <mergeCell ref="D345:D349"/>
-    <mergeCell ref="E345:E349"/>
-    <mergeCell ref="F345:F349"/>
-    <mergeCell ref="G345:G349"/>
-    <mergeCell ref="H345:H349"/>
-    <mergeCell ref="I345:I349"/>
-    <mergeCell ref="J345:J349"/>
-    <mergeCell ref="C340:C344"/>
-    <mergeCell ref="D340:D344"/>
-    <mergeCell ref="E340:E344"/>
-    <mergeCell ref="F340:F344"/>
-    <mergeCell ref="G340:G344"/>
-    <mergeCell ref="H340:H344"/>
-    <mergeCell ref="I330:I334"/>
-    <mergeCell ref="J330:J334"/>
-    <mergeCell ref="C335:C339"/>
-    <mergeCell ref="D335:D339"/>
-    <mergeCell ref="E335:E339"/>
-    <mergeCell ref="F335:F339"/>
-    <mergeCell ref="G335:G339"/>
-    <mergeCell ref="H335:H339"/>
-    <mergeCell ref="I335:I339"/>
-    <mergeCell ref="J335:J339"/>
-    <mergeCell ref="C330:C334"/>
-    <mergeCell ref="D330:D334"/>
-    <mergeCell ref="E330:E334"/>
-    <mergeCell ref="F330:F334"/>
-    <mergeCell ref="G330:G334"/>
-    <mergeCell ref="H330:H334"/>
-    <mergeCell ref="I319:I323"/>
-    <mergeCell ref="J319:J323"/>
-    <mergeCell ref="C324:C328"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="E324:E328"/>
-    <mergeCell ref="F324:F328"/>
-    <mergeCell ref="G324:G328"/>
-    <mergeCell ref="H324:H328"/>
-    <mergeCell ref="I324:I328"/>
-    <mergeCell ref="J324:J328"/>
-    <mergeCell ref="C319:C323"/>
-    <mergeCell ref="D319:D323"/>
-    <mergeCell ref="E319:E323"/>
-    <mergeCell ref="F319:F323"/>
-    <mergeCell ref="G319:G323"/>
-    <mergeCell ref="H319:H323"/>
-    <mergeCell ref="I309:I313"/>
-    <mergeCell ref="J309:J313"/>
-    <mergeCell ref="C314:C318"/>
-    <mergeCell ref="D314:D318"/>
-    <mergeCell ref="E314:E318"/>
-    <mergeCell ref="F314:F318"/>
-    <mergeCell ref="G314:G318"/>
-    <mergeCell ref="H314:H318"/>
-    <mergeCell ref="I314:I318"/>
-    <mergeCell ref="J314:J318"/>
-    <mergeCell ref="C309:C313"/>
-    <mergeCell ref="D309:D313"/>
-    <mergeCell ref="E309:E313"/>
-    <mergeCell ref="F309:F313"/>
-    <mergeCell ref="G309:G313"/>
-    <mergeCell ref="H309:H313"/>
-    <mergeCell ref="I298:I302"/>
-    <mergeCell ref="J298:J302"/>
-    <mergeCell ref="C303:C307"/>
-    <mergeCell ref="D303:D307"/>
-    <mergeCell ref="E303:E307"/>
-    <mergeCell ref="F303:F307"/>
-    <mergeCell ref="G303:G307"/>
-    <mergeCell ref="H303:H307"/>
-    <mergeCell ref="I303:I307"/>
-    <mergeCell ref="J303:J307"/>
-    <mergeCell ref="C298:C302"/>
-    <mergeCell ref="D298:D302"/>
-    <mergeCell ref="E298:E302"/>
-    <mergeCell ref="F298:F302"/>
-    <mergeCell ref="G298:G302"/>
-    <mergeCell ref="H298:H302"/>
-    <mergeCell ref="I288:I292"/>
-    <mergeCell ref="J288:J292"/>
-    <mergeCell ref="C293:C297"/>
-    <mergeCell ref="D293:D297"/>
-    <mergeCell ref="E293:E297"/>
-    <mergeCell ref="F293:F297"/>
-    <mergeCell ref="G293:G297"/>
-    <mergeCell ref="H293:H297"/>
-    <mergeCell ref="I293:I297"/>
-    <mergeCell ref="J293:J297"/>
-    <mergeCell ref="C288:C292"/>
-    <mergeCell ref="D288:D292"/>
-    <mergeCell ref="E288:E292"/>
-    <mergeCell ref="F288:F292"/>
-    <mergeCell ref="G288:G292"/>
-    <mergeCell ref="H288:H292"/>
-    <mergeCell ref="I273:I277"/>
-    <mergeCell ref="J273:J277"/>
-    <mergeCell ref="C278:C282"/>
-    <mergeCell ref="D278:D282"/>
-    <mergeCell ref="E278:E282"/>
-    <mergeCell ref="F278:F282"/>
-    <mergeCell ref="G278:G282"/>
-    <mergeCell ref="H278:H282"/>
-    <mergeCell ref="I278:I282"/>
-    <mergeCell ref="J278:J282"/>
-    <mergeCell ref="C273:C277"/>
-    <mergeCell ref="D273:D277"/>
-    <mergeCell ref="E273:E277"/>
-    <mergeCell ref="F273:F277"/>
-    <mergeCell ref="G273:G277"/>
-    <mergeCell ref="H273:H277"/>
-    <mergeCell ref="I263:I267"/>
-    <mergeCell ref="J263:J267"/>
-    <mergeCell ref="C268:C272"/>
-    <mergeCell ref="D268:D272"/>
-    <mergeCell ref="E268:E272"/>
-    <mergeCell ref="F268:F272"/>
-    <mergeCell ref="G268:G272"/>
-    <mergeCell ref="H268:H272"/>
-    <mergeCell ref="I268:I272"/>
-    <mergeCell ref="J268:J272"/>
-    <mergeCell ref="C263:C267"/>
-    <mergeCell ref="D263:D267"/>
-    <mergeCell ref="E263:E267"/>
-    <mergeCell ref="F263:F267"/>
-    <mergeCell ref="G263:G267"/>
-    <mergeCell ref="H263:H267"/>
-    <mergeCell ref="I252:I256"/>
-    <mergeCell ref="J252:J256"/>
-    <mergeCell ref="C257:C261"/>
-    <mergeCell ref="D257:D261"/>
-    <mergeCell ref="E257:E261"/>
-    <mergeCell ref="F257:F261"/>
-    <mergeCell ref="G257:G261"/>
-    <mergeCell ref="H257:H261"/>
-    <mergeCell ref="I257:I261"/>
-    <mergeCell ref="J257:J261"/>
-    <mergeCell ref="C252:C256"/>
-    <mergeCell ref="D252:D256"/>
-    <mergeCell ref="E252:E256"/>
-    <mergeCell ref="F252:F256"/>
-    <mergeCell ref="G252:G256"/>
-    <mergeCell ref="H252:H256"/>
-    <mergeCell ref="I242:I246"/>
-    <mergeCell ref="J242:J246"/>
-    <mergeCell ref="C247:C251"/>
-    <mergeCell ref="D247:D251"/>
-    <mergeCell ref="E247:E251"/>
-    <mergeCell ref="F247:F251"/>
-    <mergeCell ref="G247:G251"/>
-    <mergeCell ref="H247:H251"/>
-    <mergeCell ref="I247:I251"/>
-    <mergeCell ref="J247:J251"/>
-    <mergeCell ref="C242:C246"/>
-    <mergeCell ref="D242:D246"/>
-    <mergeCell ref="E242:E246"/>
-    <mergeCell ref="F242:F246"/>
-    <mergeCell ref="G242:G246"/>
-    <mergeCell ref="H242:H246"/>
-    <mergeCell ref="I231:I235"/>
-    <mergeCell ref="J231:J235"/>
-    <mergeCell ref="C236:C240"/>
-    <mergeCell ref="D236:D240"/>
-    <mergeCell ref="E236:E240"/>
-    <mergeCell ref="F236:F240"/>
-    <mergeCell ref="G236:G240"/>
-    <mergeCell ref="H236:H240"/>
-    <mergeCell ref="I236:I240"/>
-    <mergeCell ref="J236:J240"/>
-    <mergeCell ref="C231:C235"/>
-    <mergeCell ref="D231:D235"/>
-    <mergeCell ref="E231:E235"/>
-    <mergeCell ref="F231:F235"/>
-    <mergeCell ref="G231:G235"/>
-    <mergeCell ref="H231:H235"/>
-    <mergeCell ref="I221:I225"/>
-    <mergeCell ref="J221:J225"/>
-    <mergeCell ref="C226:C230"/>
-    <mergeCell ref="D226:D230"/>
-    <mergeCell ref="E226:E230"/>
-    <mergeCell ref="F226:F230"/>
-    <mergeCell ref="G226:G230"/>
-    <mergeCell ref="H226:H230"/>
-    <mergeCell ref="I226:I230"/>
-    <mergeCell ref="J226:J230"/>
-    <mergeCell ref="C221:C225"/>
-    <mergeCell ref="D221:D225"/>
-    <mergeCell ref="E221:E225"/>
-    <mergeCell ref="F221:F225"/>
-    <mergeCell ref="G221:G225"/>
-    <mergeCell ref="H221:H225"/>
-    <mergeCell ref="I209:I213"/>
-    <mergeCell ref="J209:J213"/>
-    <mergeCell ref="C214:C218"/>
-    <mergeCell ref="D214:D218"/>
-    <mergeCell ref="E214:E218"/>
-    <mergeCell ref="F214:F218"/>
-    <mergeCell ref="G214:G218"/>
-    <mergeCell ref="H214:H218"/>
-    <mergeCell ref="I214:I218"/>
-    <mergeCell ref="J214:J218"/>
-    <mergeCell ref="C209:C213"/>
-    <mergeCell ref="D209:D213"/>
-    <mergeCell ref="E209:E213"/>
-    <mergeCell ref="F209:F213"/>
-    <mergeCell ref="G209:G213"/>
-    <mergeCell ref="H209:H213"/>
-    <mergeCell ref="I199:I203"/>
-    <mergeCell ref="J199:J203"/>
-    <mergeCell ref="C204:C208"/>
-    <mergeCell ref="D204:D208"/>
-    <mergeCell ref="E204:E208"/>
-    <mergeCell ref="F204:F208"/>
-    <mergeCell ref="G204:G208"/>
-    <mergeCell ref="H204:H208"/>
-    <mergeCell ref="I204:I208"/>
-    <mergeCell ref="J204:J208"/>
-    <mergeCell ref="C199:C203"/>
-    <mergeCell ref="D199:D203"/>
-    <mergeCell ref="E199:E203"/>
-    <mergeCell ref="F199:F203"/>
-    <mergeCell ref="G199:G203"/>
-    <mergeCell ref="H199:H203"/>
-    <mergeCell ref="I188:I192"/>
-    <mergeCell ref="J188:J192"/>
-    <mergeCell ref="C193:C197"/>
-    <mergeCell ref="D193:D197"/>
-    <mergeCell ref="E193:E197"/>
-    <mergeCell ref="F193:F197"/>
-    <mergeCell ref="G193:G197"/>
-    <mergeCell ref="H193:H197"/>
-    <mergeCell ref="I193:I197"/>
-    <mergeCell ref="J193:J197"/>
-    <mergeCell ref="C188:C192"/>
-    <mergeCell ref="D188:D192"/>
-    <mergeCell ref="E188:E192"/>
-    <mergeCell ref="F188:F192"/>
-    <mergeCell ref="G188:G192"/>
-    <mergeCell ref="H188:H192"/>
-    <mergeCell ref="I178:I182"/>
-    <mergeCell ref="J178:J182"/>
-    <mergeCell ref="C183:C187"/>
-    <mergeCell ref="D183:D187"/>
-    <mergeCell ref="E183:E187"/>
-    <mergeCell ref="F183:F187"/>
-    <mergeCell ref="G183:G187"/>
-    <mergeCell ref="H183:H187"/>
-    <mergeCell ref="I183:I187"/>
-    <mergeCell ref="J183:J187"/>
-    <mergeCell ref="C178:C182"/>
-    <mergeCell ref="D178:D182"/>
-    <mergeCell ref="E178:E182"/>
-    <mergeCell ref="F178:F182"/>
-    <mergeCell ref="G178:G182"/>
-    <mergeCell ref="H178:H182"/>
-    <mergeCell ref="I167:I171"/>
-    <mergeCell ref="J167:J171"/>
-    <mergeCell ref="C172:C176"/>
-    <mergeCell ref="D172:D176"/>
-    <mergeCell ref="E172:E176"/>
-    <mergeCell ref="F172:F176"/>
-    <mergeCell ref="G172:G176"/>
-    <mergeCell ref="H172:H176"/>
-    <mergeCell ref="I172:I176"/>
-    <mergeCell ref="J172:J176"/>
-    <mergeCell ref="C167:C171"/>
-    <mergeCell ref="D167:D171"/>
-    <mergeCell ref="E167:E171"/>
-    <mergeCell ref="F167:F171"/>
-    <mergeCell ref="G167:G171"/>
-    <mergeCell ref="H167:H171"/>
-    <mergeCell ref="I157:I161"/>
-    <mergeCell ref="J157:J161"/>
-    <mergeCell ref="C162:C166"/>
-    <mergeCell ref="D162:D166"/>
-    <mergeCell ref="E162:E166"/>
-    <mergeCell ref="F162:F166"/>
-    <mergeCell ref="G162:G166"/>
-    <mergeCell ref="H162:H166"/>
-    <mergeCell ref="I162:I166"/>
-    <mergeCell ref="J162:J166"/>
-    <mergeCell ref="C157:C161"/>
-    <mergeCell ref="D157:D161"/>
-    <mergeCell ref="E157:E161"/>
-    <mergeCell ref="F157:F161"/>
-    <mergeCell ref="G157:G161"/>
-    <mergeCell ref="H157:H161"/>
-    <mergeCell ref="I145:I149"/>
-    <mergeCell ref="J145:J149"/>
-    <mergeCell ref="C150:C154"/>
-    <mergeCell ref="D150:D154"/>
-    <mergeCell ref="E150:E154"/>
-    <mergeCell ref="F150:F154"/>
-    <mergeCell ref="G150:G154"/>
-    <mergeCell ref="H150:H154"/>
-    <mergeCell ref="I150:I154"/>
-    <mergeCell ref="J150:J154"/>
-    <mergeCell ref="C145:C149"/>
-    <mergeCell ref="D145:D149"/>
-    <mergeCell ref="E145:E149"/>
-    <mergeCell ref="F145:F149"/>
-    <mergeCell ref="G145:G149"/>
-    <mergeCell ref="H145:H149"/>
-    <mergeCell ref="I135:I139"/>
-    <mergeCell ref="J135:J139"/>
-    <mergeCell ref="C140:C144"/>
-    <mergeCell ref="D140:D144"/>
-    <mergeCell ref="E140:E144"/>
-    <mergeCell ref="F140:F144"/>
-    <mergeCell ref="G140:G144"/>
-    <mergeCell ref="H140:H144"/>
-    <mergeCell ref="I140:I144"/>
-    <mergeCell ref="J140:J144"/>
-    <mergeCell ref="C135:C139"/>
-    <mergeCell ref="D135:D139"/>
-    <mergeCell ref="E135:E139"/>
-    <mergeCell ref="F135:F139"/>
-    <mergeCell ref="G135:G139"/>
-    <mergeCell ref="H135:H139"/>
-    <mergeCell ref="I124:I128"/>
-    <mergeCell ref="J124:J128"/>
-    <mergeCell ref="C129:C133"/>
-    <mergeCell ref="D129:D133"/>
-    <mergeCell ref="E129:E133"/>
-    <mergeCell ref="F129:F133"/>
-    <mergeCell ref="G129:G133"/>
-    <mergeCell ref="H129:H133"/>
-    <mergeCell ref="I129:I133"/>
-    <mergeCell ref="J129:J133"/>
-    <mergeCell ref="C124:C128"/>
-    <mergeCell ref="D124:D128"/>
-    <mergeCell ref="E124:E128"/>
-    <mergeCell ref="F124:F128"/>
-    <mergeCell ref="G124:G128"/>
-    <mergeCell ref="H124:H128"/>
-    <mergeCell ref="I114:I118"/>
-    <mergeCell ref="J114:J118"/>
-    <mergeCell ref="C119:C123"/>
-    <mergeCell ref="D119:D123"/>
-    <mergeCell ref="E119:E123"/>
-    <mergeCell ref="F119:F123"/>
-    <mergeCell ref="G119:G123"/>
-    <mergeCell ref="H119:H123"/>
-    <mergeCell ref="I119:I123"/>
-    <mergeCell ref="J119:J123"/>
-    <mergeCell ref="C114:C118"/>
-    <mergeCell ref="D114:D118"/>
-    <mergeCell ref="E114:E118"/>
-    <mergeCell ref="F114:F118"/>
-    <mergeCell ref="G114:G118"/>
-    <mergeCell ref="H114:H118"/>
-    <mergeCell ref="I103:I107"/>
-    <mergeCell ref="J103:J107"/>
-    <mergeCell ref="C108:C112"/>
-    <mergeCell ref="D108:D112"/>
-    <mergeCell ref="E108:E112"/>
-    <mergeCell ref="F108:F112"/>
-    <mergeCell ref="G108:G112"/>
-    <mergeCell ref="H108:H112"/>
-    <mergeCell ref="I108:I112"/>
-    <mergeCell ref="J108:J112"/>
-    <mergeCell ref="C103:C107"/>
-    <mergeCell ref="D103:D107"/>
-    <mergeCell ref="E103:E107"/>
-    <mergeCell ref="F103:F107"/>
-    <mergeCell ref="G103:G107"/>
-    <mergeCell ref="H103:H107"/>
-    <mergeCell ref="I93:I97"/>
-    <mergeCell ref="J93:J97"/>
-    <mergeCell ref="C98:C102"/>
-    <mergeCell ref="D98:D102"/>
-    <mergeCell ref="E98:E102"/>
-    <mergeCell ref="F98:F102"/>
-    <mergeCell ref="G98:G102"/>
-    <mergeCell ref="H98:H102"/>
-    <mergeCell ref="I98:I102"/>
-    <mergeCell ref="J98:J102"/>
-    <mergeCell ref="C93:C97"/>
-    <mergeCell ref="D93:D97"/>
-    <mergeCell ref="E93:E97"/>
-    <mergeCell ref="F93:F97"/>
-    <mergeCell ref="G93:G97"/>
-    <mergeCell ref="H93:H97"/>
-    <mergeCell ref="I81:I85"/>
-    <mergeCell ref="J81:J85"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="D86:D90"/>
-    <mergeCell ref="E86:E90"/>
-    <mergeCell ref="F86:F90"/>
-    <mergeCell ref="G86:G90"/>
-    <mergeCell ref="H86:H90"/>
-    <mergeCell ref="I86:I90"/>
-    <mergeCell ref="J86:J90"/>
-    <mergeCell ref="C81:C85"/>
-    <mergeCell ref="D81:D85"/>
-    <mergeCell ref="E81:E85"/>
-    <mergeCell ref="F81:F85"/>
-    <mergeCell ref="G81:G85"/>
-    <mergeCell ref="H81:H85"/>
-    <mergeCell ref="I71:I75"/>
-    <mergeCell ref="J71:J75"/>
-    <mergeCell ref="C76:C80"/>
-    <mergeCell ref="D76:D80"/>
-    <mergeCell ref="E76:E80"/>
-    <mergeCell ref="F76:F80"/>
-    <mergeCell ref="G76:G80"/>
-    <mergeCell ref="H76:H80"/>
-    <mergeCell ref="I76:I80"/>
-    <mergeCell ref="J76:J80"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="D71:D75"/>
-    <mergeCell ref="E71:E75"/>
-    <mergeCell ref="F71:F75"/>
-    <mergeCell ref="G71:G75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="I60:I64"/>
-    <mergeCell ref="J60:J64"/>
-    <mergeCell ref="C65:C69"/>
-    <mergeCell ref="D65:D69"/>
-    <mergeCell ref="E65:E69"/>
-    <mergeCell ref="F65:F69"/>
-    <mergeCell ref="G65:G69"/>
-    <mergeCell ref="H65:H69"/>
-    <mergeCell ref="I65:I69"/>
-    <mergeCell ref="J65:J69"/>
-    <mergeCell ref="C60:C64"/>
-    <mergeCell ref="D60:D64"/>
-    <mergeCell ref="E60:E64"/>
-    <mergeCell ref="F60:F64"/>
-    <mergeCell ref="G60:G64"/>
-    <mergeCell ref="H60:H64"/>
-    <mergeCell ref="I50:I54"/>
-    <mergeCell ref="J50:J54"/>
-    <mergeCell ref="C55:C59"/>
-    <mergeCell ref="D55:D59"/>
-    <mergeCell ref="E55:E59"/>
-    <mergeCell ref="F55:F59"/>
-    <mergeCell ref="G55:G59"/>
-    <mergeCell ref="H55:H59"/>
-    <mergeCell ref="I55:I59"/>
-    <mergeCell ref="J55:J59"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="I39:I43"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="D44:D48"/>
-    <mergeCell ref="E44:E48"/>
-    <mergeCell ref="F44:F48"/>
-    <mergeCell ref="G44:G48"/>
-    <mergeCell ref="H44:H48"/>
-    <mergeCell ref="I44:I48"/>
-    <mergeCell ref="J44:J48"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="D39:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="H39:H43"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="J29:J33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="G22:G26"/>
-    <mergeCell ref="H22:H26"/>
-    <mergeCell ref="I22:I26"/>
-    <mergeCell ref="J22:J26"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="H7:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
